--- a/examples/036200_general/036200_model_example.xlsx
+++ b/examples/036200_general/036200_model_example.xlsx
@@ -327,7 +327,7 @@
     <t>기본</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml excel.default_scenario</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml excel.default_scenario</t>
   </si>
   <si>
     <t>🔸</t>
@@ -384,7 +384,7 @@
     <t>날짜</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.as_of</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.as_of</t>
   </si>
   <si>
     <t>2026-09-30</t>
@@ -396,7 +396,7 @@
     <t>할인 기준일(재무상태표일)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.bs_date</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.bs_date</t>
   </si>
   <si>
     <t>순현금(6/30 재무상태표)과 시작점을 맞춘다. EV는 평가기준일로 이월</t>
@@ -405,7 +405,7 @@
     <t>현금흐름 시작일</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.bs_date + 1일</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.bs_date + 1일</t>
   </si>
   <si>
     <t>연 일수</t>
@@ -432,7 +432,7 @@
     <t>mid-year 할인(1=예, 0=기말)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml forecast.mid_year</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml forecast.mid_year</t>
   </si>
   <si>
     <t>명시 기간 마지막 연도(생성 시 고정)</t>
@@ -462,7 +462,7 @@
     <t>consolidated</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure (규칙 판정)</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure (규칙 판정)</t>
   </si>
   <si>
     <t>Bridge 시트의 구조 판단 규칙(valuation_rules.yaml) 결과와 같아야 한다</t>
@@ -588,7 +588,7 @@
     <t>Hamada 세율(언레버·리레버)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml beta.tax</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml beta.tax</t>
   </si>
   <si>
     <t>피어 대부분의 과세표준 구간 한계세율</t>
@@ -612,7 +612,7 @@
     <t>배</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml (공개 모드 집계 입력)</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml (공개 모드 집계 입력)</t>
   </si>
   <si>
     <t>자체 D/E 시점 평균(5개 시점, PC에서 계산한 집계값. 시점별 시가총액은 공개 모드에 표시하지 않음)</t>
@@ -711,7 +711,7 @@
     <t>중요 종속회사 상장 여부(1=예)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure.listed_subsidiary (otrCprInvstmntSttus)</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure.listed_subsidiary (otrCprInvstmntSttus)</t>
   </si>
   <si>
     <t>5. 기계적 예측 규칙 (P7-B 자동 초안 규칙)</t>
@@ -720,7 +720,7 @@
     <t>영구성장률 g(사람 값)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml forecast.human.g_terminal</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml forecast.human.g_terminal</t>
   </si>
   <si>
     <t>세 시나리오 같음. 2030년까지 출발 성장률에서 같은 폭으로 체감</t>
@@ -729,7 +729,7 @@
     <t>출발 성장률 → g 도달 연도</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml params.fade_to_terminal_by</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml params.fade_to_terminal_by</t>
   </si>
   <si>
     <t>2031~2032 = g</t>
@@ -738,7 +738,7 @@
     <t>D&amp;A 반기 ÷ 연간 하한</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml params.ebitda_rule</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml params.ebitda_rule</t>
   </si>
   <si>
     <t>반기 D&amp;A가 3개월 값으로 보이면 LTM = FY D&amp;A</t>
@@ -759,7 +759,7 @@
     <t>%p</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure.segments</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure.segments</t>
   </si>
   <si>
     <t>단일 부문(자동 초안: 부문 미수집)</t>
@@ -870,7 +870,7 @@
     <t>KOSDAQ</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.target.market</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.target.market</t>
   </si>
   <si>
     <t>C3 판정: CV q50 손실 개선</t>
@@ -969,7 +969,7 @@
     <t>곳</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml relative.n_warn</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml relative.n_warn</t>
   </si>
   <si>
     <t>N/M(분모 ≤ 0) 제외 후 표본 수</t>
@@ -1110,7 +1110,7 @@
     <t>정상 이익률 이동</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml scenarios.human · 상태 ⚠️(±2%p 사용자 지시)</t>
+    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml scenarios.human · 상태 ⚠️(±2%p 사용자 지시)</t>
   </si>
   <si>
     <t>표 5. 실제 차입(약정이자율·잔액, Kd 규칙의 '실제 가중' 계산용)</t>
@@ -3615,7 +3615,7 @@
     <t>v1</t>
   </si>
   <si>
-    <t>2026-10-23T08:56:39</t>
+    <t>2026-10-23T11:06:05</t>
   </si>
   <si>
     <t>그대로 유지한 판단 0건 · 남은 미처리 34건</t>
@@ -3816,7 +3816,7 @@
     <t>생성</t>
   </si>
   <si>
-    <t>src/excel/build.py ← C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_yzdskxji/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml (P4, 엔진 형태 mechanical). 결과 확인: Checks 시트의 master check</t>
+    <t>src/excel/build.py ← C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml (P4, 엔진 형태 mechanical). 결과 확인: Checks 시트의 master check</t>
   </si>
   <si>
     <t>현재 선택</t>

--- a/examples/036200_general/036200_model_example.xlsx
+++ b/examples/036200_general/036200_model_example.xlsx
@@ -327,7 +327,7 @@
     <t>기본</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml excel.default_scenario</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml excel.default_scenario</t>
   </si>
   <si>
     <t>🔸</t>
@@ -384,7 +384,7 @@
     <t>날짜</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.as_of</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.as_of</t>
   </si>
   <si>
     <t>2026-09-30</t>
@@ -396,7 +396,7 @@
     <t>할인 기준일(재무상태표일)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.bs_date</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.bs_date</t>
   </si>
   <si>
     <t>순현금(6/30 재무상태표)과 시작점을 맞춘다. EV는 평가기준일로 이월</t>
@@ -405,7 +405,7 @@
     <t>현금흐름 시작일</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.bs_date + 1일</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.bs_date + 1일</t>
   </si>
   <si>
     <t>연 일수</t>
@@ -432,7 +432,7 @@
     <t>mid-year 할인(1=예, 0=기말)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml forecast.mid_year</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml forecast.mid_year</t>
   </si>
   <si>
     <t>명시 기간 마지막 연도(생성 시 고정)</t>
@@ -462,7 +462,7 @@
     <t>consolidated</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure (규칙 판정)</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure (규칙 판정)</t>
   </si>
   <si>
     <t>Bridge 시트의 구조 판단 규칙(valuation_rules.yaml) 결과와 같아야 한다</t>
@@ -588,7 +588,7 @@
     <t>Hamada 세율(언레버·리레버)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml beta.tax</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml beta.tax</t>
   </si>
   <si>
     <t>피어 대부분의 과세표준 구간 한계세율</t>
@@ -612,7 +612,7 @@
     <t>배</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml (공개 모드 집계 입력)</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml (공개 모드 집계 입력)</t>
   </si>
   <si>
     <t>자체 D/E 시점 평균(5개 시점, PC에서 계산한 집계값. 시점별 시가총액은 공개 모드에 표시하지 않음)</t>
@@ -711,7 +711,7 @@
     <t>중요 종속회사 상장 여부(1=예)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure.listed_subsidiary (otrCprInvstmntSttus)</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure.listed_subsidiary (otrCprInvstmntSttus)</t>
   </si>
   <si>
     <t>5. 기계적 예측 규칙 (P7-B 자동 초안 규칙)</t>
@@ -720,7 +720,7 @@
     <t>영구성장률 g(사람 값)</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml forecast.human.g_terminal</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml forecast.human.g_terminal</t>
   </si>
   <si>
     <t>세 시나리오 같음. 2030년까지 출발 성장률에서 같은 폭으로 체감</t>
@@ -729,7 +729,7 @@
     <t>출발 성장률 → g 도달 연도</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml params.fade_to_terminal_by</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml params.fade_to_terminal_by</t>
   </si>
   <si>
     <t>2031~2032 = g</t>
@@ -738,7 +738,7 @@
     <t>D&amp;A 반기 ÷ 연간 하한</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml params.ebitda_rule</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml params.ebitda_rule</t>
   </si>
   <si>
     <t>반기 D&amp;A가 3개월 값으로 보이면 LTM = FY D&amp;A</t>
@@ -759,7 +759,7 @@
     <t>%p</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure.segments</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml structure.segments</t>
   </si>
   <si>
     <t>단일 부문(자동 초안: 부문 미수집)</t>
@@ -870,7 +870,7 @@
     <t>KOSDAQ</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.target.market</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml meta.target.market</t>
   </si>
   <si>
     <t>C3 판정: CV q50 손실 개선</t>
@@ -969,7 +969,7 @@
     <t>곳</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml relative.n_warn</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml relative.n_warn</t>
   </si>
   <si>
     <t>N/M(분모 ≤ 0) 제외 후 표본 수</t>
@@ -1110,7 +1110,7 @@
     <t>정상 이익률 이동</t>
   </si>
   <si>
-    <t>C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml scenarios.human · 상태 ⚠️(±2%p 사용자 지시)</t>
+    <t>공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml scenarios.human · 상태 ⚠️(±2%p 사용자 지시)</t>
   </si>
   <si>
     <t>표 5. 실제 차입(약정이자율·잔액, Kd 규칙의 '실제 가중' 계산용)</t>
@@ -2631,7 +2631,7 @@
     <t>Checks — 모델 점검</t>
   </si>
   <si>
-    <t>ERR가 하나라도 있으면 master check = ERR. WARN은 주의 표시, INFO는 엔진 값 대조(입력을 바꾸면 달라지는 것이 정상)</t>
+    <t>ERR(또는 이 표 안 수식 오류)가 하나라도 있으면 master check = ERR. WARN은 주의 표시, INFO는 엔진 값 대조(입력을 바꾸면 달라지는 것이 정상). N/M = 양쪽 모두 숫자가 아님(일치), 한쪽만 N/M이면 DIFF</t>
   </si>
   <si>
     <t>#</t>
@@ -3615,7 +3615,7 @@
     <t>v1</t>
   </si>
   <si>
-    <t>2026-10-23T11:06:05</t>
+    <t>2026-10-24T02:01:25</t>
   </si>
   <si>
     <t>그대로 유지한 판단 0건 · 남은 미처리 34건</t>
@@ -3816,7 +3816,7 @@
     <t>생성</t>
   </si>
   <si>
-    <t>src/excel/build.py ← C:/Users/Mevius/AppData/Local/Temp/kvi_p7d_dta74qf4/ws/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml (P4, 엔진 형태 mechanical). 결과 확인: Checks 시트의 master check</t>
+    <t>src/excel/build.py ← 공개 배포 작업 공간/sessions/036200_20260930_001/v1_public/valuation_036200_036200_20260930_001v1p.yaml (P4, 엔진 형태 mechanical). 결과 확인: Checks 시트의 master check</t>
   </si>
   <si>
     <t>현재 선택</t>
@@ -15468,11 +15468,11 @@
         <v>915</v>
       </c>
       <c r="C3" s="3" t="str">
-        <f>IF(COUNTIF($C$6:$C$69,"ERR")=0,"OK","ERR")</f>
+        <f>IF(AND(COUNTIF($C$6:$C$69,"ERR")=0,SUMPRODUCT(ISERROR($C$6:$E$69)*1)=0),"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D3" s="7" t="str">
-        <f>"ERR "&amp;COUNTIF($C$6:$C$69,"ERR")&amp;" / WARN "&amp;COUNTIF($C$6:$C$69,"WARN")&amp;" / INFO 차이 "&amp;COUNTIF($C$6:$C$69,"DIFF")</f>
+        <f>"ERR "&amp;COUNTIF($C$6:$C$69,"ERR")&amp;" / WARN "&amp;COUNTIF($C$6:$C$69,"WARN")&amp;" / INFO 차이 "&amp;COUNTIF($C$6:$C$69,"DIFF")&amp;IF(SUMPRODUCT(ISERROR($C$6:$E$69)*1)&gt;0," / 수식 오류 "&amp;SUMPRODUCT(ISERROR($C$6:$E$69)*1),"")</f>
         <v>ERR 0 / WARN 1 / INFO 차이 0</v>
       </c>
     </row>
@@ -15795,11 +15795,11 @@
         <v>804</v>
       </c>
       <c r="C20" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Cover!$A$1:$B$2))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Cover!$A$1:$B$2)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D20" s="5">
-        <f>SUMPRODUCT(--ISERROR(Cover!$A$1:$B$2))</f>
+        <f>SUMPRODUCT(ISERROR(Cover!$A$1:$B$2)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -15820,11 +15820,11 @@
         <v>808</v>
       </c>
       <c r="C21" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Forecast!$A$1:$R$95))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Forecast!$A$1:$R$95)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D21" s="5">
-        <f>SUMPRODUCT(--ISERROR(Forecast!$A$1:$R$95))</f>
+        <f>SUMPRODUCT(ISERROR(Forecast!$A$1:$R$95)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E21" s="7" t="s">
@@ -15845,11 +15845,11 @@
         <v>810</v>
       </c>
       <c r="C22" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(WACC!$A$1:$E$33))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(WACC!$A$1:$E$33)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D22" s="5">
-        <f>SUMPRODUCT(--ISERROR(WACC!$A$1:$E$33))</f>
+        <f>SUMPRODUCT(ISERROR(WACC!$A$1:$E$33)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E22" s="7" t="s">
@@ -15870,11 +15870,11 @@
         <v>812</v>
       </c>
       <c r="C23" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(DCF!$A$1:$R$59))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(DCF!$A$1:$R$59)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D23" s="5">
-        <f>SUMPRODUCT(--ISERROR(DCF!$A$1:$R$59))</f>
+        <f>SUMPRODUCT(ISERROR(DCF!$A$1:$R$59)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E23" s="7" t="s">
@@ -15895,11 +15895,11 @@
         <v>814</v>
       </c>
       <c r="C24" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Bridge!$A$1:$D$28))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Bridge!$A$1:$D$28)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D24" s="5">
-        <f>SUMPRODUCT(--ISERROR(Bridge!$A$1:$D$28))</f>
+        <f>SUMPRODUCT(ISERROR(Bridge!$A$1:$D$28)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E24" s="7" t="s">
@@ -15920,11 +15920,11 @@
         <v>816</v>
       </c>
       <c r="C25" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Peers!$A$1:$N$20))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Peers!$A$1:$N$20)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D25" s="5">
-        <f>SUMPRODUCT(--ISERROR(Peers!$A$1:$N$20))</f>
+        <f>SUMPRODUCT(ISERROR(Peers!$A$1:$N$20)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E25" s="7" t="s">
@@ -15945,11 +15945,11 @@
         <v>818</v>
       </c>
       <c r="C26" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Premium!$A$1:$F$33))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Premium!$A$1:$F$33)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D26" s="5">
-        <f>SUMPRODUCT(--ISERROR(Premium!$A$1:$F$33))</f>
+        <f>SUMPRODUCT(ISERROR(Premium!$A$1:$F$33)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E26" s="7" t="s">
@@ -15970,11 +15970,11 @@
         <v>820</v>
       </c>
       <c r="C27" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Scenarios!$A$1:$T$138))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Scenarios!$A$1:$T$138)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D27" s="5">
-        <f>SUMPRODUCT(--ISERROR(Scenarios!$A$1:$T$138))</f>
+        <f>SUMPRODUCT(ISERROR(Scenarios!$A$1:$T$138)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E27" s="7" t="s">
@@ -15995,11 +15995,11 @@
         <v>822</v>
       </c>
       <c r="C28" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Scen_Calc!$A$1:$R$220))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Scen_Calc!$A$1:$R$220)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D28" s="5">
-        <f>SUMPRODUCT(--ISERROR(Scen_Calc!$A$1:$R$220))</f>
+        <f>SUMPRODUCT(ISERROR(Scen_Calc!$A$1:$R$220)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E28" s="7" t="s">
@@ -16020,11 +16020,11 @@
         <v>824</v>
       </c>
       <c r="C29" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Football!$A$1:$H$15))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Football!$A$1:$H$15)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D29" s="5">
-        <f>SUMPRODUCT(--ISERROR(Football!$A$1:$H$15))</f>
+        <f>SUMPRODUCT(ISERROR(Football!$A$1:$H$15)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E29" s="7" t="s">
@@ -16045,11 +16045,11 @@
         <v>826</v>
       </c>
       <c r="C30" s="6" t="str">
-        <f>IF(SUMPRODUCT(--ISERROR(Convergence!$A$1:$G$17))=0,"OK","ERR")</f>
+        <f>IF(SUMPRODUCT(ISERROR(Convergence!$A$1:$G$17)*1)=0,"OK","ERR")</f>
         <v>OK</v>
       </c>
       <c r="D30" s="5">
-        <f>SUMPRODUCT(--ISERROR(Convergence!$A$1:$G$17))</f>
+        <f>SUMPRODUCT(ISERROR(Convergence!$A$1:$G$17)*1)</f>
         <v>0.0</v>
       </c>
       <c r="E30" s="7" t="s">
@@ -16230,7 +16230,7 @@
         <v>843</v>
       </c>
       <c r="C38" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(PerShare)),NOT(ISNUMBER(INDEX(Scenarios!$B$32:$D$34,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(PerShare-INDEX(Scenarios!$B$32:$D$34,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(PerShare),ISNUMBER(INDEX(Scenarios!$B$32:$D$34,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(PerShare-INDEX(Scenarios!$B$32:$D$34,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(PerShare)),NOT(ISNUMBER(INDEX(Scenarios!$B$32:$D$34,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D38" s="5">
@@ -16256,7 +16256,7 @@
         <v>847</v>
       </c>
       <c r="C39" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(WACC)),NOT(ISNUMBER(INDEX(Scenarios!$B$37:$D$39,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(WACC-INDEX(Scenarios!$B$37:$D$39,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(WACC),ISNUMBER(INDEX(Scenarios!$B$37:$D$39,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(WACC-INDEX(Scenarios!$B$37:$D$39,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF"),IF(AND(NOT(ISNUMBER(WACC)),NOT(ISNUMBER(INDEX(Scenarios!$B$37:$D$39,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D39" s="5">
@@ -16282,7 +16282,7 @@
         <v>850</v>
       </c>
       <c r="C40" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(RONIC)),NOT(ISNUMBER(INDEX(Scenarios!$B$42:$D$44,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(RONIC-INDEX(Scenarios!$B$42:$D$44,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(RONIC),ISNUMBER(INDEX(Scenarios!$B$42:$D$44,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(RONIC-INDEX(Scenarios!$B$42:$D$44,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF"),IF(AND(NOT(ISNUMBER(RONIC)),NOT(ISNUMBER(INDEX(Scenarios!$B$42:$D$44,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D40" s="5">
@@ -16308,7 +16308,7 @@
         <v>852</v>
       </c>
       <c r="C41" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(TVShare)),NOT(ISNUMBER(INDEX(Scenarios!$B$47:$D$49,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(TVShare-INDEX(Scenarios!$B$47:$D$49,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(TVShare),ISNUMBER(INDEX(Scenarios!$B$47:$D$49,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(TVShare-INDEX(Scenarios!$B$47:$D$49,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF"),IF(AND(NOT(ISNUMBER(TVShare)),NOT(ISNUMBER(INDEX(Scenarios!$B$47:$D$49,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D41" s="5">
@@ -16334,7 +16334,7 @@
         <v>854</v>
       </c>
       <c r="C42" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(ImpliedMultiple)),NOT(ISNUMBER(INDEX(Scenarios!$B$52:$D$54,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(ImpliedMultiple-INDEX(Scenarios!$B$52:$D$54,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=0.0001,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(ImpliedMultiple),ISNUMBER(INDEX(Scenarios!$B$52:$D$54,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(ImpliedMultiple-INDEX(Scenarios!$B$52:$D$54,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=0.0001,"OK","DIFF"),IF(AND(NOT(ISNUMBER(ImpliedMultiple)),NOT(ISNUMBER(INDEX(Scenarios!$B$52:$D$54,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D42" s="5">
@@ -16360,7 +16360,7 @@
         <v>857</v>
       </c>
       <c r="C43" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(PerShareExit)),NOT(ISNUMBER(INDEX(Scenarios!$B$57:$D$59,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(PerShareExit-INDEX(Scenarios!$B$57:$D$59,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(PerShareExit),ISNUMBER(INDEX(Scenarios!$B$57:$D$59,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(PerShareExit-INDEX(Scenarios!$B$57:$D$59,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(PerShareExit)),NOT(ISNUMBER(INDEX(Scenarios!$B$57:$D$59,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D43" s="5">
@@ -16386,7 +16386,7 @@
         <v>860</v>
       </c>
       <c r="C44" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(EV_930)),NOT(ISNUMBER(INDEX(Scenarios!$B$62:$D$64,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(EV_930-INDEX(Scenarios!$B$62:$D$64,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=0.01,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(EV_930),ISNUMBER(INDEX(Scenarios!$B$62:$D$64,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(EV_930-INDEX(Scenarios!$B$62:$D$64,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=0.01,"OK","DIFF"),IF(AND(NOT(ISNUMBER(EV_930)),NOT(ISNUMBER(INDEX(Scenarios!$B$62:$D$64,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D44" s="5">
@@ -16412,7 +16412,7 @@
         <v>863</v>
       </c>
       <c r="C45" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(ImpliedG_Exit)),NOT(ISNUMBER(INDEX(Scenarios!$B$67:$D$69,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(ImpliedG_Exit-INDEX(Scenarios!$B$67:$D$69,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(ImpliedG_Exit),ISNUMBER(INDEX(Scenarios!$B$67:$D$69,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(ImpliedG_Exit-INDEX(Scenarios!$B$67:$D$69,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF"),IF(AND(NOT(ISNUMBER(ImpliedG_Exit)),NOT(ISNUMBER(INDEX(Scenarios!$B$67:$D$69,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D45" s="5">
@@ -16438,7 +16438,7 @@
         <v>865</v>
       </c>
       <c r="C46" s="6" t="str">
-        <f>IF(AND(NOT(ISNUMBER(TVShare_Exit)),NOT(ISNUMBER(INDEX(Scenarios!$B$72:$D$74,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/A",IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(TVShare_Exit-INDEX(Scenarios!$B$72:$D$74,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF")))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(TVShare_Exit),ISNUMBER(INDEX(Scenarios!$B$72:$D$74,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))),IF(ABS(TVShare_Exit-INDEX(Scenarios!$B$72:$D$74,ScenIdx,MATCH(SRP_Sel,SRP_List,0)))&lt;=1e-06,"OK","DIFF"),IF(AND(NOT(ISNUMBER(TVShare_Exit)),NOT(ISNUMBER(INDEX(Scenarios!$B$72:$D$74,ScenIdx,MATCH(SRP_Sel,SRP_List,0))))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D46" s="5">
@@ -16533,7 +16533,7 @@
         <v>875</v>
       </c>
       <c r="C50" s="6" t="str">
-        <f>IF(ABS(BetaU-WACC!$E$6)&lt;1E-9,"OK","DIFF")</f>
+        <f>IF(AND(ISNUMBER(BetaU),ISNUMBER(WACC!$E$6)),IF(ABS(BetaU-WACC!$E$6)&lt;=1E-9,"OK","DIFF"),IF(AND(NOT(ISNUMBER(BetaU)),NOT(ISNUMBER(WACC!$E$6))),"N/M","DIFF"))</f>
         <v>OK</v>
       </c>
       <c r="D50" s="5">
@@ -16660,7 +16660,7 @@
         <v>885</v>
       </c>
       <c r="C55" s="6" t="str">
-        <f>IF(MAX(ABS(Block_q1-Premium!$E$23),ABS(Block_q2-Premium!$E$24),ABS(Block_q3-Premium!$E$25))&lt;=1,"OK","DIFF")</f>
+        <f>IF(AND(ISNUMBER(Block_q1),ISNUMBER(Premium!$E$23),ISNUMBER(Block_q2),ISNUMBER(Premium!$E$24),ISNUMBER(Block_q3),ISNUMBER(Premium!$E$25)),IF(MAX(ABS(Block_q1-Premium!$E$23),ABS(Block_q2-Premium!$E$24),ABS(Block_q3-Premium!$E$25))&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(Block_q1)),NOT(ISNUMBER(Premium!$E$23)),NOT(ISNUMBER(Block_q2)),NOT(ISNUMBER(Premium!$E$24)),NOT(ISNUMBER(Block_q3)),NOT(ISNUMBER(Premium!$E$25))),"N/M","DIFF"))</f>
         <v>OK</v>
       </c>
       <c r="D55" s="5">
@@ -16731,7 +16731,7 @@
         <v>892</v>
       </c>
       <c r="C58" s="6" t="str">
-        <f>IF(AND(ScenSel="기본",SRP_Sel=SRP_1,RonicStart="normal",RfTenor=5),IF(ABS(Scenarios!$D$91-PerShare)&lt;=1,"OK","DIFF"),"N/A")</f>
+        <f>IF(AND(ScenSel="기본",SRP_Sel=SRP_1,RonicStart="normal",RfTenor=5),IF(AND(ISNUMBER(Scenarios!$D$91),ISNUMBER(PerShare)),IF(ABS(Scenarios!$D$91-PerShare)&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(Scenarios!$D$91)),NOT(ISNUMBER(PerShare))),"N/M","DIFF")),"N/A")</f>
         <v>OK</v>
       </c>
       <c r="D58" s="5">
@@ -16779,7 +16779,7 @@
         <v>896</v>
       </c>
       <c r="C60" s="6" t="str">
-        <f>IF(AND(ScenSel="기본",SRP_Sel=SRP_1,RonicStart="normal",RfTenor=5),IF(ABS(Scenarios!$D$100-PerShare)&lt;=1,"OK","DIFF"),"N/A")</f>
+        <f>IF(AND(ScenSel="기본",SRP_Sel=SRP_1,RonicStart="normal",RfTenor=5),IF(AND(ISNUMBER(Scenarios!$D$100),ISNUMBER(PerShare)),IF(ABS(Scenarios!$D$100-PerShare)&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(Scenarios!$D$100)),NOT(ISNUMBER(PerShare))),"N/M","DIFF")),"N/A")</f>
         <v>OK</v>
       </c>
       <c r="D60" s="5">
@@ -16827,7 +16827,7 @@
         <v>900</v>
       </c>
       <c r="C62" s="6" t="str">
-        <f>IF(AND(ScenSel="기본",SRP_Sel=SRP_1,RonicStart="normal",RfTenor=5),IF(ABS(Scenarios!$B$108-PerShare)&lt;=1,"OK","DIFF"),"N/A")</f>
+        <f>IF(AND(ScenSel="기본",SRP_Sel=SRP_1,RonicStart="normal",RfTenor=5),IF(AND(ISNUMBER(Scenarios!$B$108),ISNUMBER(PerShare)),IF(ABS(Scenarios!$B$108-PerShare)&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(Scenarios!$B$108)),NOT(ISNUMBER(PerShare))),"N/M","DIFF")),"N/A")</f>
         <v>OK</v>
       </c>
       <c r="D62" s="5">
@@ -16875,7 +16875,7 @@
         <v>904</v>
       </c>
       <c r="C64" s="6" t="str">
-        <f>IF(AND(ScenSel="기본",SRP_Sel=SRP_1,RonicStart="normal",RfTenor=5),IF(ABS(Scenarios!$B$121-PerShare)&lt;=1,"OK","DIFF"),"N/A")</f>
+        <f>IF(AND(ScenSel="기본",SRP_Sel=SRP_1,RonicStart="normal",RfTenor=5),IF(AND(ISNUMBER(Scenarios!$B$121),ISNUMBER(PerShare)),IF(ABS(Scenarios!$B$121-PerShare)&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(Scenarios!$B$121)),NOT(ISNUMBER(PerShare))),"N/M","DIFF")),"N/A")</f>
         <v>OK</v>
       </c>
       <c r="D64" s="5">
@@ -16921,7 +16921,7 @@
         <v>908</v>
       </c>
       <c r="C66" s="6" t="str">
-        <f>IF(ABS(Convergence!$B$13-Convergence!$B$8)&lt;=1,"OK","DIFF")</f>
+        <f>IF(AND(ISNUMBER(Convergence!$B$13),ISNUMBER(Convergence!$B$8)),IF(ABS(Convergence!$B$13-Convergence!$B$8)&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(Convergence!$B$13)),NOT(ISNUMBER(Convergence!$B$8))),"N/M","DIFF"))</f>
         <v>OK</v>
       </c>
       <c r="D66" s="5">
@@ -16990,7 +16990,7 @@
         <v>914</v>
       </c>
       <c r="C69" s="6" t="str">
-        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(ABS(Scenarios!$K$91-INDEX(ScenGridPS,MATCH("기본",ScenNames,0),1))&lt;=1,"OK","DIFF"))</f>
+        <f>IF(RfTenor&lt;&gt;5,"N/A",IF(AND(ISNUMBER(Scenarios!$K$91),ISNUMBER(INDEX(ScenGridPS,MATCH("기본",ScenNames,0),1))),IF(ABS(Scenarios!$K$91-INDEX(ScenGridPS,MATCH("기본",ScenNames,0),1))&lt;=1,"OK","DIFF"),IF(AND(NOT(ISNUMBER(Scenarios!$K$91)),NOT(ISNUMBER(INDEX(ScenGridPS,MATCH("기본",ScenNames,0),1)))),"N/M","DIFF")))</f>
         <v>OK</v>
       </c>
       <c r="D69" s="5">
@@ -17010,27 +17010,33 @@
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"N/M"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"ERR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"WARN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"DIFF"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:C69">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+      <formula>"N/M"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>"ERR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
       <formula>"WARN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
       <formula>"DIFF"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/examples/036200_general/036200_model_example.xlsx
+++ b/examples/036200_general/036200_model_example.xlsx
@@ -1287,12 +1287,12 @@
     <t>2025 H1</t>
   </si>
   <si>
+    <t>20250814003707</t>
+  </si>
+  <si>
     <t>20260814000905</t>
   </si>
   <si>
-    <t>20250814003707</t>
-  </si>
-  <si>
     <t>2026 H1</t>
   </si>
   <si>
@@ -3324,6 +3324,18 @@
     <t>4 ★</t>
   </si>
   <si>
+    <t>재투자 비율</t>
+  </si>
+  <si>
+    <t>CAPEX ÷ 매출(3년 평균)</t>
+  </si>
+  <si>
+    <t>마지막 명시 연도 재투자 = 수렴 규칙(A) CAPEX ÷ 매출 1.54%(명시 → 수렴 FCFF 2.71배, 기본 CAPEX ÷ 매출 3년 평균 5.59%)</t>
+  </si>
+  <si>
+    <t>5 ★</t>
+  </si>
+  <si>
     <t>시나리오 폭</t>
   </si>
   <si>
@@ -3333,9 +3345,6 @@
     <t>낙관(+2%p)</t>
   </si>
   <si>
-    <t>5 ★</t>
-  </si>
-  <si>
     <t>할인율</t>
   </si>
   <si>
@@ -3345,25 +3354,25 @@
     <t>SRP 2%</t>
   </si>
   <si>
-    <t>재투자 비율</t>
-  </si>
-  <si>
-    <t>CAPEX ÷ 매출(3년 평균)</t>
-  </si>
-  <si>
-    <t>CAPEX ÷ 매출 5년 평균 4.35%(FY2021~2025, 기본 3년 평균 5.59%)</t>
-  </si>
-  <si>
     <t>MRP</t>
   </si>
   <si>
     <t>MRP 7%(기본 8%, 한공회 가이던스 7~9%)</t>
   </si>
   <si>
+    <t>RONIC</t>
+  </si>
+  <si>
+    <t>영구 구간 RONIC(하한 WACC)</t>
+  </si>
+  <si>
+    <t>RONIC = 과거 3년 ROIC 7.18%(규칙 전 값, 기본 = WACC 11.90%)</t>
+  </si>
+  <si>
     <t>운전자본 회전일수(3년 평균)</t>
   </si>
   <si>
-    <t>회전일수 5년 평균 DSO 0·DIO 67·DPO 0일(FY2021~2025, 기본 DSO 0·DIO 83·DPO 0일)</t>
+    <t>회전일수 5년 평균 DSO 74·DIO 67·DPO 22일(FY2021~2025, 기본 DSO 78·DIO 83·DPO 24일)</t>
   </si>
   <si>
     <t>수렴 도달 연도</t>
@@ -3372,25 +3381,25 @@
     <t>도달 연도 2030(기본 2032)</t>
   </si>
   <si>
-    <t>RONIC</t>
-  </si>
-  <si>
-    <t>영구 구간 RONIC(하한 WACC)</t>
-  </si>
-  <si>
-    <t>RONIC = 과거 3년 ROIC 9.89%(규칙 전 값, 기본 = WACC 11.97%)</t>
+    <t>Rf 만기</t>
+  </si>
+  <si>
+    <t>Rf 국고채 10년</t>
   </si>
   <si>
     <t>목표 D/E(자기 평균)</t>
   </si>
   <si>
-    <t>피어 D/E 중앙값 0.102배(기본 자기 평균 0.012배)</t>
-  </si>
-  <si>
-    <t>Rf 만기</t>
-  </si>
-  <si>
-    <t>Rf 국고채 10년</t>
+    <t>피어 D/E 중앙값 0.102배(기본 자기 평균 0.028배)</t>
+  </si>
+  <si>
+    <t>Kd 근거</t>
+  </si>
+  <si>
+    <t>신용등급 자동 탐색 안 함</t>
+  </si>
+  <si>
+    <t>세전 Kd 10.51%(BBB- 3년, 기본 5.56%)</t>
   </si>
   <si>
     <t>D&amp;A ÷ 매출(3년 평균)</t>
@@ -3405,15 +3414,6 @@
     <t>g 3%</t>
   </si>
   <si>
-    <t>Kd 근거</t>
-  </si>
-  <si>
-    <t>신용등급 자동 탐색 안 함</t>
-  </si>
-  <si>
-    <t>세전 Kd 10.51%(BBB- 3년, 기본 11.65%)</t>
-  </si>
-  <si>
     <t>비지배지분 차감 방법</t>
   </si>
   <si>
@@ -3615,10 +3615,10 @@
     <t>v1</t>
   </si>
   <si>
-    <t>2026-10-24T02:01:25</t>
-  </si>
-  <si>
-    <t>그대로 유지한 판단 0건 · 남은 미처리 34건</t>
+    <t>2026-10-26T12:36:38</t>
+  </si>
+  <si>
+    <t>그대로 유지한 판단 0건 · 남은 미처리 33건</t>
   </si>
   <si>
     <t>자동 초안 대표값 판정(기록): 표시</t>
@@ -4313,10 +4313,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>4628.393636578313</c:v>
+                  <c:v>3982.276759282653</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5345.077547961856</c:v>
+                  <c:v>4691.380095525618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4401,10 +4401,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6035.580005626037</c:v>
+                  <c:v>5325.210821879023</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7002.664468500521</c:v>
+                  <c:v>6283.193634259378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4489,10 +4489,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7562.232416944719</c:v>
+                  <c:v>6786.310052270534</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8801.431083570636</c:v>
+                  <c:v>8014.795986412259</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4577,10 +4577,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>5260.596670699279</c:v>
+                  <c:v>5090.621453425907</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7286.707794228766</c:v>
+                  <c:v>7116.732576955395</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4753,10 +4753,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>10755.750497574374</c:v>
+                  <c:v>10585.775280301003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17067.37314657971</c:v>
+                  <c:v>16897.39792930634</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5073,22 +5073,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>5345.077547961856</c:v>
+                  <c:v>4691.380095525618</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7002.664468500521</c:v>
+                  <c:v>6283.193634259378</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8801.431083570636</c:v>
+                  <c:v>8014.795986412259</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6561.230037235493</c:v>
+                  <c:v>6391.2548199621215</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>6817.130015864909</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12826.06021530625</c:v>
+                  <c:v>12656.084998032879</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>12524.180489009468</c:v>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C17" s="5" t="str">
         <f>"시나리오: "&amp;ScenSel&amp;" / SRP: "&amp;TEXT(SRP_Sel,"0.0%")&amp;" / 주당 가치(Gordon): "&amp;TEXT(PerShare,"#,##0")&amp;"원"</f>
-        <v>시나리오: 기본 / SRP: 0.0% / 주당 가치(Gordon): 7,003원</v>
+        <v>시나리오: 기본 / SRP: 0.0% / 주당 가치(Gordon): 6,283원</v>
       </c>
     </row>
     <row r="18" spans="2:3">
@@ -6163,27 +6163,27 @@
       </c>
       <c r="B6" s="57">
         <f>Scen_Calc!$C$47</f>
-        <v>5345.077547961856</v>
+        <v>4691.380095525618</v>
       </c>
       <c r="C6" s="57">
         <f>Scen_Calc!$C$60</f>
-        <v>4955.207884882286</v>
+        <v>4305.660068987254</v>
       </c>
       <c r="D6" s="57">
         <f>Scen_Calc!$C$73</f>
-        <v>4628.393636578313</v>
+        <v>3982.276759282653</v>
       </c>
       <c r="F6" s="28">
         <f>B6/Close-1</f>
-        <v>-0.7327461226019072</v>
+        <v>-0.765430995223719</v>
       </c>
       <c r="G6" s="28">
         <f>C6/Close-1</f>
-        <v>-0.7522396057558858</v>
+        <v>-0.7847169965506373</v>
       </c>
       <c r="H6" s="28">
         <f>D6/Close-1</f>
-        <v>-0.7685803181710844</v>
+        <v>-0.8008861620358674</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6192,27 +6192,27 @@
       </c>
       <c r="B7" s="57">
         <f>Scen_Calc!$C$120</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="C7" s="57">
         <f>Scen_Calc!$C$133</f>
-        <v>6477.75406264789</v>
+        <v>5763.295620696146</v>
       </c>
       <c r="D7" s="57">
         <f>Scen_Calc!$C$146</f>
-        <v>6035.580005626037</v>
+        <v>5325.210821879023</v>
       </c>
       <c r="F7" s="28">
         <f>B7/Close-1</f>
-        <v>-0.6498667765749739</v>
+        <v>-0.6858403182870311</v>
       </c>
       <c r="G7" s="28">
         <f>C7/Close-1</f>
-        <v>-0.6761122968676054</v>
+        <v>-0.7118352189651926</v>
       </c>
       <c r="H7" s="28">
         <f>D7/Close-1</f>
-        <v>-0.6982209997186981</v>
+        <v>-0.7337394589060489</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6221,27 +6221,27 @@
       </c>
       <c r="B8" s="57">
         <f>Scen_Calc!$C$193</f>
-        <v>8801.431083570636</v>
+        <v>8014.795986412259</v>
       </c>
       <c r="C8" s="57">
         <f>Scen_Calc!$C$206</f>
-        <v>8129.7712869778525</v>
+        <v>7349.064915189951</v>
       </c>
       <c r="D8" s="57">
         <f>Scen_Calc!$C$219</f>
-        <v>7562.232416944719</v>
+        <v>6786.310052270534</v>
       </c>
       <c r="F8" s="28">
         <f>B8/Close-1</f>
-        <v>-0.5599284458214682</v>
+        <v>-0.599260200679387</v>
       </c>
       <c r="G8" s="28">
         <f>C8/Close-1</f>
-        <v>-0.5935114356511073</v>
+        <v>-0.6325467542405026</v>
       </c>
       <c r="H8" s="28">
         <f>D8/Close-1</f>
-        <v>-0.6218883791527641</v>
+        <v>-0.6606844973864734</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6272,15 +6272,15 @@
       </c>
       <c r="B12" s="45">
         <f>Scen_Calc!$C$38</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="C12" s="45">
         <f>Scen_Calc!$C$51</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
       <c r="D12" s="45">
         <f>Scen_Calc!$C$64</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6289,15 +6289,15 @@
       </c>
       <c r="B13" s="45">
         <f>Scen_Calc!$C$111</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="C13" s="45">
         <f>Scen_Calc!$C$124</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
       <c r="D13" s="45">
         <f>Scen_Calc!$C$137</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -6306,15 +6306,15 @@
       </c>
       <c r="B14" s="45">
         <f>Scen_Calc!$C$184</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="C14" s="45">
         <f>Scen_Calc!$C$197</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
       <c r="D14" s="45">
         <f>Scen_Calc!$C$210</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -6345,15 +6345,15 @@
       </c>
       <c r="B18" s="30">
         <f>Scen_Calc!$C$39</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="C18" s="30">
         <f>Scen_Calc!$C$52</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
       <c r="D18" s="30">
         <f>Scen_Calc!$C$65</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -6362,15 +6362,15 @@
       </c>
       <c r="B19" s="30">
         <f>Scen_Calc!$C$112</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="C19" s="30">
         <f>Scen_Calc!$C$125</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
       <c r="D19" s="30">
         <f>Scen_Calc!$C$138</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -6379,15 +6379,15 @@
       </c>
       <c r="B20" s="30">
         <f>Scen_Calc!$C$185</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="C20" s="30">
         <f>Scen_Calc!$C$198</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
       <c r="D20" s="30">
         <f>Scen_Calc!$C$211</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -6418,15 +6418,15 @@
       </c>
       <c r="B24" s="28">
         <f>Scen_Calc!$C$48</f>
-        <v>0.5157788615810551</v>
+        <v>0.6278406752329133</v>
       </c>
       <c r="C24" s="28">
         <f>Scen_Calc!$C$61</f>
-        <v>0.4869077412296116</v>
+        <v>0.6115051432139936</v>
       </c>
       <c r="D24" s="28">
         <f>Scen_Calc!$C$74</f>
-        <v>0.46048543156605665</v>
+        <v>0.5990913870064306</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6435,15 +6435,15 @@
       </c>
       <c r="B25" s="28">
         <f>Scen_Calc!$C$121</f>
-        <v>0.4285652185570535</v>
+        <v>0.4948615812826791</v>
       </c>
       <c r="C25" s="28">
         <f>Scen_Calc!$C$134</f>
-        <v>0.3960797606762963</v>
+        <v>0.466021939653644</v>
       </c>
       <c r="D25" s="28">
         <f>Scen_Calc!$C$147</f>
-        <v>0.36627591672062065</v>
+        <v>0.4397008128958683</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6452,15 +6452,15 @@
       </c>
       <c r="B26" s="28">
         <f>Scen_Calc!$C$194</f>
-        <v>0.38521043279975187</v>
+        <v>0.43337984771901245</v>
       </c>
       <c r="C26" s="28">
         <f>Scen_Calc!$C$207</f>
-        <v>0.3523389297454</v>
+        <v>0.4019693737952122</v>
       </c>
       <c r="D26" s="28">
         <f>Scen_Calc!$C$220</f>
-        <v>0.3223877413501897</v>
+        <v>0.373199514539146</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C28" s="57">
         <f>INDEX(ScenGridPS,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>697</v>
@@ -6499,13 +6499,13 @@
         <v>268</v>
       </c>
       <c r="B32" s="58">
-        <v>5345.077547961827</v>
+        <v>4691.380095525581</v>
       </c>
       <c r="C32" s="58">
-        <v>4955.207884882252</v>
+        <v>4305.660068987227</v>
       </c>
       <c r="D32" s="58">
-        <v>4628.393636578287</v>
+        <v>3982.276759282627</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -6513,13 +6513,13 @@
         <v>11</v>
       </c>
       <c r="B33" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="C33" s="58">
-        <v>6477.754062647854</v>
+        <v>5763.295620696118</v>
       </c>
       <c r="D33" s="58">
-        <v>6035.580005626011</v>
+        <v>5325.210821878997</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -6527,13 +6527,13 @@
         <v>269</v>
       </c>
       <c r="B34" s="58">
-        <v>8801.431083570602</v>
+        <v>8014.795986412213</v>
       </c>
       <c r="C34" s="58">
-        <v>8129.771286977811</v>
+        <v>7349.06491518992</v>
       </c>
       <c r="D34" s="58">
-        <v>7562.23241694469</v>
+        <v>6786.310052270504</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -6555,13 +6555,13 @@
         <v>268</v>
       </c>
       <c r="B37" s="60">
-        <v>0.1197417689130948</v>
+        <v>0.1189526032239875</v>
       </c>
       <c r="C37" s="60">
-        <v>0.1296263969080912</v>
+        <v>0.128683016883204</v>
       </c>
       <c r="D37" s="60">
-        <v>0.1395110249030875</v>
+        <v>0.1384134305424206</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -6569,13 +6569,13 @@
         <v>11</v>
       </c>
       <c r="B38" s="60">
-        <v>0.1197417689130948</v>
+        <v>0.1189526032239875</v>
       </c>
       <c r="C38" s="60">
-        <v>0.1296263969080912</v>
+        <v>0.128683016883204</v>
       </c>
       <c r="D38" s="60">
-        <v>0.1395110249030875</v>
+        <v>0.1384134305424206</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -6583,13 +6583,13 @@
         <v>269</v>
       </c>
       <c r="B39" s="60">
-        <v>0.1197417689130948</v>
+        <v>0.1189526032239875</v>
       </c>
       <c r="C39" s="60">
-        <v>0.1296263969080912</v>
+        <v>0.128683016883204</v>
       </c>
       <c r="D39" s="60">
-        <v>0.1395110249030875</v>
+        <v>0.1384134305424206</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -6611,13 +6611,13 @@
         <v>268</v>
       </c>
       <c r="B42" s="18">
-        <v>0.1197417689130948</v>
+        <v>0.1189526032239875</v>
       </c>
       <c r="C42" s="18">
-        <v>0.1296263969080912</v>
+        <v>0.128683016883204</v>
       </c>
       <c r="D42" s="18">
-        <v>0.1395110249030875</v>
+        <v>0.1384134305424206</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -6625,13 +6625,13 @@
         <v>11</v>
       </c>
       <c r="B43" s="18">
-        <v>0.1197417689130948</v>
+        <v>0.1189526032239875</v>
       </c>
       <c r="C43" s="18">
-        <v>0.1296263969080912</v>
+        <v>0.128683016883204</v>
       </c>
       <c r="D43" s="18">
-        <v>0.1395110249030875</v>
+        <v>0.1384134305424206</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -6639,13 +6639,13 @@
         <v>269</v>
       </c>
       <c r="B44" s="18">
-        <v>0.1197417689130948</v>
+        <v>0.1189526032239875</v>
       </c>
       <c r="C44" s="18">
-        <v>0.1296263969080912</v>
+        <v>0.128683016883204</v>
       </c>
       <c r="D44" s="18">
-        <v>0.1395110249030875</v>
+        <v>0.1384134305424206</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -6667,13 +6667,13 @@
         <v>268</v>
       </c>
       <c r="B47" s="41">
-        <v>0.515778861581058</v>
+        <v>0.6278406752329181</v>
       </c>
       <c r="C47" s="41">
-        <v>0.4869077412296143</v>
+        <v>0.6115051432139988</v>
       </c>
       <c r="D47" s="41">
-        <v>0.4604854315660598</v>
+        <v>0.5990913870064366</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -6681,13 +6681,13 @@
         <v>11</v>
       </c>
       <c r="B48" s="41">
-        <v>0.4285652185570548</v>
+        <v>0.4948615812826809</v>
       </c>
       <c r="C48" s="41">
-        <v>0.3960797606762975</v>
+        <v>0.4660219396536461</v>
       </c>
       <c r="D48" s="41">
-        <v>0.366275916720622</v>
+        <v>0.4397008128958704</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -6695,13 +6695,13 @@
         <v>269</v>
       </c>
       <c r="B49" s="41">
-        <v>0.3852104327997526</v>
+        <v>0.4333798477190131</v>
       </c>
       <c r="C49" s="41">
-        <v>0.3523389297454004</v>
+        <v>0.4019693737952131</v>
       </c>
       <c r="D49" s="41">
-        <v>0.3223877413501904</v>
+        <v>0.3731995145391472</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -6723,13 +6723,13 @@
         <v>268</v>
       </c>
       <c r="B52" s="61">
-        <v>6.255417762108222</v>
+        <v>6.294698652385345</v>
       </c>
       <c r="C52" s="61">
-        <v>5.803861174545329</v>
+        <v>5.84396774528927</v>
       </c>
       <c r="D52" s="61">
-        <v>5.416188686054102</v>
+        <v>5.456508321711205</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -6737,13 +6737,13 @@
         <v>11</v>
       </c>
       <c r="B53" s="61">
-        <v>6.355342936027975</v>
+        <v>6.39525130634591</v>
       </c>
       <c r="C53" s="61">
-        <v>5.896573101922195</v>
+        <v>5.937320342275958</v>
       </c>
       <c r="D53" s="61">
-        <v>5.502707863032897</v>
+        <v>5.543671571837253</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -6751,13 +6751,13 @@
         <v>269</v>
       </c>
       <c r="B54" s="61">
-        <v>6.424901652403879</v>
+        <v>6.465246816619469</v>
       </c>
       <c r="C54" s="61">
-        <v>5.961110619427541</v>
+        <v>6.002303835043912</v>
       </c>
       <c r="D54" s="61">
-        <v>5.562934557232876</v>
+        <v>5.604346610529593</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -6779,13 +6779,13 @@
         <v>268</v>
       </c>
       <c r="B57" s="58">
-        <v>5636.20296160053</v>
+        <v>4975.855179336544</v>
       </c>
       <c r="C57" s="58">
-        <v>5308.340853127579</v>
+        <v>4654.369891934643</v>
       </c>
       <c r="D57" s="58">
-        <v>5013.282344534317</v>
+        <v>4364.792734527766</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -6793,13 +6793,13 @@
         <v>11</v>
       </c>
       <c r="B58" s="58">
-        <v>7344.433524163182</v>
+        <v>6615.940270514668</v>
       </c>
       <c r="C58" s="58">
-        <v>6904.517789101456</v>
+        <v>6183.916403193751</v>
       </c>
       <c r="D58" s="58">
-        <v>6507.448374554066</v>
+        <v>5793.595451512269</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -6807,13 +6807,13 @@
         <v>269</v>
       </c>
       <c r="B59" s="58">
-        <v>9197.747864279476</v>
+        <v>8399.50872717948</v>
       </c>
       <c r="C59" s="58">
-        <v>8636.109657428329</v>
+        <v>7847.387109038671</v>
       </c>
       <c r="D59" s="58">
-        <v>8128.225106768455</v>
+        <v>7347.607026141207</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -6835,13 +6835,13 @@
         <v>268</v>
       </c>
       <c r="B62" s="62">
-        <v>86251.03617995512</v>
+        <v>72021.83727312555</v>
       </c>
       <c r="C62" s="62">
-        <v>74782.60950771421</v>
+        <v>60675.47652931191</v>
       </c>
       <c r="D62" s="62">
-        <v>65169.02425844963</v>
+        <v>51162.815951726</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -6849,13 +6849,13 @@
         <v>11</v>
       </c>
       <c r="B63" s="62">
-        <v>135010.7008866273</v>
+        <v>118846.7086946353</v>
       </c>
       <c r="C63" s="62">
-        <v>119569.9085678146</v>
+        <v>103553.3611730649</v>
       </c>
       <c r="D63" s="62">
-        <v>106562.8930712351</v>
+        <v>90666.63551256614</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -6863,13 +6863,13 @@
         <v>269</v>
       </c>
       <c r="B64" s="62">
-        <v>187923.3149701603</v>
+        <v>169783.6152604889</v>
       </c>
       <c r="C64" s="62">
-        <v>168165.7347956175</v>
+        <v>150200.4347856672</v>
       </c>
       <c r="D64" s="62">
-        <v>151470.9813151631</v>
+        <v>133646.4079120219</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -6891,13 +6891,13 @@
         <v>268</v>
       </c>
       <c r="B67" s="18">
-        <v>0.03488081915043958</v>
+        <v>0.03428332525678119</v>
       </c>
       <c r="C67" s="18">
-        <v>0.0424550680369292</v>
+        <v>0.04172553208545384</v>
       </c>
       <c r="D67" s="18">
-        <v>0.05017102390531825</v>
+        <v>0.04930823423281941</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -6905,13 +6905,13 @@
         <v>11</v>
       </c>
       <c r="B68" s="18">
-        <v>0.03362948443738434</v>
+        <v>0.03303465533567442</v>
       </c>
       <c r="C68" s="18">
-        <v>0.0411716156912976</v>
+        <v>0.04044505231300387</v>
       </c>
       <c r="D68" s="18">
-        <v>0.04885742592257426</v>
+        <v>0.04799790018182545</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -6919,13 +6919,13 @@
         <v>269</v>
       </c>
       <c r="B69" s="18">
-        <v>0.03276020522117066</v>
+        <v>0.03216722453747659</v>
       </c>
       <c r="C69" s="18">
-        <v>0.04028005826370763</v>
+        <v>0.03955555679483187</v>
       </c>
       <c r="D69" s="18">
-        <v>0.04794495809574432</v>
+        <v>0.04708769637250237</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -6947,13 +6947,13 @@
         <v>268</v>
       </c>
       <c r="B72" s="41">
-        <v>0.559514164998821</v>
+        <v>0.6665803226940783</v>
       </c>
       <c r="C72" s="41">
-        <v>0.5494868685897819</v>
+        <v>0.6676855202850382</v>
       </c>
       <c r="D72" s="41">
-        <v>0.5403423962997705</v>
+        <v>0.6713668533419589</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -6961,13 +6961,13 @@
         <v>11</v>
       </c>
       <c r="B73" s="41">
-        <v>0.4681678066609171</v>
+        <v>0.5332986263853363</v>
       </c>
       <c r="C73" s="41">
-        <v>0.4534611476447148</v>
+        <v>0.5230142580088504</v>
       </c>
       <c r="D73" s="41">
-        <v>0.4393094778711684</v>
+        <v>0.513613803621346</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -6975,13 +6975,13 @@
         <v>269</v>
       </c>
       <c r="B74" s="41">
-        <v>0.4211219129802548</v>
+        <v>0.4687872207110918</v>
       </c>
       <c r="C74" s="41">
-        <v>0.405035102376589</v>
+        <v>0.4551440815927248</v>
       </c>
       <c r="D74" s="41">
-        <v>0.3894929826777485</v>
+        <v>0.4421217336760254</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -6995,15 +6995,15 @@
       </c>
       <c r="B77" s="54">
         <f>B6-B32</f>
-        <v>2.9103830456733704e-11</v>
+        <v>3.728928277269006e-11</v>
       </c>
       <c r="C77" s="54">
         <f>C6-C32</f>
-        <v>3.3651303965598345e-11</v>
+        <v>2.7284841053187847e-11</v>
       </c>
       <c r="D77" s="54">
         <f>D6-D32</f>
-        <v>2.546585164964199e-11</v>
+        <v>2.5920599000528455e-11</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -7012,11 +7012,11 @@
       </c>
       <c r="B78" s="54">
         <f>B7-B33</f>
-        <v>2.9103830456733704e-11</v>
+        <v>4.092726157978177e-11</v>
       </c>
       <c r="C78" s="54">
         <f>C7-C33</f>
-        <v>3.637978807091713e-11</v>
+        <v>2.8194335754960775e-11</v>
       </c>
       <c r="D78" s="54">
         <f>D7-D33</f>
@@ -7029,15 +7029,15 @@
       </c>
       <c r="B79" s="54">
         <f>B8-B34</f>
-        <v>3.456079866737127e-11</v>
+        <v>4.547473508864641e-11</v>
       </c>
       <c r="C79" s="54">
         <f>C8-C34</f>
-        <v>4.18367562815547e-11</v>
+        <v>3.092281986027956e-11</v>
       </c>
       <c r="D79" s="54">
         <f>D8-D34</f>
-        <v>2.9103830456733704e-11</v>
+        <v>3.001332515850663e-11</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -7103,45 +7103,45 @@
     <row r="88" spans="1:20">
       <c r="A88" s="57">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="B88" s="30">
         <f>WaccCalc+B87</f>
-        <v>0.09974176891309476</v>
+        <v>0.09895260322398748</v>
       </c>
       <c r="C88" s="30">
         <f>WaccCalc+C87</f>
-        <v>0.10974176891309477</v>
+        <v>0.10895260322398749</v>
       </c>
       <c r="D88" s="30">
         <f>WaccCalc+D87</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="E88" s="30">
         <f>WaccCalc+E87</f>
-        <v>0.12974176891309477</v>
+        <v>0.1289526032239875</v>
       </c>
       <c r="F88" s="30">
         <f>WaccCalc+F87</f>
-        <v>0.13974176891309475</v>
+        <v>0.13895260322398748</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>718</v>
       </c>
       <c r="I88" s="18">
-        <v>0.09974176891309479</v>
+        <v>0.0989526032239875</v>
       </c>
       <c r="J88" s="18">
-        <v>0.1097417689130948</v>
+        <v>0.1089526032239875</v>
       </c>
       <c r="K88" s="18">
-        <v>0.1197417689130948</v>
+        <v>0.1189526032239875</v>
       </c>
       <c r="L88" s="18">
-        <v>0.1297417689130948</v>
+        <v>0.1289526032239875</v>
       </c>
       <c r="M88" s="18">
-        <v>0.1397417689130948</v>
+        <v>0.1389526032239875</v>
       </c>
       <c r="O88" s="10" t="s">
         <v>719</v>
@@ -7153,37 +7153,37 @@
       </c>
       <c r="B89" s="54">
         <f t="dataTable" ref="B89:F93" dt2D="1" dtr="1" r1="B82" r2="E82"/>
-        <v>8383.201401628066</v>
+        <v>7675.284930077235</v>
       </c>
       <c r="C89" s="54">
-        <v>7608.909015412924</v>
+        <v>6893.569261226782</v>
       </c>
       <c r="D89" s="54">
-        <v>6975.068652416789</v>
+        <v>6255.245279580827</v>
       </c>
       <c r="E89" s="54">
-        <v>6448.560351548737</v>
+        <v>5726.263870205865</v>
       </c>
       <c r="F89" s="54">
-        <v>6005.787181887054</v>
+        <v>5282.42334739239</v>
       </c>
       <c r="H89" s="41">
         <v>0.01</v>
       </c>
       <c r="I89" s="58">
-        <v>8383.201401628066</v>
+        <v>7675.284930077235</v>
       </c>
       <c r="J89" s="58">
-        <v>7608.909015412924</v>
+        <v>6893.569261226782</v>
       </c>
       <c r="K89" s="58">
-        <v>6975.068652416789</v>
+        <v>6255.245279580827</v>
       </c>
       <c r="L89" s="58">
-        <v>6448.560351548737</v>
+        <v>5726.263870205865</v>
       </c>
       <c r="M89" s="58">
-        <v>6005.787181887054</v>
+        <v>5282.42334739239</v>
       </c>
       <c r="P89" s="54">
         <f>IF(ISNUMBER(I89),B89-I89,"")</f>
@@ -7211,37 +7211,37 @@
         <v>0.015</v>
       </c>
       <c r="B90" s="54">
-        <v>8402.454521814343</v>
+        <v>7694.813195147331</v>
       </c>
       <c r="C90" s="54">
-        <v>7625.085875370412</v>
+        <v>6909.963944976384</v>
       </c>
       <c r="D90" s="54">
-        <v>6988.789684584392</v>
+        <v>6269.141466176798</v>
       </c>
       <c r="E90" s="54">
-        <v>6460.292730724537</v>
+        <v>5738.138947781114</v>
       </c>
       <c r="F90" s="54">
-        <v>6015.88969659816</v>
+        <v>5292.643422228994</v>
       </c>
       <c r="H90" s="41">
         <v>0.015</v>
       </c>
       <c r="I90" s="58">
-        <v>8402.454521814343</v>
+        <v>7694.813195147331</v>
       </c>
       <c r="J90" s="58">
-        <v>7625.085875370412</v>
+        <v>6909.963944976384</v>
       </c>
       <c r="K90" s="58">
-        <v>6988.789684584392</v>
+        <v>6269.141466176798</v>
       </c>
       <c r="L90" s="58">
-        <v>6460.292730724537</v>
+        <v>5738.138947781114</v>
       </c>
       <c r="M90" s="58">
-        <v>6015.88969659816</v>
+        <v>5292.643422228994</v>
       </c>
       <c r="P90" s="54">
         <f>IF(ISNUMBER(I90),B90-I90,"")</f>
@@ -7269,37 +7269,37 @@
         <v>0.02</v>
       </c>
       <c r="B91" s="54">
-        <v>8421.932962546251</v>
+        <v>7714.570392980081</v>
       </c>
       <c r="C91" s="54">
-        <v>7641.447985718667</v>
+        <v>6926.546695653697</v>
       </c>
       <c r="D91" s="54">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="E91" s="54">
-        <v>6472.153755063648</v>
+        <v>5750.144458337755</v>
       </c>
       <c r="F91" s="54">
-        <v>6026.10060878837</v>
+        <v>5302.973343666243</v>
       </c>
       <c r="H91" s="41">
         <v>0.02</v>
       </c>
       <c r="I91" s="58">
-        <v>8421.932962546251</v>
+        <v>7714.570392980081</v>
       </c>
       <c r="J91" s="58">
-        <v>7641.447985718667</v>
+        <v>6926.546695653697</v>
       </c>
       <c r="K91" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="L91" s="58">
-        <v>6472.153755063648</v>
+        <v>5750.144458337755</v>
       </c>
       <c r="M91" s="58">
-        <v>6026.10060878837</v>
+        <v>5302.973343666243</v>
       </c>
       <c r="P91" s="54">
         <f>IF(ISNUMBER(I91),B91-I91,"")</f>
@@ -7327,37 +7327,37 @@
         <v>0.025</v>
       </c>
       <c r="B92" s="54">
-        <v>8441.639680524946</v>
+        <v>7734.559529423796</v>
       </c>
       <c r="C92" s="54">
-        <v>7657.997759451951</v>
+        <v>6943.319964372949</v>
       </c>
       <c r="D92" s="54">
-        <v>7016.694992039728</v>
+        <v>6297.403801718126</v>
       </c>
       <c r="E92" s="54">
-        <v>6484.145075447009</v>
+        <v>5762.282076689805</v>
       </c>
       <c r="F92" s="54">
-        <v>6036.421299085939</v>
+        <v>5313.414511621777</v>
       </c>
       <c r="H92" s="41">
         <v>0.025</v>
       </c>
       <c r="I92" s="58">
-        <v>8441.639680524946</v>
+        <v>7734.559529423796</v>
       </c>
       <c r="J92" s="58">
-        <v>7657.997759451951</v>
+        <v>6943.319964372949</v>
       </c>
       <c r="K92" s="58">
-        <v>7016.694992039728</v>
+        <v>6297.403801718126</v>
       </c>
       <c r="L92" s="58">
-        <v>6484.145075447009</v>
+        <v>5762.282076689805</v>
       </c>
       <c r="M92" s="58">
-        <v>6036.421299085939</v>
+        <v>5313.414511621777</v>
       </c>
       <c r="P92" s="54">
         <f>IF(ISNUMBER(I92),B92-I92,"")</f>
@@ -7385,37 +7385,37 @@
         <v>0.03</v>
       </c>
       <c r="B93" s="54">
-        <v>8461.577665924317</v>
+        <v>7754.783644365514</v>
       </c>
       <c r="C93" s="54">
-        <v>7674.737636784133</v>
+        <v>6960.286229905857</v>
       </c>
       <c r="D93" s="54">
-        <v>7030.883265420206</v>
+        <v>6311.77400913013</v>
       </c>
       <c r="E93" s="54">
-        <v>6496.268361244288</v>
+        <v>5774.553496413406</v>
       </c>
       <c r="F93" s="54">
-        <v>6046.853163525179</v>
+        <v>5323.968341639022</v>
       </c>
       <c r="H93" s="41">
         <v>0.03</v>
       </c>
       <c r="I93" s="58">
-        <v>8461.577665924317</v>
+        <v>7754.783644365514</v>
       </c>
       <c r="J93" s="58">
-        <v>7674.737636784133</v>
+        <v>6960.286229905857</v>
       </c>
       <c r="K93" s="58">
-        <v>7030.883265420206</v>
+        <v>6311.77400913013</v>
       </c>
       <c r="L93" s="58">
-        <v>6496.268361244288</v>
+        <v>5774.553496413406</v>
       </c>
       <c r="M93" s="58">
-        <v>6046.853163525179</v>
+        <v>5323.968341639022</v>
       </c>
       <c r="P93" s="54">
         <f>IF(ISNUMBER(I93),B93-I93,"")</f>
@@ -7446,7 +7446,7 @@
     <row r="97" spans="1:20">
       <c r="A97" s="57">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="B97" s="12">
         <v>-0.04</v>
@@ -7491,37 +7491,37 @@
       </c>
       <c r="B98" s="54">
         <f t="dataTable" ref="B98:F102" dt2D="1" dtr="1" r1="B83" r2="E83"/>
-        <v>3822.025091413425</v>
+        <v>3232.695727619735</v>
       </c>
       <c r="C98" s="54">
-        <v>5295.79715927793</v>
+        <v>4715.741718028938</v>
       </c>
       <c r="D98" s="54">
-        <v>6762.912347118139</v>
+        <v>6192.113851034607</v>
       </c>
       <c r="E98" s="54">
-        <v>8222.847676067229</v>
+        <v>7661.29793397807</v>
       </c>
       <c r="F98" s="54">
-        <v>9680.318134448777</v>
+        <v>9128.016318228707</v>
       </c>
       <c r="H98" s="18">
         <v>-0.04</v>
       </c>
       <c r="I98" s="58">
-        <v>3822.025091413425</v>
+        <v>3232.695727619735</v>
       </c>
       <c r="J98" s="58">
-        <v>5295.79715927793</v>
+        <v>4715.741718028938</v>
       </c>
       <c r="K98" s="58">
-        <v>6762.912347118139</v>
+        <v>6192.113851034607</v>
       </c>
       <c r="L98" s="58">
-        <v>8222.847676067229</v>
+        <v>7661.29793397807</v>
       </c>
       <c r="M98" s="58">
-        <v>9680.318134448777</v>
+        <v>9128.016318228707</v>
       </c>
       <c r="P98" s="54">
         <f>IF(ISNUMBER(I98),B98-I98,"")</f>
@@ -7549,37 +7549,37 @@
         <v>-0.02</v>
       </c>
       <c r="B99" s="54">
-        <v>3802.496409454239</v>
+        <v>3139.070482028321</v>
       </c>
       <c r="C99" s="54">
-        <v>5345.077547961827</v>
+        <v>4691.380095525581</v>
       </c>
       <c r="D99" s="54">
-        <v>6880.632518573726</v>
+        <v>6236.647260493442</v>
       </c>
       <c r="E99" s="54">
-        <v>8409.274664427936</v>
+        <v>7774.994523752053</v>
       </c>
       <c r="F99" s="54">
-        <v>9935.739985853405</v>
+        <v>9311.164356378949</v>
       </c>
       <c r="H99" s="18">
         <v>-0.02</v>
       </c>
       <c r="I99" s="58">
-        <v>3802.496409454239</v>
+        <v>3139.070482028321</v>
       </c>
       <c r="J99" s="58">
-        <v>5345.077547961827</v>
+        <v>4691.380095525581</v>
       </c>
       <c r="K99" s="58">
-        <v>6880.632518573726</v>
+        <v>6236.647260493442</v>
       </c>
       <c r="L99" s="58">
-        <v>8409.274664427936</v>
+        <v>7774.994523752053</v>
       </c>
       <c r="M99" s="58">
-        <v>9935.739985853405</v>
+        <v>9311.164356378949</v>
       </c>
       <c r="P99" s="54">
         <f>IF(ISNUMBER(I99),B99-I99,"")</f>
@@ -7607,37 +7607,37 @@
         <v>0</v>
       </c>
       <c r="B100" s="54">
-        <v>3782.885351360114</v>
+        <v>3043.032525877043</v>
       </c>
       <c r="C100" s="54">
-        <v>5396.541070699867</v>
+        <v>4666.887278405403</v>
       </c>
       <c r="D100" s="54">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="E100" s="54">
-        <v>8602.059065382919</v>
+        <v>7892.765266830422</v>
       </c>
       <c r="F100" s="54">
-        <v>10199.76730272153</v>
+        <v>9500.650159251662</v>
       </c>
       <c r="H100" s="18">
         <v>0</v>
       </c>
       <c r="I100" s="58">
-        <v>3782.885351360114</v>
+        <v>3043.032525877043</v>
       </c>
       <c r="J100" s="58">
-        <v>5396.541070699867</v>
+        <v>4666.887278405403</v>
       </c>
       <c r="K100" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="L100" s="58">
-        <v>8602.059065382919</v>
+        <v>7892.765266830422</v>
       </c>
       <c r="M100" s="58">
-        <v>10199.76730272153</v>
+        <v>9500.650159251662</v>
       </c>
       <c r="P100" s="54">
         <f>IF(ISNUMBER(I100),B100-I100,"")</f>
@@ -7665,37 +7665,37 @@
         <v>0.02</v>
       </c>
       <c r="B101" s="54">
-        <v>3763.325152353584</v>
+        <v>2944.670254543868</v>
       </c>
       <c r="C101" s="54">
-        <v>5450.233100552699</v>
+        <v>4642.263605689768</v>
       </c>
       <c r="D101" s="54">
-        <v>7129.101072679445</v>
+        <v>6331.801145806958</v>
       </c>
       <c r="E101" s="54">
-        <v>8801.431083570602</v>
+        <v>8014.795986412213</v>
       </c>
       <c r="F101" s="54">
-        <v>10472.57734180449</v>
+        <v>9696.60692302578</v>
       </c>
       <c r="H101" s="18">
         <v>0.02</v>
       </c>
       <c r="I101" s="58">
-        <v>3763.325152353584</v>
+        <v>2944.670254543868</v>
       </c>
       <c r="J101" s="58">
-        <v>5450.233100552699</v>
+        <v>4642.263605689768</v>
       </c>
       <c r="K101" s="58">
-        <v>7129.101072679445</v>
+        <v>6331.801145806958</v>
       </c>
       <c r="L101" s="58">
-        <v>8801.431083570602</v>
+        <v>8014.795986412213</v>
       </c>
       <c r="M101" s="58">
-        <v>10472.57734180449</v>
+        <v>9696.60692302578</v>
       </c>
       <c r="P101" s="54">
         <f>IF(ISNUMBER(I101),B101-I101,"")</f>
@@ -7723,37 +7723,37 @@
         <v>0.04</v>
       </c>
       <c r="B102" s="54">
-        <v>3743.699020141189</v>
+        <v>2843.820710220757</v>
       </c>
       <c r="C102" s="54">
-        <v>5505.697283481368</v>
+        <v>4617.006317723994</v>
       </c>
       <c r="D102" s="54">
-        <v>7259.882203192313</v>
+        <v>6382.364491054584</v>
       </c>
       <c r="E102" s="54">
-        <v>9007.52713769844</v>
+        <v>8141.178330463527</v>
       </c>
       <c r="F102" s="54">
-        <v>10754.34893596853</v>
+        <v>9899.169033636428</v>
       </c>
       <c r="H102" s="18">
         <v>0.04</v>
       </c>
       <c r="I102" s="58">
-        <v>3743.699020141189</v>
+        <v>2843.820710220757</v>
       </c>
       <c r="J102" s="58">
-        <v>5505.697283481368</v>
+        <v>4617.006317723994</v>
       </c>
       <c r="K102" s="58">
-        <v>7259.882203192313</v>
+        <v>6382.364491054584</v>
       </c>
       <c r="L102" s="58">
-        <v>9007.52713769844</v>
+        <v>8141.178330463527</v>
       </c>
       <c r="M102" s="58">
-        <v>10754.34893596853</v>
+        <v>9899.169033636428</v>
       </c>
       <c r="P102" s="54">
         <f>IF(ISNUMBER(I102),B102-I102,"")</f>
@@ -7784,7 +7784,7 @@
     <row r="106" spans="1:20">
       <c r="A106" s="57">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="B106" s="12">
         <v>0</v>
@@ -7817,25 +7817,25 @@
       </c>
       <c r="B107" s="54">
         <f t="dataTable" ref="B107:D109" dt2D="1" dtr="1" r1="B84" r2="E84"/>
-        <v>7616.476211986733</v>
+        <v>6899.060007157484</v>
       </c>
       <c r="C107" s="54">
-        <v>6988.712209031949</v>
+        <v>6276.219080294962</v>
       </c>
       <c r="D107" s="54">
-        <v>6466.063995734726</v>
+        <v>5757.449818299216</v>
       </c>
       <c r="F107" s="18">
         <v>0.07000000000000001</v>
       </c>
       <c r="G107" s="58">
-        <v>7616.476211986733</v>
+        <v>6899.060007157484</v>
       </c>
       <c r="H107" s="58">
-        <v>6988.712209031949</v>
+        <v>6276.219080294962</v>
       </c>
       <c r="I107" s="58">
-        <v>6466.063995734726</v>
+        <v>5757.449818299216</v>
       </c>
       <c r="L107" s="54">
         <f>IF(ISNUMBER(G107),B107-G107,"")</f>
@@ -7855,25 +7855,25 @@
         <v>0.08</v>
       </c>
       <c r="B108" s="54">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="C108" s="54">
-        <v>6477.754062647854</v>
+        <v>5763.295620696118</v>
       </c>
       <c r="D108" s="54">
-        <v>6035.580005626011</v>
+        <v>5325.210821878997</v>
       </c>
       <c r="F108" s="18">
         <v>0.08</v>
       </c>
       <c r="G108" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="H108" s="58">
-        <v>6477.754062647854</v>
+        <v>5763.295620696118</v>
       </c>
       <c r="I108" s="58">
-        <v>6035.580005626011</v>
+        <v>5325.210821878997</v>
       </c>
       <c r="L108" s="54">
         <f>IF(ISNUMBER(G108),B108-G108,"")</f>
@@ -7893,25 +7893,25 @@
         <v>0.09</v>
       </c>
       <c r="B109" s="54">
-        <v>6489.493051617442</v>
+        <v>5769.15372540618</v>
       </c>
       <c r="C109" s="54">
-        <v>6045.522529868341</v>
+        <v>5330.173624887009</v>
       </c>
       <c r="D109" s="54">
-        <v>5667.742287548721</v>
+        <v>4956.570429776669</v>
       </c>
       <c r="F109" s="18">
         <v>0.09</v>
       </c>
       <c r="G109" s="58">
-        <v>6489.493051617442</v>
+        <v>5769.15372540618</v>
       </c>
       <c r="H109" s="58">
-        <v>6045.522529868341</v>
+        <v>5330.173624887009</v>
       </c>
       <c r="I109" s="58">
-        <v>5667.742287548721</v>
+        <v>4956.570429776669</v>
       </c>
       <c r="L109" s="54">
         <f>IF(ISNUMBER(G109),B109-G109,"")</f>
@@ -7949,7 +7949,7 @@
         <v>726</v>
       </c>
       <c r="B114" s="18">
-        <v>0.05321349372182026</v>
+        <v>0.04930984234746559</v>
       </c>
     </row>
     <row r="115" spans="1:17">
@@ -7979,7 +7979,7 @@
     <row r="120" spans="1:17">
       <c r="A120" s="57">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="B120" s="30">
         <f>SRP_1</f>
@@ -8023,31 +8023,31 @@
       </c>
       <c r="B121" s="54">
         <f t="dataTable" ref="B121:E122" dt2D="1" dtr="1" r1="B84" r2="B118"/>
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="C121" s="54">
-        <v>6477.754062647854</v>
+        <v>5763.295620696118</v>
       </c>
       <c r="D121" s="54">
-        <v>6035.580005626011</v>
+        <v>5325.210821878997</v>
       </c>
       <c r="E121" s="54">
-        <v>5330.068726047874</v>
+        <v>4626.222900837293</v>
       </c>
       <c r="G121" s="60">
         <v>0.04203</v>
       </c>
       <c r="H121" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="I121" s="58">
-        <v>6477.754062647854</v>
+        <v>5763.295620696118</v>
       </c>
       <c r="J121" s="58">
-        <v>6035.580005626011</v>
+        <v>5325.210821878997</v>
       </c>
       <c r="K121" s="58">
-        <v>5330.068726047874</v>
+        <v>4626.222900837293</v>
       </c>
       <c r="N121" s="54">
         <f>IF(ISNUMBER(H121),B121-H121,"")</f>
@@ -8072,31 +8072,31 @@
         <v>0.04407</v>
       </c>
       <c r="B122" s="54">
-        <v>6887.855686951773</v>
+        <v>6169.501211431947</v>
       </c>
       <c r="C122" s="54">
-        <v>6381.458633369221</v>
+        <v>5667.898054295025</v>
       </c>
       <c r="D122" s="54">
-        <v>5953.92680774794</v>
+        <v>5244.306653386163</v>
       </c>
       <c r="E122" s="54">
-        <v>5269.924492983359</v>
+        <v>4566.649464403594</v>
       </c>
       <c r="G122" s="60">
         <v>0.04407</v>
       </c>
       <c r="H122" s="58">
-        <v>6887.855686951773</v>
+        <v>6169.501211431947</v>
       </c>
       <c r="I122" s="58">
-        <v>6381.458633369221</v>
+        <v>5667.898054295025</v>
       </c>
       <c r="J122" s="58">
-        <v>5953.92680774794</v>
+        <v>5244.306653386163</v>
       </c>
       <c r="K122" s="58">
-        <v>5269.924492983359</v>
+        <v>4566.649464403594</v>
       </c>
       <c r="N122" s="54">
         <f>IF(ISNUMBER(H122),B122-H122,"")</f>
@@ -8139,13 +8139,13 @@
         <v>268</v>
       </c>
       <c r="B126" s="58">
-        <v>5259.649884837849</v>
+        <v>4606.871835156038</v>
       </c>
       <c r="C126" s="58">
-        <v>4883.898181301841</v>
+        <v>4235.099937744161</v>
       </c>
       <c r="D126" s="58">
-        <v>4568.231822927995</v>
+        <v>3922.74828538521</v>
       </c>
     </row>
     <row r="127" spans="1:17">
@@ -8153,13 +8153,13 @@
         <v>11</v>
       </c>
       <c r="B127" s="58">
-        <v>6887.855686951773</v>
+        <v>6169.501211431947</v>
       </c>
       <c r="C127" s="58">
-        <v>6381.458633369221</v>
+        <v>5667.898054295025</v>
       </c>
       <c r="D127" s="58">
-        <v>5953.92680774794</v>
+        <v>5244.306653386163</v>
       </c>
     </row>
     <row r="128" spans="1:17">
@@ -8167,13 +8167,13 @@
         <v>269</v>
       </c>
       <c r="B128" s="58">
-        <v>8654.694003942546</v>
+        <v>7869.384918780078</v>
       </c>
       <c r="C128" s="58">
-        <v>8006.323370297026</v>
+        <v>7226.671751369666</v>
       </c>
       <c r="D128" s="58">
-        <v>7457.223635219655</v>
+        <v>6682.171874911774</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -8195,13 +8195,13 @@
         <v>268</v>
       </c>
       <c r="B131" s="60">
-        <v>0.121758233024074</v>
+        <v>0.1209376076104677</v>
       </c>
       <c r="C131" s="60">
-        <v>0.1316428610190704</v>
+        <v>0.1306680212696842</v>
       </c>
       <c r="D131" s="60">
-        <v>0.1415274890140668</v>
+        <v>0.1403984349289007</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -8209,13 +8209,13 @@
         <v>11</v>
       </c>
       <c r="B132" s="60">
-        <v>0.121758233024074</v>
+        <v>0.1209376076104677</v>
       </c>
       <c r="C132" s="60">
-        <v>0.1316428610190704</v>
+        <v>0.1306680212696842</v>
       </c>
       <c r="D132" s="60">
-        <v>0.1415274890140668</v>
+        <v>0.1403984349289007</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -8223,13 +8223,13 @@
         <v>269</v>
       </c>
       <c r="B133" s="60">
-        <v>0.121758233024074</v>
+        <v>0.1209376076104677</v>
       </c>
       <c r="C133" s="60">
-        <v>0.1316428610190704</v>
+        <v>0.1306680212696842</v>
       </c>
       <c r="D133" s="60">
-        <v>0.1415274890140668</v>
+        <v>0.1403984349289007</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -9265,67 +9265,67 @@
       </c>
       <c r="C19" s="27">
         <f>NWC_Open</f>
-        <v>59585.00276</v>
+        <v>95121.90486000001</v>
       </c>
       <c r="D19" s="27">
         <f>IF(D11=1,D13*DSO/DaysYr+D13*COGSR*DIO/DaysYr-D13*COGSR*DPO/DaysYr,C19)</f>
-        <v>56734.01807608174</v>
+        <v>101763.48138606524</v>
       </c>
       <c r="E19" s="27">
         <f>IF(E11=1,E13*DSO/DaysYr+E13*COGSR*DIO/DaysYr-E13*COGSR*DPO/DaysYr,D19)</f>
-        <v>59053.98054961954</v>
+        <v>105924.78470986002</v>
       </c>
       <c r="F19" s="27">
         <f>IF(F11=1,F13*DSO/DaysYr+F13*COGSR*DIO/DaysYr-F13*COGSR*DPO/DaysYr,E19)</f>
-        <v>61057.56053648811</v>
+        <v>109518.59458995293</v>
       </c>
       <c r="G19" s="27">
         <f>IF(G11=1,G13*DSO/DaysYr+G13*COGSR*DIO/DaysYr-G13*COGSR*DPO/DaysYr,F19)</f>
-        <v>62703.91480740065</v>
+        <v>112471.65076126455</v>
       </c>
       <c r="H19" s="27">
         <f>IF(H11=1,H13*DSO/DaysYr+H13*COGSR*DIO/DaysYr-H13*COGSR*DPO/DaysYr,G19)</f>
-        <v>63957.99310354867</v>
+        <v>114721.08377648986</v>
       </c>
       <c r="I19" s="27">
         <f>IF(I11=1,I13*DSO/DaysYr+I13*COGSR*DIO/DaysYr-I13*COGSR*DPO/DaysYr,H19)</f>
-        <v>65237.152965619636</v>
+        <v>117015.50545201964</v>
       </c>
       <c r="J19" s="27">
         <f>IF(J11=1,J13*DSO/DaysYr+J13*COGSR*DIO/DaysYr-J13*COGSR*DPO/DaysYr,I19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
       <c r="K19" s="27">
         <f>IF(K11=1,K13*DSO/DaysYr+K13*COGSR*DIO/DaysYr-K13*COGSR*DPO/DaysYr,J19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
       <c r="L19" s="27">
         <f>IF(L11=1,L13*DSO/DaysYr+L13*COGSR*DIO/DaysYr-L13*COGSR*DPO/DaysYr,K19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
       <c r="M19" s="27">
         <f>IF(M11=1,M13*DSO/DaysYr+M13*COGSR*DIO/DaysYr-M13*COGSR*DPO/DaysYr,L19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
       <c r="N19" s="27">
         <f>IF(N11=1,N13*DSO/DaysYr+N13*COGSR*DIO/DaysYr-N13*COGSR*DPO/DaysYr,M19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
       <c r="O19" s="27">
         <f>IF(O11=1,O13*DSO/DaysYr+O13*COGSR*DIO/DaysYr-O13*COGSR*DPO/DaysYr,N19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
       <c r="P19" s="27">
         <f>IF(P11=1,P13*DSO/DaysYr+P13*COGSR*DIO/DaysYr-P13*COGSR*DPO/DaysYr,O19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
       <c r="Q19" s="27">
         <f>IF(Q11=1,Q13*DSO/DaysYr+Q13*COGSR*DIO/DaysYr-Q13*COGSR*DPO/DaysYr,P19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
       <c r="R19" s="27">
         <f>IF(R11=1,R13*DSO/DaysYr+R13*COGSR*DIO/DaysYr-R13*COGSR*DPO/DaysYr,Q19)</f>
-        <v>66541.89602493204</v>
+        <v>119355.81556106005</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -9337,31 +9337,31 @@
       </c>
       <c r="D20" s="40">
         <f>IF(D11=1,D19-C19,0)</f>
-        <v>-2850.9846839182646</v>
+        <v>6641.576526065226</v>
       </c>
       <c r="E20" s="40">
         <f>IF(E11=1,E19-D19,0)</f>
-        <v>2319.962473537802</v>
+        <v>4161.303323794782</v>
       </c>
       <c r="F20" s="40">
         <f>IF(F11=1,F19-E19,0)</f>
-        <v>2003.5799868685717</v>
+        <v>3593.8098800929147</v>
       </c>
       <c r="G20" s="40">
         <f>IF(G11=1,G19-F19,0)</f>
-        <v>1646.3542709125395</v>
+        <v>2953.0561713116185</v>
       </c>
       <c r="H20" s="40">
         <f>IF(H11=1,H19-G19,0)</f>
-        <v>1254.0782961480218</v>
+        <v>2249.4330152253096</v>
       </c>
       <c r="I20" s="40">
         <f>IF(I11=1,I19-H19,0)</f>
-        <v>1279.1598620709628</v>
+        <v>2294.421675529782</v>
       </c>
       <c r="J20" s="40">
         <f>IF(J11=1,J19-I19,0)</f>
-        <v>1304.7430593124009</v>
+        <v>2340.310109040409</v>
       </c>
       <c r="K20" s="40">
         <f>IF(K11=1,K19-J19,0)</f>
@@ -9609,31 +9609,31 @@
       </c>
       <c r="D24" s="40">
         <f>D23+D17-D18-D20</f>
-        <v>145.70352556671423</v>
+        <v>-9346.857684416776</v>
       </c>
       <c r="E24" s="40">
         <f>E23+E17-E18-E20</f>
-        <v>-6589.156332412305</v>
+        <v>-8430.497182669285</v>
       </c>
       <c r="F24" s="40">
         <f>F23+F17-F18-F20</f>
-        <v>-4495.213828413787</v>
+        <v>-6085.44372163813</v>
       </c>
       <c r="G24" s="40">
         <f>G23+G17-G18-G20</f>
-        <v>-2230.7584731651077</v>
+        <v>-3537.4603735641867</v>
       </c>
       <c r="H24" s="40">
         <f>H23+H17-H18-H20</f>
-        <v>138.61449908402574</v>
+        <v>-856.7402199932621</v>
       </c>
       <c r="I24" s="40">
         <f>I23+I17-I18-I20</f>
-        <v>2128.9884415996785</v>
+        <v>1113.7266281408592</v>
       </c>
       <c r="J24" s="40">
         <f>J23+J17-J18-J20</f>
-        <v>4199.10669601629</v>
+        <v>3163.539646288282</v>
       </c>
       <c r="K24" s="40">
         <f>K23+K17-K18-K20</f>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="C31" s="40">
         <f>SUMPRODUCT(($D$5:$R$5&gt;1)*$D$11:$R$11*($D$18:$R$18-$D$17:$R$17+$D$20:$R$20))</f>
-        <v>99183.61068226986</v>
+        <v>106968.06690841439</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C32" s="31">
         <f>IF(C31&gt;0,(C30-C28)/C31,0)</f>
-        <v>0.13819884145817216</v>
+        <v>0.12814160790307644</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="C38" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_1)+WD*Kd_Pre*(1-C33)</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="C39" s="30">
         <f>IF(C31&lt;=0,C38,IF(C32&lt;C38,C38,IF(C32&gt;RonicCap,MAX(RonicCap,C38),C32)))</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -9815,63 +9815,63 @@
       </c>
       <c r="D40" s="40">
         <f>D24-IF(D11=1,0,D23*D12/C39)</f>
-        <v>145.70352556671423</v>
+        <v>-9346.857684416776</v>
       </c>
       <c r="E40" s="40">
         <f>E24-IF(E11=1,0,E23*E12/C39)</f>
-        <v>-6589.156332412305</v>
+        <v>-8430.497182669285</v>
       </c>
       <c r="F40" s="40">
         <f>F24-IF(F11=1,0,F23*F12/C39)</f>
-        <v>-4495.213828413787</v>
+        <v>-6085.44372163813</v>
       </c>
       <c r="G40" s="40">
         <f>G24-IF(G11=1,0,G23*G12/C39)</f>
-        <v>-2230.7584731651077</v>
+        <v>-3537.4603735641867</v>
       </c>
       <c r="H40" s="40">
         <f>H24-IF(H11=1,0,H23*H12/C39)</f>
-        <v>138.61449908402574</v>
+        <v>-856.7402199932621</v>
       </c>
       <c r="I40" s="40">
         <f>I24-IF(I11=1,0,I23*I12/C39)</f>
-        <v>2128.9884415996785</v>
+        <v>1113.7266281408592</v>
       </c>
       <c r="J40" s="40">
         <f>J24-IF(J11=1,0,J23*J12/C39)</f>
-        <v>4199.10669601629</v>
+        <v>3163.539646288282</v>
       </c>
       <c r="K40" s="40">
         <f>K24-IF(K11=1,0,K23*K12/C39)</f>
-        <v>18016.68200255181</v>
+        <v>17992.714543892478</v>
       </c>
       <c r="L40" s="40">
         <f>L24-IF(L11=1,0,L23*L12/C39)</f>
-        <v>18369.318963715246</v>
+        <v>18344.88239471766</v>
       </c>
       <c r="M40" s="40">
         <f>M24-IF(M11=1,0,M23*M12/C39)</f>
-        <v>18729.008664101955</v>
+        <v>18704.093602559347</v>
       </c>
       <c r="N40" s="40">
         <f>N24-IF(N11=1,0,N23*N12/C39)</f>
-        <v>19095.892158496397</v>
+        <v>19070.48903455787</v>
       </c>
       <c r="O40" s="40">
         <f>O24-IF(O11=1,0,O23*O12/C39)</f>
-        <v>19470.11332277873</v>
+        <v>19444.212375196366</v>
       </c>
       <c r="P40" s="40">
         <f>P24-IF(P11=1,0,P23*P12/C39)</f>
-        <v>19851.81891034671</v>
+        <v>19825.41018264763</v>
       </c>
       <c r="Q40" s="40">
         <f>Q24-IF(Q11=1,0,Q23*Q12/C39)</f>
-        <v>20241.158609666043</v>
+        <v>20214.231946247917</v>
       </c>
       <c r="R40" s="40">
         <f>R24-IF(R11=1,0,R23*R12/C39)</f>
-        <v>20638.28510297177</v>
+        <v>20610.830145120213</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -9880,63 +9880,63 @@
       </c>
       <c r="D41" s="27">
         <f>D40*(1+C38)^(-DCF!D10)</f>
-        <v>141.60861123071928</v>
+        <v>-9085.784030702644</v>
       </c>
       <c r="E41" s="27">
         <f>E40*(1+C38)^(-DCF!E10)</f>
-        <v>-5881.797638246135</v>
+        <v>-7530.796300740354</v>
       </c>
       <c r="F41" s="27">
         <f>F40*(1+C38)^(-DCF!F10)</f>
-        <v>-3582.9888663988995</v>
+        <v>-4857.3724704293745</v>
       </c>
       <c r="G41" s="27">
         <f>G40*(1+C38)^(-DCF!G10)</f>
-        <v>-1587.678235626635</v>
+        <v>-2523.0286606169925</v>
       </c>
       <c r="H41" s="27">
         <f>H40*(1+C38)^(-DCF!H10)</f>
-        <v>88.10503363503722</v>
+        <v>-546.094829807098</v>
       </c>
       <c r="I41" s="27">
         <f>I40*(1+C38)^(-DCF!I10)</f>
-        <v>1208.5023142262567</v>
+        <v>634.4330832525787</v>
       </c>
       <c r="J41" s="27">
         <f>J40*(1+C38)^(-DCF!J10)</f>
-        <v>2128.364121013598</v>
+        <v>1610.2820192259683</v>
       </c>
       <c r="K41" s="27">
         <f>K40*(1+C38)^(-DCF!K10)</f>
-        <v>8154.149490062477</v>
+        <v>8183.645260048995</v>
       </c>
       <c r="L41" s="27">
         <f>L40*(1+C38)^(-DCF!L10)</f>
-        <v>7424.702087199679</v>
+        <v>7456.814622535738</v>
       </c>
       <c r="M41" s="27">
         <f>M40*(1+C38)^(-DCF!M10)</f>
-        <v>6760.563386588731</v>
+        <v>6794.59211627706</v>
       </c>
       <c r="N41" s="27">
         <f>N40*(1+C38)^(-DCF!N10)</f>
-        <v>6154.926745727955</v>
+        <v>6190.275778224012</v>
       </c>
       <c r="O41" s="27">
         <f>O40*(1+C38)^(-DCF!O10)</f>
-        <v>5603.588700621363</v>
+        <v>5639.751480536866</v>
       </c>
       <c r="P41" s="27">
         <f>P40*(1+C38)^(-DCF!P10)</f>
-        <v>5102.4669200150065</v>
+        <v>5139.017558358743</v>
       </c>
       <c r="Q41" s="27">
         <f>Q40*(1+C38)^(-DCF!Q10)</f>
-        <v>4646.194456032431</v>
+        <v>4682.776968395202</v>
       </c>
       <c r="R41" s="27">
         <f>R40*(1+C38)^(-DCF!R10)</f>
-        <v>4230.098287277329</v>
+        <v>4266.415583111204</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="C42" s="27">
         <f>C35*(1-GTermCfg/C39)/(C38-GTermCfg)*IF(MidYear=1,(1+C38)^0.5,1)</f>
-        <v>223252.76015826367</v>
+        <v>224654.6756672426</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="C43" s="27">
         <f>C42*(1+C38)^(-DCF!R9)</f>
-        <v>43236.19467567898</v>
+        <v>43955.216520373615</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="C44" s="40">
         <f>SUM(D41:R41)+C43</f>
-        <v>83827.0000890379</v>
+        <v>70010.14469804353</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="C45" s="27">
         <f>C44*(1+C38)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>86251.03617995599</v>
+        <v>72021.83727312666</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="C46" s="27">
         <f>C45+BridgeAdj</f>
-        <v>157231.084439956</v>
+        <v>138001.88553312665</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="C47" s="56">
         <f>C46*MnToWon/Shares</f>
-        <v>5345.077547961856</v>
+        <v>4691.380095525618</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="C48" s="29">
         <f>C43/C44</f>
-        <v>0.5157788615810551</v>
+        <v>0.6278406752329133</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="C51" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_2)+WD*Kd_Pre*(1-C33)</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
     </row>
     <row r="52" spans="1:18">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="C52" s="30">
         <f>IF(C31&lt;=0,C51,IF(C32&lt;C51,C51,IF(C32&gt;RonicCap,MAX(RonicCap,C51),C32)))</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -10053,63 +10053,63 @@
       </c>
       <c r="D53" s="40">
         <f>D24-IF(D11=1,0,D23*D12/C52)</f>
-        <v>145.70352556671423</v>
+        <v>-9346.857684416776</v>
       </c>
       <c r="E53" s="40">
         <f>E24-IF(E11=1,0,E23*E12/C52)</f>
-        <v>-6589.156332412305</v>
+        <v>-8430.497182669285</v>
       </c>
       <c r="F53" s="40">
         <f>F24-IF(F11=1,0,F23*F12/C52)</f>
-        <v>-4495.213828413787</v>
+        <v>-6085.44372163813</v>
       </c>
       <c r="G53" s="40">
         <f>G24-IF(G11=1,0,G23*G12/C52)</f>
-        <v>-2230.7584731651077</v>
+        <v>-3537.4603735641867</v>
       </c>
       <c r="H53" s="40">
         <f>H24-IF(H11=1,0,H23*H12/C52)</f>
-        <v>138.61449908402574</v>
+        <v>-856.7402199932621</v>
       </c>
       <c r="I53" s="40">
         <f>I24-IF(I11=1,0,I23*I12/C52)</f>
-        <v>2128.9884415996785</v>
+        <v>1113.7266281408592</v>
       </c>
       <c r="J53" s="40">
         <f>J24-IF(J11=1,0,J23*J12/C52)</f>
-        <v>4199.10669601629</v>
+        <v>3163.539646288282</v>
       </c>
       <c r="K53" s="40">
         <f>K24-IF(K11=1,0,K23*K12/C52)</f>
-        <v>18292.16488763734</v>
+        <v>18267.699877222796</v>
       </c>
       <c r="L53" s="40">
         <f>L24-IF(L11=1,0,L23*L12/C52)</f>
-        <v>18650.193820942783</v>
+        <v>18625.249961707672</v>
       </c>
       <c r="M53" s="40">
         <f>M24-IF(M11=1,0,M23*M12/C52)</f>
-        <v>19015.383332914334</v>
+        <v>18989.951047882245</v>
       </c>
       <c r="N53" s="40">
         <f>N24-IF(N11=1,0,N23*N12/C52)</f>
-        <v>19387.876635125314</v>
+        <v>19361.94615578031</v>
       </c>
       <c r="O53" s="40">
         <f>O24-IF(O11=1,0,O23*O12/C52)</f>
-        <v>19767.81980338052</v>
+        <v>19741.38116583634</v>
       </c>
       <c r="P53" s="40">
         <f>P24-IF(P11=1,0,P23*P12/C52)</f>
-        <v>20155.36183500083</v>
+        <v>20128.404876093493</v>
       </c>
       <c r="Q53" s="40">
         <f>Q24-IF(Q11=1,0,Q23*Q12/C52)</f>
-        <v>20550.65470725354</v>
+        <v>20523.16906055578</v>
       </c>
       <c r="R53" s="40">
         <f>R24-IF(R11=1,0,R23*R12/C52)</f>
-        <v>20953.853436951307</v>
+        <v>20925.828528707323</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -10118,63 +10118,63 @@
       </c>
       <c r="D54" s="27">
         <f>D53*(1+C51)^(-DCF!D10)</f>
-        <v>141.29525650354455</v>
+        <v>-9065.976895600013</v>
       </c>
       <c r="E54" s="27">
         <f>E53*(1+C51)^(-DCF!E10)</f>
-        <v>-5830.119262097567</v>
+        <v>-7465.607406759314</v>
       </c>
       <c r="F54" s="27">
         <f>F53*(1+C51)^(-DCF!F10)</f>
-        <v>-3520.388847820648</v>
+        <v>-4773.7558550200265</v>
       </c>
       <c r="G54" s="27">
         <f>G53*(1+C51)^(-DCF!G10)</f>
-        <v>-1546.2705586078073</v>
+        <v>-2458.190469102033</v>
       </c>
       <c r="H54" s="27">
         <f>H53*(1+C51)^(-DCF!H10)</f>
-        <v>85.05635414163136</v>
+        <v>-527.4740662944586</v>
       </c>
       <c r="I54" s="27">
         <f>I53*(1+C51)^(-DCF!I10)</f>
-        <v>1156.475867287315</v>
+        <v>607.517187958719</v>
       </c>
       <c r="J54" s="27">
         <f>J53*(1+C51)^(-DCF!J10)</f>
-        <v>2018.8908279639716</v>
+        <v>1528.6541545745404</v>
       </c>
       <c r="K54" s="27">
         <f>K53*(1+C51)^(-DCF!K10)</f>
-        <v>7784.194641950232</v>
+        <v>7819.44304329679</v>
       </c>
       <c r="L54" s="27">
         <f>L53*(1+C51)^(-DCF!L10)</f>
-        <v>7025.821253075184</v>
+        <v>7063.534526103608</v>
       </c>
       <c r="M54" s="27">
         <f>M53*(1+C51)^(-DCF!M10)</f>
-        <v>6341.383225276563</v>
+        <v>6380.751294400329</v>
       </c>
       <c r="N54" s="27">
         <f>N53*(1+C51)^(-DCF!N10)</f>
-        <v>5722.7110279020635</v>
+        <v>5763.057773505824</v>
       </c>
       <c r="O54" s="27">
         <f>O53*(1+C51)^(-DCF!O10)</f>
-        <v>5164.437150217824</v>
+        <v>5205.200854950708</v>
       </c>
       <c r="P54" s="27">
         <f>P53*(1+C51)^(-DCF!P10)</f>
-        <v>4661.438832940346</v>
+        <v>4702.159187752297</v>
       </c>
       <c r="Q54" s="27">
         <f>Q53*(1+C51)^(-DCF!Q10)</f>
-        <v>4207.462177365344</v>
+        <v>4247.764201455202</v>
       </c>
       <c r="R54" s="27">
         <f>R53*(1+C51)^(-DCF!R10)</f>
-        <v>3797.091952665681</v>
+        <v>3836.671653296908</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="C55" s="27">
         <f>C35*(1-GTermCfg/C52)/(C51-GTermCfg)*IF(MidYear=1,(1+C51)^0.5,1)</f>
-        <v>207136.92930972786</v>
+        <v>208568.31294541486</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="C56" s="27">
         <f>C55*(1+C51)^(-DCF!R9)</f>
-        <v>35310.577191817225</v>
+        <v>35988.37919027963</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C57" s="40">
         <f>SUM(D54:R54)+C56</f>
-        <v>72520.0570905809</v>
+        <v>58852.12837479872</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="C58" s="27">
         <f>C57*(1+C51)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>74782.6095077152</v>
+        <v>60675.47652931271</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="C59" s="27">
         <f>C58+BridgeAdj</f>
-        <v>145762.65776771522</v>
+        <v>126655.52478931272</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C60" s="56">
         <f>C59*MnToWon/Shares</f>
-        <v>4955.207884882286</v>
+        <v>4305.660068987254</v>
       </c>
     </row>
     <row r="61" spans="1:18">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="C61" s="29">
         <f>C56/C57</f>
-        <v>0.4869077412296116</v>
+        <v>0.6115051432139936</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="C64" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_3)+WD*Kd_Pre*(1-C33)</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="65" spans="1:18">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="C65" s="30">
         <f>IF(C31&lt;=0,C64,IF(C32&lt;C64,C64,IF(C32&gt;RonicCap,MAX(RonicCap,C64),C32)))</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -10291,63 +10291,63 @@
       </c>
       <c r="D66" s="40">
         <f>D24-IF(D11=1,0,D23*D12/C65)</f>
-        <v>145.70352556671423</v>
+        <v>-9346.857684416776</v>
       </c>
       <c r="E66" s="40">
         <f>E24-IF(E11=1,0,E23*E12/C65)</f>
-        <v>-6589.156332412305</v>
+        <v>-8430.497182669285</v>
       </c>
       <c r="F66" s="40">
         <f>F24-IF(F11=1,0,F23*F12/C65)</f>
-        <v>-4495.213828413787</v>
+        <v>-6085.44372163813</v>
       </c>
       <c r="G66" s="40">
         <f>G24-IF(G11=1,0,G23*G12/C65)</f>
-        <v>-2230.7584731651077</v>
+        <v>-3537.4603735641867</v>
       </c>
       <c r="H66" s="40">
         <f>H24-IF(H11=1,0,H23*H12/C65)</f>
-        <v>138.61449908402574</v>
+        <v>-856.7402199932621</v>
       </c>
       <c r="I66" s="40">
         <f>I24-IF(I11=1,0,I23*I12/C65)</f>
-        <v>2128.9884415996785</v>
+        <v>1113.7266281408592</v>
       </c>
       <c r="J66" s="40">
         <f>J24-IF(J11=1,0,J23*J12/C65)</f>
-        <v>4199.10669601629</v>
+        <v>3163.539646288282</v>
       </c>
       <c r="K66" s="40">
         <f>K24-IF(K11=1,0,K23*K12/C65)</f>
-        <v>18528.610774178127</v>
+        <v>18504.022473374564</v>
       </c>
       <c r="L66" s="40">
         <f>L24-IF(L11=1,0,L23*L12/C65)</f>
-        <v>18891.267616157184</v>
+        <v>18866.1980533946</v>
       </c>
       <c r="M66" s="40">
         <f>M24-IF(M11=1,0,M23*M12/C65)</f>
-        <v>19261.17759497582</v>
+        <v>19235.617145015036</v>
       </c>
       <c r="N66" s="40">
         <f>N24-IF(N11=1,0,N23*N12/C65)</f>
-        <v>19638.485773370827</v>
+        <v>19612.424618467885</v>
       </c>
       <c r="O66" s="40">
         <f>O24-IF(O11=1,0,O23*O12/C65)</f>
-        <v>20023.34011533374</v>
+        <v>19996.768241389793</v>
       </c>
       <c r="P66" s="40">
         <f>P24-IF(P11=1,0,P23*P12/C65)</f>
-        <v>20415.891544135913</v>
+        <v>20388.79873677014</v>
       </c>
       <c r="Q66" s="40">
         <f>Q24-IF(Q11=1,0,Q23*Q12/C65)</f>
-        <v>20816.29400151412</v>
+        <v>20788.669842058087</v>
       </c>
       <c r="R66" s="40">
         <f>R24-IF(R11=1,0,R23*R12/C65)</f>
-        <v>21224.704508039897</v>
+        <v>21196.538369451795</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -10356,63 +10356,63 @@
       </c>
       <c r="D67" s="27">
         <f>D66*(1+C64)^(-DCF!D10)</f>
-        <v>140.9853161981698</v>
+        <v>-9046.382413359759</v>
       </c>
       <c r="E67" s="27">
         <f>E66*(1+C64)^(-DCF!E10)</f>
-        <v>-5779.339274788051</v>
+        <v>-7401.535166996822</v>
       </c>
       <c r="F67" s="27">
         <f>F66*(1+C64)^(-DCF!F10)</f>
-        <v>-3459.413738719964</v>
+        <v>-4692.278012847919</v>
       </c>
       <c r="G67" s="27">
         <f>G66*(1+C64)^(-DCF!G10)</f>
-        <v>-1506.2895876360335</v>
+        <v>-2395.5538335630717</v>
       </c>
       <c r="H67" s="27">
         <f>H66*(1+C64)^(-DCF!H10)</f>
-        <v>82.13836451888663</v>
+        <v>-509.63998708868917</v>
       </c>
       <c r="I67" s="27">
         <f>I66*(1+C64)^(-DCF!I10)</f>
-        <v>1107.1135435360484</v>
+        <v>581.9597292449093</v>
       </c>
       <c r="J67" s="27">
         <f>J66*(1+C64)^(-DCF!J10)</f>
-        <v>1915.929576866018</v>
+        <v>1451.812319321625</v>
       </c>
       <c r="K67" s="27">
         <f>K66*(1+C64)^(-DCF!K10)</f>
-        <v>7417.699956170923</v>
+        <v>7458.065770181398</v>
       </c>
       <c r="L67" s="27">
         <f>L66*(1+C64)^(-DCF!L10)</f>
-        <v>6636.956526278547</v>
+        <v>6679.507475588662</v>
       </c>
       <c r="M67" s="27">
         <f>M66*(1+C64)^(-DCF!M10)</f>
-        <v>5938.437319072001</v>
+        <v>5982.272127740492</v>
       </c>
       <c r="N67" s="27">
         <f>N66*(1+C64)^(-DCF!N10)</f>
-        <v>5312.526527011514</v>
+        <v>5356.908070809481</v>
       </c>
       <c r="O67" s="27">
         <f>O66*(1+C64)^(-DCF!O10)</f>
-        <v>4752.623482459347</v>
+        <v>4796.954348572142</v>
       </c>
       <c r="P67" s="27">
         <f>P66*(1+C64)^(-DCF!P10)</f>
-        <v>4252.523318525796</v>
+        <v>4296.327707505235</v>
       </c>
       <c r="Q67" s="27">
         <f>Q66*(1+C64)^(-DCF!Q10)</f>
-        <v>3805.075123697091</v>
+        <v>3847.976868529684</v>
       </c>
       <c r="R67" s="27">
         <f>R66*(1+C64)^(-DCF!R10)</f>
-        <v>3404.1230248391807</v>
+        <v>3445.8277032061865</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="C68" s="27">
         <f>C35*(1-GTermCfg/C65)/(C64-GTermCfg)*IF(MidYear=1,(1+C64)^0.5,1)</f>
-        <v>193301.09030032487</v>
+        <v>194740.07811718175</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="C69" s="27">
         <f>C68*(1+C64)^(-DCF!R9)</f>
-        <v>29037.61452839426</v>
+        <v>29665.852144698703</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="C70" s="40">
         <f>SUM(D67:R67)+C69</f>
-        <v>63058.70400642374</v>
+        <v>49518.07485154226</v>
       </c>
     </row>
     <row r="71" spans="1:18">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="C71" s="27">
         <f>C70*(1+C64)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>65169.02425845037</v>
+        <v>51162.81595172674</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="C72" s="27">
         <f>C71+BridgeAdj</f>
-        <v>136149.07251845038</v>
+        <v>117142.86421172676</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="C73" s="56">
         <f>C72*MnToWon/Shares</f>
-        <v>4628.393636578313</v>
+        <v>3982.276759282653</v>
       </c>
     </row>
     <row r="74" spans="1:18">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C74" s="29">
         <f>C69/C70</f>
-        <v>0.46048543156605665</v>
+        <v>0.5990913870064306</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -11444,67 +11444,67 @@
       </c>
       <c r="C92" s="27">
         <f>NWC_Open</f>
-        <v>59585.00276</v>
+        <v>95121.90486000001</v>
       </c>
       <c r="D92" s="27">
         <f>IF(D84=1,D86*DSO/DaysYr+D86*COGSR*DIO/DaysYr-D86*COGSR*DPO/DaysYr,C92)</f>
-        <v>57816.8772557815</v>
+        <v>103705.79965848745</v>
       </c>
       <c r="E92" s="27">
         <f>IF(E84=1,E86*DSO/DaysYr+E86*COGSR*DIO/DaysYr-E86*COGSR*DPO/DaysYr,D92)</f>
-        <v>61048.37307042094</v>
+        <v>109502.115084996</v>
       </c>
       <c r="F92" s="27">
         <f>IF(F84=1,F86*DSO/DaysYr+F86*COGSR*DIO/DaysYr-F86*COGSR*DPO/DaysYr,E92)</f>
-        <v>63730.10242041083</v>
+        <v>114312.31757099289</v>
       </c>
       <c r="G92" s="27">
         <f>IF(G84=1,G86*DSO/DaysYr+G86*COGSR*DIO/DaysYr-G86*COGSR*DPO/DaysYr,F92)</f>
-        <v>65767.16954437266</v>
+        <v>117966.19313597513</v>
       </c>
       <c r="H92" s="27">
         <f>IF(H84=1,H86*DSO/DaysYr+H86*COGSR*DIO/DaysYr-H86*COGSR*DPO/DaysYr,G92)</f>
-        <v>67082.51293526014</v>
+        <v>120325.51699869466</v>
       </c>
       <c r="I92" s="27">
         <f>IF(I84=1,I86*DSO/DaysYr+I86*COGSR*DIO/DaysYr-I86*COGSR*DPO/DaysYr,H92)</f>
-        <v>68424.16319396533</v>
+        <v>122732.02733866854</v>
       </c>
       <c r="J92" s="27">
         <f>IF(J84=1,J86*DSO/DaysYr+J86*COGSR*DIO/DaysYr-J86*COGSR*DPO/DaysYr,I92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="K92" s="27">
         <f>IF(K84=1,K86*DSO/DaysYr+K86*COGSR*DIO/DaysYr-K86*COGSR*DPO/DaysYr,J92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="L92" s="27">
         <f>IF(L84=1,L86*DSO/DaysYr+L86*COGSR*DIO/DaysYr-L86*COGSR*DPO/DaysYr,K92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="M92" s="27">
         <f>IF(M84=1,M86*DSO/DaysYr+M86*COGSR*DIO/DaysYr-M86*COGSR*DPO/DaysYr,L92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="N92" s="27">
         <f>IF(N84=1,N86*DSO/DaysYr+N86*COGSR*DIO/DaysYr-N86*COGSR*DPO/DaysYr,M92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="O92" s="27">
         <f>IF(O84=1,O86*DSO/DaysYr+O86*COGSR*DIO/DaysYr-O86*COGSR*DPO/DaysYr,N92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="P92" s="27">
         <f>IF(P84=1,P86*DSO/DaysYr+P86*COGSR*DIO/DaysYr-P86*COGSR*DPO/DaysYr,O92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="Q92" s="27">
         <f>IF(Q84=1,Q86*DSO/DaysYr+Q86*COGSR*DIO/DaysYr-Q86*COGSR*DPO/DaysYr,P92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="R92" s="27">
         <f>IF(R84=1,R86*DSO/DaysYr+R86*COGSR*DIO/DaysYr-R86*COGSR*DPO/DaysYr,Q92)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
     </row>
     <row r="93" spans="1:18">
@@ -11516,31 +11516,31 @@
       </c>
       <c r="D93" s="40">
         <f>IF(D84=1,D92-C92,0)</f>
-        <v>-1768.1255042185003</v>
+        <v>8583.89479848744</v>
       </c>
       <c r="E93" s="40">
         <f>IF(E84=1,E92-D92,0)</f>
-        <v>3231.4958146394347</v>
+        <v>5796.315426508547</v>
       </c>
       <c r="F93" s="40">
         <f>IF(F84=1,F92-E92,0)</f>
-        <v>2681.729349989895</v>
+        <v>4810.202485996895</v>
       </c>
       <c r="G93" s="40">
         <f>IF(G84=1,G92-F92,0)</f>
-        <v>2037.0671239618314</v>
+        <v>3653.8755649822415</v>
       </c>
       <c r="H93" s="40">
         <f>IF(H84=1,H92-G92,0)</f>
-        <v>1315.3433908874722</v>
+        <v>2359.323862719524</v>
       </c>
       <c r="I93" s="40">
         <f>IF(I84=1,I92-H92,0)</f>
-        <v>1341.6502587051946</v>
+        <v>2406.5103399738873</v>
       </c>
       <c r="J93" s="40">
         <f>IF(J84=1,J92-I92,0)</f>
-        <v>1368.4832638793014</v>
+        <v>2454.640546773371</v>
       </c>
       <c r="K93" s="40">
         <f>IF(K84=1,K92-J92,0)</f>
@@ -11788,31 +11788,31 @@
       </c>
       <c r="D97" s="40">
         <f>D96+D90-D91-D93</f>
-        <v>1088.1558589868573</v>
+        <v>-9263.864443719081</v>
       </c>
       <c r="E97" s="40">
         <f>E96+E90-E91-E93</f>
-        <v>-2837.8321879682517</v>
+        <v>-5402.651799837364</v>
       </c>
       <c r="F97" s="40">
         <f>F96+F90-F91-F93</f>
-        <v>-316.36124490337534</v>
+        <v>-2444.8343809103753</v>
       </c>
       <c r="G97" s="40">
         <f>G96+G90-G91-G93</f>
-        <v>2402.205094190198</v>
+        <v>785.3966531697879</v>
       </c>
       <c r="H97" s="40">
         <f>H96+H90-H91-H93</f>
-        <v>5256.800480641788</v>
+        <v>4212.8200088097365</v>
       </c>
       <c r="I97" s="40">
         <f>I96+I90-I91-I93</f>
-        <v>7447.089223449144</v>
+        <v>6382.229142180451</v>
       </c>
       <c r="J97" s="40">
         <f>J96+J90-J91-J93</f>
-        <v>9723.071595776491</v>
+        <v>8636.914312882422</v>
       </c>
       <c r="K97" s="40">
         <f>K96+K90-K91-K93</f>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C104" s="40">
         <f>SUMPRODUCT(($D$78:$R$78&gt;1)*$D$84:$R$84*($D$91:$R$91-$D$90:$R$90+$D$93:$R$93))</f>
-        <v>105434.23062591458</v>
+        <v>114939.32965080593</v>
       </c>
     </row>
     <row r="105" spans="1:18">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="C105" s="31">
         <f>IF(C104&gt;0,(C103-C101)/C104,0)</f>
-        <v>0.14574114982678935</v>
+        <v>0.13368884305491455</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="C111" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_1)+WD*Kd_Pre*(1-C106)</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C112" s="30">
         <f>IF(C104&lt;=0,C111,IF(C105&lt;C111,C111,IF(C105&gt;RonicCap,MAX(RonicCap,C111),C105)))</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
     </row>
     <row r="113" spans="1:18">
@@ -11994,63 +11994,63 @@
       </c>
       <c r="D113" s="40">
         <f>D97-IF(D84=1,0,D96*D85/C112)</f>
-        <v>1088.1558589868573</v>
+        <v>-9263.864443719081</v>
       </c>
       <c r="E113" s="40">
         <f>E97-IF(E84=1,0,E96*E85/C112)</f>
-        <v>-2837.8321879682517</v>
+        <v>-5402.651799837364</v>
       </c>
       <c r="F113" s="40">
         <f>F97-IF(F84=1,0,F96*F85/C112)</f>
-        <v>-316.36124490337534</v>
+        <v>-2444.8343809103753</v>
       </c>
       <c r="G113" s="40">
         <f>G97-IF(G84=1,0,G96*G85/C112)</f>
-        <v>2402.205094190198</v>
+        <v>785.3966531697879</v>
       </c>
       <c r="H113" s="40">
         <f>H97-IF(H84=1,0,H96*H85/C112)</f>
-        <v>5256.800480641788</v>
+        <v>4212.8200088097365</v>
       </c>
       <c r="I113" s="40">
         <f>I97-IF(I84=1,0,I96*I85/C112)</f>
-        <v>7447.089223449144</v>
+        <v>6382.229142180451</v>
       </c>
       <c r="J113" s="40">
         <f>J97-IF(J84=1,0,J96*J85/C112)</f>
-        <v>9723.071595776491</v>
+        <v>8636.914312882422</v>
       </c>
       <c r="K113" s="40">
         <f>K97-IF(K84=1,0,K96*K85/C112)</f>
-        <v>23416.274533362044</v>
+        <v>23385.1240367415</v>
       </c>
       <c r="L113" s="40">
         <f>L97-IF(L84=1,0,L96*L85/C112)</f>
-        <v>23876.903345141684</v>
+        <v>23845.14007742366</v>
       </c>
       <c r="M113" s="40">
         <f>M97-IF(M84=1,0,M96*M85/C112)</f>
-        <v>24346.74473315692</v>
+        <v>24314.35643891947</v>
       </c>
       <c r="N113" s="40">
         <f>N97-IF(N84=1,0,N96*N85/C112)</f>
-        <v>24825.982948932466</v>
+        <v>24792.957127645197</v>
       </c>
       <c r="O113" s="40">
         <f>O97-IF(O84=1,0,O96*O85/C112)</f>
-        <v>25314.805929023518</v>
+        <v>25281.129830145434</v>
       </c>
       <c r="P113" s="40">
         <f>P97-IF(P84=1,0,P96*P85/C112)</f>
-        <v>25813.40536871639</v>
+        <v>25779.065986695678</v>
       </c>
       <c r="Q113" s="40">
         <f>Q97-IF(Q84=1,0,Q96*Q85/C112)</f>
-        <v>26321.97679720312</v>
+        <v>26286.96086637693</v>
       </c>
       <c r="R113" s="40">
         <f>R97-IF(R84=1,0,R96*R85/C112)</f>
-        <v>26840.719654259585</v>
+        <v>26805.0136436518</v>
       </c>
     </row>
     <row r="114" spans="1:18">
@@ -12059,63 +12059,63 @@
       </c>
       <c r="D114" s="27">
         <f>D113*(1+C111)^(-DCF!D10)</f>
-        <v>1057.5738603054187</v>
+        <v>-9005.108932563024</v>
       </c>
       <c r="E114" s="27">
         <f>E113*(1+C111)^(-DCF!E10)</f>
-        <v>-2533.185406274874</v>
+        <v>-4826.081938802244</v>
       </c>
       <c r="F114" s="27">
         <f>F113*(1+C111)^(-DCF!F10)</f>
-        <v>-252.16126785427485</v>
+        <v>-1951.4552692957225</v>
       </c>
       <c r="G114" s="27">
         <f>G113*(1+C111)^(-DCF!G10)</f>
-        <v>1709.7004410996685</v>
+        <v>560.169742312474</v>
       </c>
       <c r="H114" s="27">
         <f>H113*(1+C111)^(-DCF!H10)</f>
-        <v>3341.2852639525872</v>
+        <v>2685.293828900648</v>
       </c>
       <c r="I114" s="27">
         <f>I113*(1+C111)^(-DCF!I10)</f>
-        <v>4227.277323321409</v>
+        <v>3635.629435795345</v>
       </c>
       <c r="J114" s="27">
         <f>J113*(1+C111)^(-DCF!J10)</f>
-        <v>4928.247417511401</v>
+        <v>4396.299517203079</v>
       </c>
       <c r="K114" s="27">
         <f>K113*(1+C111)^(-DCF!K10)</f>
-        <v>10597.944894533473</v>
+        <v>10636.280535218</v>
       </c>
       <c r="L114" s="27">
         <f>L113*(1+C111)^(-DCF!L10)</f>
-        <v>9650.814733671721</v>
+        <v>9692.555415724282</v>
       </c>
       <c r="M114" s="27">
         <f>M113*(1+C111)^(-DCF!M10)</f>
-        <v>8788.383516586679</v>
+        <v>8832.619109093148</v>
       </c>
       <c r="N114" s="27">
         <f>N113*(1+C111)^(-DCF!N10)</f>
-        <v>8001.831240620191</v>
+        <v>8047.787432178276</v>
       </c>
       <c r="O114" s="27">
         <f>O113*(1+C111)^(-DCF!O10)</f>
-        <v>7285.718275524338</v>
+        <v>7332.736684726092</v>
       </c>
       <c r="P114" s="27">
         <f>P113*(1+C111)^(-DCF!P10)</f>
-        <v>6634.759645030071</v>
+        <v>6682.28659700929</v>
       </c>
       <c r="Q114" s="27">
         <f>Q113*(1+C111)^(-DCF!Q10)</f>
-        <v>6041.997151713302</v>
+        <v>6089.569726987546</v>
       </c>
       <c r="R114" s="27">
         <f>R113*(1+C111)^(-DCF!R10)</f>
-        <v>5501.371924667598</v>
+        <v>5548.603676298816</v>
       </c>
     </row>
     <row r="115" spans="1:18">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="C115" s="27">
         <f>C108*(1-GTermCfg/C112)/(C111-GTermCfg)*IF(MidYear=1,(1+C111)^0.5,1)</f>
-        <v>290371.5681902389</v>
+        <v>292194.95619459706</v>
       </c>
     </row>
     <row r="116" spans="1:18">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="C116" s="27">
         <f>C115*(1+C111)^(-DCF!R9)</f>
-        <v>56234.743264340585</v>
+        <v>57169.932152751244</v>
       </c>
     </row>
     <row r="117" spans="1:18">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="C117" s="40">
         <f>SUM(D114:R114)+C116</f>
-        <v>131216.3022787493</v>
+        <v>115527.11771353724</v>
       </c>
     </row>
     <row r="118" spans="1:18">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="C118" s="27">
         <f>C117*(1+C111)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>135010.70088662815</v>
+        <v>118846.70869463647</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="C119" s="27">
         <f>C118+BridgeAdj</f>
-        <v>205990.74914662816</v>
+        <v>184826.75695463648</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="C120" s="56">
         <f>C119*MnToWon/Shares</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
     </row>
     <row r="121" spans="1:18">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="C121" s="29">
         <f>C116/C117</f>
-        <v>0.4285652185570535</v>
+        <v>0.4948615812826791</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="C124" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_2)+WD*Kd_Pre*(1-C106)</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="C125" s="30">
         <f>IF(C104&lt;=0,C124,IF(C105&lt;C124,C124,IF(C105&gt;RonicCap,MAX(RonicCap,C124),C105)))</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -12232,63 +12232,63 @@
       </c>
       <c r="D126" s="40">
         <f>D97-IF(D84=1,0,D96*D85/C125)</f>
-        <v>1088.1558589868573</v>
+        <v>-9263.864443719081</v>
       </c>
       <c r="E126" s="40">
         <f>E97-IF(E84=1,0,E96*E85/C125)</f>
-        <v>-2837.8321879682517</v>
+        <v>-5402.651799837364</v>
       </c>
       <c r="F126" s="40">
         <f>F97-IF(F84=1,0,F96*F85/C125)</f>
-        <v>-316.36124490337534</v>
+        <v>-2444.8343809103753</v>
       </c>
       <c r="G126" s="40">
         <f>G97-IF(G84=1,0,G96*G85/C125)</f>
-        <v>2402.205094190198</v>
+        <v>785.3966531697879</v>
       </c>
       <c r="H126" s="40">
         <f>H97-IF(H84=1,0,H96*H85/C125)</f>
-        <v>5256.800480641788</v>
+        <v>4212.8200088097365</v>
       </c>
       <c r="I126" s="40">
         <f>I97-IF(I84=1,0,I96*I85/C125)</f>
-        <v>7447.089223449144</v>
+        <v>6382.229142180451</v>
       </c>
       <c r="J126" s="40">
         <f>J97-IF(J84=1,0,J96*J85/C125)</f>
-        <v>9723.071595776491</v>
+        <v>8636.914312882422</v>
       </c>
       <c r="K126" s="40">
         <f>K97-IF(K84=1,0,K96*K85/C125)</f>
-        <v>23774.319531075373</v>
+        <v>23742.522366633693</v>
       </c>
       <c r="L126" s="40">
         <f>L97-IF(L84=1,0,L96*L85/C125)</f>
-        <v>24241.991557249574</v>
+        <v>24209.568900906786</v>
       </c>
       <c r="M126" s="40">
         <f>M97-IF(M84=1,0,M96*M85/C125)</f>
-        <v>24719.01702394726</v>
+        <v>24685.956365865346</v>
       </c>
       <c r="N126" s="40">
         <f>N97-IF(N84=1,0,N96*N85/C125)</f>
-        <v>25205.582999978906</v>
+        <v>25171.871580123076</v>
       </c>
       <c r="O126" s="40">
         <f>O97-IF(O84=1,0,O96*O85/C125)</f>
-        <v>25701.880295531177</v>
+        <v>25667.505098665955</v>
       </c>
       <c r="P126" s="40">
         <f>P97-IF(P84=1,0,P96*P85/C125)</f>
-        <v>26208.103536994495</v>
+        <v>26173.0512875797</v>
       </c>
       <c r="Q126" s="40">
         <f>Q97-IF(Q84=1,0,Q96*Q85/C125)</f>
-        <v>26724.451243287083</v>
+        <v>26688.708400271717</v>
       </c>
       <c r="R126" s="40">
         <f>R97-IF(R84=1,0,R96*R85/C125)</f>
-        <v>27251.12590370552</v>
+        <v>27214.67865521757</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -12297,63 +12297,63 @@
       </c>
       <c r="D127" s="27">
         <f>D126*(1+C124)^(-DCF!D10)</f>
-        <v>1055.2336370267428</v>
+        <v>-8985.477670292377</v>
       </c>
       <c r="E127" s="27">
         <f>E126*(1+C124)^(-DCF!E10)</f>
-        <v>-2510.9284507774096</v>
+        <v>-4784.305886006676</v>
       </c>
       <c r="F127" s="27">
         <f>F126*(1+C124)^(-DCF!F10)</f>
-        <v>-247.75564432570997</v>
+        <v>-1917.8621928465486</v>
       </c>
       <c r="G127" s="27">
         <f>G126*(1+C124)^(-DCF!G10)</f>
-        <v>1665.1103459056883</v>
+        <v>545.7741892219041</v>
       </c>
       <c r="H127" s="27">
         <f>H126*(1+C124)^(-DCF!H10)</f>
-        <v>3225.6674899667373</v>
+        <v>2593.7305717140307</v>
       </c>
       <c r="I127" s="27">
         <f>I126*(1+C124)^(-DCF!I10)</f>
-        <v>4045.291557329076</v>
+        <v>3481.387445892395</v>
       </c>
       <c r="J127" s="27">
         <f>J126*(1+C124)^(-DCF!J10)</f>
-        <v>4674.7609635575745</v>
+        <v>4173.4438076610395</v>
       </c>
       <c r="K127" s="27">
         <f>K126*(1+C124)^(-DCF!K10)</f>
-        <v>10117.114723522098</v>
+        <v>10162.927056929337</v>
       </c>
       <c r="L127" s="27">
         <f>L126*(1+C124)^(-DCF!L10)</f>
-        <v>9132.339381295687</v>
+        <v>9181.360043232437</v>
       </c>
       <c r="M127" s="27">
         <f>M126*(1+C124)^(-DCF!M10)</f>
-        <v>8243.470939113628</v>
+        <v>8294.647397343944</v>
       </c>
       <c r="N127" s="27">
         <f>N126*(1+C124)^(-DCF!N10)</f>
-        <v>7439.920859479294</v>
+        <v>7492.3744243659285</v>
       </c>
       <c r="O127" s="27">
         <f>O126*(1+C124)^(-DCF!O10)</f>
-        <v>6714.738739473604</v>
+        <v>6767.73921549311</v>
       </c>
       <c r="P127" s="27">
         <f>P126*(1+C124)^(-DCF!P10)</f>
-        <v>6061.288929723765</v>
+        <v>6114.237781930502</v>
       </c>
       <c r="Q127" s="27">
         <f>Q126*(1+C124)^(-DCF!Q10)</f>
-        <v>5471.461586928771</v>
+        <v>5523.871084005039</v>
       </c>
       <c r="R127" s="27">
         <f>R126*(1+C124)^(-DCF!R10)</f>
-        <v>4938.233971206715</v>
+        <v>4989.70857984507</v>
       </c>
     </row>
     <row r="128" spans="1:18">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="C128" s="27">
         <f>C108*(1-GTermCfg/C125)/(C124-GTermCfg)*IF(MidYear=1,(1+C124)^0.5,1)</f>
-        <v>269410.66686538793</v>
+        <v>271272.38230703195</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="C129" s="27">
         <f>C128*(1+C124)^(-DCF!R9)</f>
-        <v>45926.36465332824</v>
+        <v>46807.941342801125</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="C130" s="40">
         <f>SUM(D127:R127)+C129</f>
-        <v>115952.3136827545</v>
+        <v>100441.49719129025</v>
       </c>
     </row>
     <row r="131" spans="1:18">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="C131" s="27">
         <f>C130*(1+C124)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>119569.90856781568</v>
+        <v>103553.36117306571</v>
       </c>
     </row>
     <row r="132" spans="1:18">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="C132" s="27">
         <f>C131+BridgeAdj</f>
-        <v>190549.95682781568</v>
+        <v>169533.40943306574</v>
       </c>
     </row>
     <row r="133" spans="1:18">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="C133" s="56">
         <f>C132*MnToWon/Shares</f>
-        <v>6477.75406264789</v>
+        <v>5763.295620696146</v>
       </c>
     </row>
     <row r="134" spans="1:18">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="C134" s="29">
         <f>C129/C130</f>
-        <v>0.3960797606762963</v>
+        <v>0.466021939653644</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="C137" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_3)+WD*Kd_Pre*(1-C106)</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="138" spans="1:18">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="C138" s="30">
         <f>IF(C104&lt;=0,C137,IF(C105&lt;C137,C137,IF(C105&gt;RonicCap,MAX(RonicCap,C137),C105)))</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="139" spans="1:18">
@@ -12470,63 +12470,63 @@
       </c>
       <c r="D139" s="40">
         <f>D97-IF(D84=1,0,D96*D85/C138)</f>
-        <v>1088.1558589868573</v>
+        <v>-9263.864443719081</v>
       </c>
       <c r="E139" s="40">
         <f>E97-IF(E84=1,0,E96*E85/C138)</f>
-        <v>-2837.8321879682517</v>
+        <v>-5402.651799837364</v>
       </c>
       <c r="F139" s="40">
         <f>F97-IF(F84=1,0,F96*F85/C138)</f>
-        <v>-316.36124490337534</v>
+        <v>-2444.8343809103753</v>
       </c>
       <c r="G139" s="40">
         <f>G97-IF(G84=1,0,G96*G85/C138)</f>
-        <v>2402.205094190198</v>
+        <v>785.3966531697879</v>
       </c>
       <c r="H139" s="40">
         <f>H97-IF(H84=1,0,H96*H85/C138)</f>
-        <v>5256.800480641788</v>
+        <v>4212.8200088097365</v>
       </c>
       <c r="I139" s="40">
         <f>I97-IF(I84=1,0,I96*I85/C138)</f>
-        <v>7447.089223449144</v>
+        <v>6382.229142180451</v>
       </c>
       <c r="J139" s="40">
         <f>J97-IF(J84=1,0,J96*J85/C138)</f>
-        <v>9723.071595776491</v>
+        <v>8636.914312882422</v>
       </c>
       <c r="K139" s="40">
         <f>K97-IF(K84=1,0,K96*K85/C138)</f>
-        <v>24081.6281570887</v>
+        <v>24049.670752176764</v>
       </c>
       <c r="L139" s="40">
         <f>L97-IF(L84=1,0,L96*L85/C138)</f>
-        <v>24555.345346725964</v>
+        <v>24522.759297772842</v>
       </c>
       <c r="M139" s="40">
         <f>M97-IF(M84=1,0,M96*M85/C138)</f>
-        <v>25038.536880155978</v>
+        <v>25005.309614280846</v>
       </c>
       <c r="N139" s="40">
         <f>N97-IF(N84=1,0,N96*N85/C138)</f>
-        <v>25531.39224425459</v>
+        <v>25497.510937119012</v>
       </c>
       <c r="O139" s="40">
         <f>O97-IF(O84=1,0,O96*O85/C138)</f>
-        <v>26034.104715635178</v>
+        <v>25999.556286413936</v>
       </c>
       <c r="P139" s="40">
         <f>P97-IF(P84=1,0,P96*P85/C138)</f>
-        <v>26546.871436443373</v>
+        <v>26511.642542694764</v>
       </c>
       <c r="Q139" s="40">
         <f>Q97-IF(Q84=1,0,Q96*Q85/C138)</f>
-        <v>27069.893491667735</v>
+        <v>27033.970524101205</v>
       </c>
       <c r="R139" s="40">
         <f>R97-IF(R84=1,0,R96*R85/C138)</f>
-        <v>27603.37598799658</v>
+        <v>27566.74506513578</v>
       </c>
     </row>
     <row r="140" spans="1:18">
@@ -12535,63 +12535,63 @@
       </c>
       <c r="D140" s="27">
         <f>D139*(1+C137)^(-DCF!D10)</f>
-        <v>1052.9189136326593</v>
+        <v>-8966.05717268266</v>
       </c>
       <c r="E140" s="27">
         <f>E139*(1+C137)^(-DCF!E10)</f>
-        <v>-2489.05841534014</v>
+        <v>-4743.245436786191</v>
       </c>
       <c r="F140" s="27">
         <f>F139*(1+C137)^(-DCF!F10)</f>
-        <v>-243.4643776230494</v>
+        <v>-1885.1283711341794</v>
       </c>
       <c r="G140" s="27">
         <f>G139*(1+C137)^(-DCF!G10)</f>
-        <v>1622.0566073255561</v>
+        <v>531.8674316266098</v>
       </c>
       <c r="H140" s="27">
         <f>H139*(1+C137)^(-DCF!H10)</f>
-        <v>3115.005983755516</v>
+        <v>2506.0356509393837</v>
       </c>
       <c r="I140" s="27">
         <f>I139*(1+C137)^(-DCF!I10)</f>
-        <v>3872.6247536632686</v>
+        <v>3334.9299996197533</v>
       </c>
       <c r="J140" s="27">
         <f>J139*(1+C137)^(-DCF!J10)</f>
-        <v>4436.353204839304</v>
+        <v>3963.6546408008307</v>
       </c>
       <c r="K140" s="27">
         <f>K139*(1+C137)^(-DCF!K10)</f>
-        <v>9640.781724137913</v>
+        <v>9693.24515677762</v>
       </c>
       <c r="L140" s="27">
         <f>L139*(1+C137)^(-DCF!L10)</f>
-        <v>8626.883217439063</v>
+        <v>8682.192012823829</v>
       </c>
       <c r="M140" s="27">
         <f>M139*(1+C137)^(-DCF!M10)</f>
-        <v>7719.6620554946685</v>
+        <v>7776.645044622337</v>
       </c>
       <c r="N140" s="27">
         <f>N139*(1+C137)^(-DCF!N10)</f>
-        <v>6906.652586884117</v>
+        <v>6964.351668991961</v>
       </c>
       <c r="O140" s="27">
         <f>O139*(1+C137)^(-DCF!O10)</f>
-        <v>6179.303587895484</v>
+        <v>6236.9420440105805</v>
       </c>
       <c r="P140" s="27">
         <f>P139*(1+C137)^(-DCF!P10)</f>
-        <v>5529.574330532127</v>
+        <v>5586.533365609051</v>
       </c>
       <c r="Q140" s="27">
         <f>Q139*(1+C137)^(-DCF!Q10)</f>
-        <v>4948.190024544356</v>
+        <v>5003.980246528178</v>
       </c>
       <c r="R140" s="27">
         <f>R139*(1+C137)^(-DCF!R10)</f>
-        <v>4427.1658872064945</v>
+        <v>4481.4040942442825</v>
       </c>
     </row>
     <row r="141" spans="1:18">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C141" s="27">
         <f>C108*(1-GTermCfg/C138)/(C137-GTermCfg)*IF(MidYear=1,(1+C137)^0.5,1)</f>
-        <v>251415.21512924816</v>
+        <v>253286.82087643433</v>
       </c>
     </row>
     <row r="142" spans="1:18">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="C142" s="27">
         <f>C141*(1+C137)^(-DCF!R9)</f>
-        <v>37767.49573504167</v>
+        <v>38584.60698469924</v>
       </c>
     </row>
     <row r="143" spans="1:18">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="C143" s="40">
         <f>SUM(D140:R140)+C142</f>
-        <v>103112.14581942902</v>
+        <v>87751.95736069062</v>
       </c>
     </row>
     <row r="144" spans="1:18">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="C144" s="27">
         <f>C143*(1+C137)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>106562.89307123581</v>
+        <v>90666.63551256688</v>
       </c>
     </row>
     <row r="145" spans="1:18">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="C145" s="27">
         <f>C144+BridgeAdj</f>
-        <v>177542.9413312358</v>
+        <v>156646.6837725669</v>
       </c>
     </row>
     <row r="146" spans="1:18">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="C146" s="56">
         <f>C145*MnToWon/Shares</f>
-        <v>6035.580005626037</v>
+        <v>5325.210821879023</v>
       </c>
     </row>
     <row r="147" spans="1:18">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="C147" s="29">
         <f>C142/C143</f>
-        <v>0.36627591672062065</v>
+        <v>0.4397008128958683</v>
       </c>
     </row>
     <row r="150" spans="1:18">
@@ -13623,67 +13623,67 @@
       </c>
       <c r="C165" s="27">
         <f>NWC_Open</f>
-        <v>59585.00276</v>
+        <v>95121.90486000001</v>
       </c>
       <c r="D165" s="27">
         <f>IF(D157=1,D159*DSO/DaysYr+D159*COGSR*DIO/DaysYr-D159*COGSR*DPO/DaysYr,C165)</f>
-        <v>58899.73643548126</v>
+        <v>105648.11793090966</v>
       </c>
       <c r="E165" s="27">
         <f>IF(E157=1,E159*DSO/DaysYr+E159*COGSR*DIO/DaysYr-E159*COGSR*DPO/DaysYr,D165)</f>
-        <v>63075.251366613316</v>
+        <v>113137.71500830463</v>
       </c>
       <c r="F165" s="27">
         <f>IF(F157=1,F159*DSO/DaysYr+F159*COGSR*DIO/DaysYr-F159*COGSR*DPO/DaysYr,E165)</f>
-        <v>66476.76982112962</v>
+        <v>119238.9990644829</v>
       </c>
       <c r="G165" s="27">
         <f>IF(G157=1,G159*DSO/DaysYr+G159*COGSR*DIO/DaysYr-G159*COGSR*DPO/DaysYr,F165)</f>
-        <v>68934.01519040806</v>
+        <v>123646.54592749951</v>
       </c>
       <c r="H165" s="27">
         <f>IF(H157=1,H159*DSO/DaysYr+H159*COGSR*DIO/DaysYr-H159*COGSR*DPO/DaysYr,G165)</f>
-        <v>70312.69549421623</v>
+        <v>126119.47684604951</v>
       </c>
       <c r="I165" s="27">
         <f>IF(I157=1,I159*DSO/DaysYr+I159*COGSR*DIO/DaysYr-I159*COGSR*DPO/DaysYr,H165)</f>
-        <v>71718.94940410057</v>
+        <v>128641.8663829705</v>
       </c>
       <c r="J165" s="27">
         <f>IF(J157=1,J159*DSO/DaysYr+J159*COGSR*DIO/DaysYr-J159*COGSR*DPO/DaysYr,I165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
       <c r="K165" s="27">
         <f>IF(K157=1,K159*DSO/DaysYr+K159*COGSR*DIO/DaysYr-K159*COGSR*DPO/DaysYr,J165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
       <c r="L165" s="27">
         <f>IF(L157=1,L159*DSO/DaysYr+L159*COGSR*DIO/DaysYr-L159*COGSR*DPO/DaysYr,K165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
       <c r="M165" s="27">
         <f>IF(M157=1,M159*DSO/DaysYr+M159*COGSR*DIO/DaysYr-M159*COGSR*DPO/DaysYr,L165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
       <c r="N165" s="27">
         <f>IF(N157=1,N159*DSO/DaysYr+N159*COGSR*DIO/DaysYr-N159*COGSR*DPO/DaysYr,M165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
       <c r="O165" s="27">
         <f>IF(O157=1,O159*DSO/DaysYr+O159*COGSR*DIO/DaysYr-O159*COGSR*DPO/DaysYr,N165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
       <c r="P165" s="27">
         <f>IF(P157=1,P159*DSO/DaysYr+P159*COGSR*DIO/DaysYr-P159*COGSR*DPO/DaysYr,O165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
       <c r="Q165" s="27">
         <f>IF(Q157=1,Q159*DSO/DaysYr+Q159*COGSR*DIO/DaysYr-Q159*COGSR*DPO/DaysYr,P165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
       <c r="R165" s="27">
         <f>IF(R157=1,R159*DSO/DaysYr+R159*COGSR*DIO/DaysYr-R159*COGSR*DPO/DaysYr,Q165)</f>
-        <v>73153.32839218256</v>
+        <v>131214.70371062992</v>
       </c>
     </row>
     <row r="166" spans="1:18">
@@ -13695,31 +13695,31 @@
       </c>
       <c r="D166" s="40">
         <f>IF(D157=1,D165-C165,0)</f>
-        <v>-685.2663245187432</v>
+        <v>10526.213070909653</v>
       </c>
       <c r="E166" s="40">
         <f>IF(E157=1,E165-D165,0)</f>
-        <v>4175.5149311320565</v>
+        <v>7489.597077394967</v>
       </c>
       <c r="F166" s="40">
         <f>IF(F157=1,F165-E165,0)</f>
-        <v>3401.5184545163065</v>
+        <v>6101.284056178265</v>
       </c>
       <c r="G166" s="40">
         <f>IF(G157=1,G165-F165,0)</f>
-        <v>2457.245369278433</v>
+        <v>4407.546863016614</v>
       </c>
       <c r="H166" s="40">
         <f>IF(H157=1,H165-G165,0)</f>
-        <v>1378.6803038081707</v>
+        <v>2472.9309185500024</v>
       </c>
       <c r="I166" s="40">
         <f>IF(I157=1,I165-H165,0)</f>
-        <v>1406.2539098843408</v>
+        <v>2522.389536920993</v>
       </c>
       <c r="J166" s="40">
         <f>IF(J157=1,J165-I165,0)</f>
-        <v>1434.3789880819968</v>
+        <v>2572.837327659421</v>
       </c>
       <c r="K166" s="40">
         <f>IF(K157=1,K165-J165,0)</f>
@@ -13967,31 +13967,31 @@
       </c>
       <c r="D170" s="40">
         <f>D169+D163-D164-D166</f>
-        <v>2190.2856995021302</v>
+        <v>-9021.193695926266</v>
       </c>
       <c r="E170" s="40">
         <f>E169+E163-E164-E166</f>
-        <v>1066.9262330523525</v>
+        <v>-2247.1559132105576</v>
       </c>
       <c r="F170" s="40">
         <f>F169+F163-F164-F166</f>
-        <v>4133.507100230527</v>
+        <v>1433.7414985685682</v>
       </c>
       <c r="G170" s="40">
         <f>G169+G163-G164-G166</f>
-        <v>7449.2260690447</v>
+        <v>5498.924575306519</v>
       </c>
       <c r="H170" s="40">
         <f>H169+H163-H164-H166</f>
-        <v>10868.879313260302</v>
+        <v>9774.62869851847</v>
       </c>
       <c r="I170" s="40">
         <f>I169+I163-I164-I166</f>
-        <v>13272.25962450396</v>
+        <v>12156.123997467308</v>
       </c>
       <c r="J170" s="40">
         <f>J169+J163-J164-J166</f>
-        <v>15767.612396472105</v>
+        <v>14629.15405689468</v>
       </c>
       <c r="K170" s="40">
         <f>K169+K163-K164-K166</f>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="C177" s="40">
         <f>SUMPRODUCT(($D$151:$R$151&gt;1)*$D$157:$R$157*($D$164:$R$164-$D$163:$R$163+$D$166:$R$166))</f>
-        <v>111920.75779566335</v>
+        <v>123233.75161868229</v>
       </c>
     </row>
     <row r="178" spans="1:18">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="C178" s="31">
         <f>IF(C177&gt;0,(C176-C174)/C177,0)</f>
-        <v>0.15586138258674753</v>
+        <v>0.14155313638560083</v>
       </c>
     </row>
     <row r="179" spans="1:18">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="C184" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_1)+WD*Kd_Pre*(1-C179)</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
     </row>
     <row r="185" spans="1:18">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="C185" s="30">
         <f>IF(C177&lt;=0,C184,IF(C178&lt;C184,C184,IF(C178&gt;RonicCap,MAX(RonicCap,C184),C178)))</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
     </row>
     <row r="186" spans="1:18">
@@ -14173,63 +14173,63 @@
       </c>
       <c r="D186" s="40">
         <f>D170-IF(D157=1,0,D169*D158/C185)</f>
-        <v>2190.2856995021302</v>
+        <v>-9021.193695926266</v>
       </c>
       <c r="E186" s="40">
         <f>E170-IF(E157=1,0,E169*E158/C185)</f>
-        <v>1066.9262330523525</v>
+        <v>-2247.1559132105576</v>
       </c>
       <c r="F186" s="40">
         <f>F170-IF(F157=1,0,F169*F158/C185)</f>
-        <v>4133.507100230527</v>
+        <v>1433.7414985685682</v>
       </c>
       <c r="G186" s="40">
         <f>G170-IF(G157=1,0,G169*G158/C185)</f>
-        <v>7449.2260690447</v>
+        <v>5498.924575306519</v>
       </c>
       <c r="H186" s="40">
         <f>H170-IF(H157=1,0,H169*H158/C185)</f>
-        <v>10868.879313260302</v>
+        <v>9774.62869851847</v>
       </c>
       <c r="I186" s="40">
         <f>I170-IF(I157=1,0,I169*I158/C185)</f>
-        <v>13272.25962450396</v>
+        <v>12156.123997467308</v>
       </c>
       <c r="J186" s="40">
         <f>J170-IF(J157=1,0,J169*J158/C185)</f>
-        <v>15767.612396472105</v>
+        <v>14629.15405689468</v>
       </c>
       <c r="K186" s="40">
         <f>K170-IF(K157=1,0,K169*K158/C185)</f>
-        <v>29282.049091359302</v>
+        <v>29243.095398278725</v>
       </c>
       <c r="L186" s="40">
         <f>L170-IF(L157=1,0,L169*L158/C185)</f>
-        <v>29859.993394298886</v>
+        <v>29820.270866191633</v>
       </c>
       <c r="M186" s="40">
         <f>M170-IF(M157=1,0,M169*M158/C185)</f>
-        <v>30449.496583297267</v>
+        <v>30408.9898434628</v>
       </c>
       <c r="N186" s="40">
         <f>N170-IF(N157=1,0,N169*N158/C185)</f>
-        <v>31050.789836075615</v>
+        <v>31009.483200279392</v>
       </c>
       <c r="O186" s="40">
         <f>O170-IF(O157=1,0,O169*O158/C185)</f>
-        <v>31664.108953909534</v>
+        <v>31621.986424232324</v>
       </c>
       <c r="P186" s="40">
         <f>P170-IF(P157=1,0,P169*P158/C185)</f>
-        <v>32289.69445410013</v>
+        <v>32246.739712664305</v>
       </c>
       <c r="Q186" s="40">
         <f>Q170-IF(Q157=1,0,Q169*Q158/C185)</f>
-        <v>32927.791664294535</v>
+        <v>32883.98806686493</v>
       </c>
       <c r="R186" s="40">
         <f>R170-IF(R157=1,0,R169*R158/C185)</f>
-        <v>33578.650818692826</v>
+        <v>33533.98138814956</v>
       </c>
     </row>
     <row r="187" spans="1:18">
@@ -14238,63 +14238,63 @@
       </c>
       <c r="D187" s="27">
         <f>D186*(1+C184)^(-DCF!D10)</f>
-        <v>2128.728971372657</v>
+        <v>-8769.216392047445</v>
       </c>
       <c r="E187" s="27">
         <f>E186*(1+C184)^(-DCF!E10)</f>
-        <v>952.3896355108511</v>
+        <v>-2007.3399079216247</v>
       </c>
       <c r="F187" s="27">
         <f>F186*(1+C184)^(-DCF!F10)</f>
-        <v>3294.6841873666435</v>
+        <v>1144.405700458016</v>
       </c>
       <c r="G187" s="27">
         <f>G186*(1+C184)^(-DCF!G10)</f>
-        <v>5301.772578411029</v>
+        <v>3922.0069883329056</v>
       </c>
       <c r="H187" s="27">
         <f>H186*(1+C184)^(-DCF!H10)</f>
-        <v>6908.38969803207</v>
+        <v>6230.446605608174</v>
       </c>
       <c r="I187" s="27">
         <f>I186*(1+C184)^(-DCF!I10)</f>
-        <v>7533.886120665337</v>
+        <v>6924.721949934769</v>
       </c>
       <c r="J187" s="27">
         <f>J186*(1+C184)^(-DCF!J10)</f>
-        <v>7991.99042275783</v>
+        <v>7446.425955793905</v>
       </c>
       <c r="K187" s="27">
         <f>K186*(1+C184)^(-DCF!K10)</f>
-        <v>13252.72908921151</v>
+        <v>13300.667804265164</v>
       </c>
       <c r="L187" s="27">
         <f>L186*(1+C184)^(-DCF!L10)</f>
-        <v>12069.12219861524</v>
+        <v>12121.322288063464</v>
       </c>
       <c r="M187" s="27">
         <f>M186*(1+C184)^(-DCF!M10)</f>
-        <v>10991.278579290936</v>
+        <v>11046.602259628846</v>
       </c>
       <c r="N187" s="27">
         <f>N186*(1+C184)^(-DCF!N10)</f>
-        <v>10008.191041915054</v>
+        <v>10065.67017773303</v>
       </c>
       <c r="O187" s="27">
         <f>O186*(1+C184)^(-DCF!O10)</f>
-        <v>9113.077063695715</v>
+        <v>9171.888339436011</v>
       </c>
       <c r="P187" s="27">
         <f>P186*(1+C184)^(-DCF!P10)</f>
-        <v>8299.34519116367</v>
+        <v>8358.796113497363</v>
       </c>
       <c r="Q187" s="27">
         <f>Q186*(1+C184)^(-DCF!Q10)</f>
-        <v>7558.308594399197</v>
+        <v>7617.820076368543</v>
       </c>
       <c r="R187" s="27">
         <f>R186*(1+C184)^(-DCF!R10)</f>
-        <v>6882.402903562132</v>
+        <v>6941.49142711922</v>
       </c>
     </row>
     <row r="188" spans="1:18">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C188" s="27">
         <f>C181*(1-GTermCfg/C185)/(C184-GTermCfg)*IF(MidYear=1,(1+C184)^0.5,1)</f>
-        <v>363285.1805175724</v>
+        <v>365566.42948573176</v>
       </c>
     </row>
     <row r="189" spans="1:18">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="C189" s="27">
         <f>C188*(1+C184)^(-DCF!R9)</f>
-        <v>70355.54129996966</v>
+        <v>71525.56034233577</v>
       </c>
     </row>
     <row r="190" spans="1:18">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C190" s="40">
         <f>SUM(D187:R187)+C189</f>
-        <v>182641.83757593954</v>
+        <v>165041.2697286061</v>
       </c>
     </row>
     <row r="191" spans="1:18">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="C191" s="27">
         <f>C190*(1+C184)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>187923.31497016127</v>
+        <v>169783.61526049025</v>
       </c>
     </row>
     <row r="192" spans="1:18">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C192" s="27">
         <f>C191+BridgeAdj</f>
-        <v>258903.36323016128</v>
+        <v>235763.66352049026</v>
       </c>
     </row>
     <row r="193" spans="1:18">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C193" s="56">
         <f>C192*MnToWon/Shares</f>
-        <v>8801.431083570636</v>
+        <v>8014.795986412259</v>
       </c>
     </row>
     <row r="194" spans="1:18">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="C194" s="29">
         <f>C189/C190</f>
-        <v>0.38521043279975187</v>
+        <v>0.43337984771901245</v>
       </c>
     </row>
     <row r="196" spans="1:18">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="C197" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_2)+WD*Kd_Pre*(1-C179)</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
     </row>
     <row r="198" spans="1:18">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="C198" s="30">
         <f>IF(C177&lt;=0,C197,IF(C178&lt;C197,C197,IF(C178&gt;RonicCap,MAX(RonicCap,C197),C178)))</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
     </row>
     <row r="199" spans="1:18">
@@ -14411,63 +14411,63 @@
       </c>
       <c r="D199" s="40">
         <f>D170-IF(D157=1,0,D169*D158/C198)</f>
-        <v>2190.2856995021302</v>
+        <v>-9021.193695926266</v>
       </c>
       <c r="E199" s="40">
         <f>E170-IF(E157=1,0,E169*E158/C198)</f>
-        <v>1066.9262330523525</v>
+        <v>-2247.1559132105576</v>
       </c>
       <c r="F199" s="40">
         <f>F170-IF(F157=1,0,F169*F158/C198)</f>
-        <v>4133.507100230527</v>
+        <v>1433.7414985685682</v>
       </c>
       <c r="G199" s="40">
         <f>G170-IF(G157=1,0,G169*G158/C198)</f>
-        <v>7449.2260690447</v>
+        <v>5498.924575306519</v>
       </c>
       <c r="H199" s="40">
         <f>H170-IF(H157=1,0,H169*H158/C198)</f>
-        <v>10868.879313260302</v>
+        <v>9774.62869851847</v>
       </c>
       <c r="I199" s="40">
         <f>I170-IF(I157=1,0,I169*I158/C198)</f>
-        <v>13272.25962450396</v>
+        <v>12156.123997467308</v>
       </c>
       <c r="J199" s="40">
         <f>J170-IF(J157=1,0,J169*J158/C198)</f>
-        <v>15767.612396472105</v>
+        <v>14629.15405689468</v>
       </c>
       <c r="K199" s="40">
         <f>K170-IF(K157=1,0,K169*K158/C198)</f>
-        <v>29729.784327168054</v>
+        <v>29690.021976038253</v>
       </c>
       <c r="L199" s="40">
         <f>L170-IF(L157=1,0,L169*L158/C198)</f>
-        <v>30316.565649264106</v>
+        <v>30276.01850249944</v>
       </c>
       <c r="M199" s="40">
         <f>M170-IF(M157=1,0,M169*M158/C198)</f>
-        <v>30915.082597802084</v>
+        <v>30873.734959489848</v>
       </c>
       <c r="N199" s="40">
         <f>N170-IF(N157=1,0,N169*N158/C198)</f>
-        <v>31525.569885310822</v>
+        <v>31483.405745620068</v>
       </c>
       <c r="O199" s="40">
         <f>O170-IF(O157=1,0,O169*O158/C198)</f>
-        <v>32148.266918569738</v>
+        <v>32105.269947472898</v>
       </c>
       <c r="P199" s="40">
         <f>P170-IF(P157=1,0,P169*P158/C198)</f>
-        <v>32783.41789249383</v>
+        <v>32739.571433362777</v>
       </c>
       <c r="Q199" s="40">
         <f>Q170-IF(Q157=1,0,Q169*Q158/C198)</f>
-        <v>33431.2718858964</v>
+        <v>33386.55894897046</v>
       </c>
       <c r="R199" s="40">
         <f>R170-IF(R157=1,0,R169*R158/C198)</f>
-        <v>34092.082959167026</v>
+        <v>34046.48621489029</v>
       </c>
     </row>
     <row r="200" spans="1:18">
@@ -14476,63 +14476,63 @@
       </c>
       <c r="D200" s="27">
         <f>D199*(1+C197)^(-DCF!D10)</f>
-        <v>2124.0184719174604</v>
+        <v>-8750.099378784249</v>
       </c>
       <c r="E200" s="27">
         <f>E199*(1+C197)^(-DCF!E10)</f>
-        <v>944.0217941040183</v>
+        <v>-1989.9637549604101</v>
       </c>
       <c r="F200" s="27">
         <f>F199*(1+C197)^(-DCF!F10)</f>
-        <v>3237.1212701963445</v>
+        <v>1124.7054753033647</v>
       </c>
       <c r="G200" s="27">
         <f>G199*(1+C197)^(-DCF!G10)</f>
-        <v>5163.498914624566</v>
+        <v>3821.217074923697</v>
       </c>
       <c r="H200" s="27">
         <f>H199*(1+C197)^(-DCF!H10)</f>
-        <v>6669.340177977509</v>
+        <v>6018.000586183052</v>
       </c>
       <c r="I200" s="27">
         <f>I199*(1+C197)^(-DCF!I10)</f>
-        <v>7209.549690451898</v>
+        <v>6630.939838213882</v>
       </c>
       <c r="J200" s="27">
         <f>J199*(1+C197)^(-DCF!J10)</f>
-        <v>7580.919074128013</v>
+        <v>7068.954281392051</v>
       </c>
       <c r="K200" s="27">
         <f>K199*(1+C197)^(-DCF!K10)</f>
-        <v>12651.451005795554</v>
+        <v>12708.739324392485</v>
       </c>
       <c r="L200" s="27">
         <f>L199*(1+C197)^(-DCF!L10)</f>
-        <v>11420.726953500453</v>
+        <v>11482.031244951351</v>
       </c>
       <c r="M200" s="27">
         <f>M199*(1+C197)^(-DCF!M10)</f>
-        <v>10309.77828642571</v>
+        <v>10373.782628981904</v>
       </c>
       <c r="N200" s="27">
         <f>N199*(1+C197)^(-DCF!N10)</f>
-        <v>9305.388611598175</v>
+        <v>9370.99425640983</v>
       </c>
       <c r="O200" s="27">
         <f>O199*(1+C197)^(-DCF!O10)</f>
-        <v>8398.887972511144</v>
+        <v>8465.181700063154</v>
       </c>
       <c r="P200" s="27">
         <f>P199*(1+C197)^(-DCF!P10)</f>
-        <v>7581.997212037441</v>
+        <v>7648.230327545821</v>
       </c>
       <c r="Q200" s="27">
         <f>Q199*(1+C197)^(-DCF!Q10)</f>
-        <v>6844.590306482012</v>
+        <v>6910.152593625324</v>
       </c>
       <c r="R200" s="27">
         <f>R199*(1+C197)^(-DCF!R10)</f>
-        <v>6177.898220170926</v>
+        <v>6242.294701776512</v>
       </c>
     </row>
     <row r="201" spans="1:18">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C201" s="27">
         <f>C181*(1-GTermCfg/C198)/(C197-GTermCfg)*IF(MidYear=1,(1+C197)^0.5,1)</f>
-        <v>337060.9021935298</v>
+        <v>339390.1027915957</v>
       </c>
     </row>
     <row r="202" spans="1:18">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="C202" s="27">
         <f>C201*(1+C197)^(-DCF!R9)</f>
-        <v>57458.68225868906</v>
+        <v>58561.62683680776</v>
       </c>
     </row>
     <row r="203" spans="1:18">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="C203" s="40">
         <f>SUM(D200:R200)+C202</f>
-        <v>163077.8702206103</v>
+        <v>145686.78773682553</v>
       </c>
     </row>
     <row r="204" spans="1:18">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="C204" s="27">
         <f>C203*(1+C197)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>168165.73479561871</v>
+        <v>150200.43478566807</v>
       </c>
     </row>
     <row r="205" spans="1:18">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="C205" s="27">
         <f>C204+BridgeAdj</f>
-        <v>239145.78305561873</v>
+        <v>216180.48304566808</v>
       </c>
     </row>
     <row r="206" spans="1:18">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="C206" s="56">
         <f>C205*MnToWon/Shares</f>
-        <v>8129.7712869778525</v>
+        <v>7349.064915189951</v>
       </c>
     </row>
     <row r="207" spans="1:18">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="C207" s="29">
         <f>C202/C203</f>
-        <v>0.3523389297454</v>
+        <v>0.4019693737952122</v>
       </c>
     </row>
     <row r="209" spans="1:18">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="C210" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_3)+WD*Kd_Pre*(1-C179)</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="211" spans="1:18">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="C211" s="30">
         <f>IF(C177&lt;=0,C210,IF(C178&lt;C210,C210,IF(C178&gt;RonicCap,MAX(RonicCap,C210),C178)))</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
     <row r="212" spans="1:18">
@@ -14649,63 +14649,63 @@
       </c>
       <c r="D212" s="40">
         <f>D170-IF(D157=1,0,D169*D158/C211)</f>
-        <v>2190.2856995021302</v>
+        <v>-9021.193695926266</v>
       </c>
       <c r="E212" s="40">
         <f>E170-IF(E157=1,0,E169*E158/C211)</f>
-        <v>1066.9262330523525</v>
+        <v>-2247.1559132105576</v>
       </c>
       <c r="F212" s="40">
         <f>F170-IF(F157=1,0,F169*F158/C211)</f>
-        <v>4133.507100230527</v>
+        <v>1433.7414985685682</v>
       </c>
       <c r="G212" s="40">
         <f>G170-IF(G157=1,0,G169*G158/C211)</f>
-        <v>7449.2260690447</v>
+        <v>5498.924575306519</v>
       </c>
       <c r="H212" s="40">
         <f>H170-IF(H157=1,0,H169*H158/C211)</f>
-        <v>10868.879313260302</v>
+        <v>9774.62869851847</v>
       </c>
       <c r="I212" s="40">
         <f>I170-IF(I157=1,0,I169*I158/C211)</f>
-        <v>13272.25962450396</v>
+        <v>12156.123997467308</v>
       </c>
       <c r="J212" s="40">
         <f>J170-IF(J157=1,0,J169*J158/C211)</f>
-        <v>15767.612396472105</v>
+        <v>14629.15405689468</v>
       </c>
       <c r="K212" s="40">
         <f>K170-IF(K157=1,0,K169*K158/C211)</f>
-        <v>30114.073734960046</v>
+        <v>30074.111003137332</v>
       </c>
       <c r="L212" s="40">
         <f>L170-IF(L157=1,0,L169*L158/C211)</f>
-        <v>30708.439836154736</v>
+        <v>30667.688353752623</v>
       </c>
       <c r="M212" s="40">
         <f>M170-IF(M157=1,0,M169*M158/C211)</f>
-        <v>31314.69325937332</v>
+        <v>31273.13725138022</v>
       </c>
       <c r="N212" s="40">
         <f>N170-IF(N157=1,0,N169*N158/C211)</f>
-        <v>31933.071751056286</v>
+        <v>31890.695126960374</v>
       </c>
       <c r="O212" s="40">
         <f>O170-IF(O157=1,0,O169*O158/C211)</f>
-        <v>32563.81781257291</v>
+        <v>32520.60416005213</v>
       </c>
       <c r="P212" s="40">
         <f>P170-IF(P157=1,0,P169*P158/C211)</f>
-        <v>33207.178795319865</v>
+        <v>33163.111373805725</v>
       </c>
       <c r="Q212" s="40">
         <f>Q170-IF(Q157=1,0,Q169*Q158/C211)</f>
-        <v>33863.40699772175</v>
+        <v>33818.468731834386</v>
       </c>
       <c r="R212" s="40">
         <f>R170-IF(R157=1,0,R169*R158/C211)</f>
-        <v>34532.75976417168</v>
+        <v>34486.93323702362</v>
       </c>
     </row>
     <row r="213" spans="1:18">
@@ -14714,63 +14714,63 @@
       </c>
       <c r="D213" s="27">
         <f>D212*(1+C210)^(-DCF!D10)</f>
-        <v>2119.359299698249</v>
+        <v>-8731.187609114808</v>
       </c>
       <c r="E213" s="27">
         <f>E212*(1+C210)^(-DCF!E10)</f>
-        <v>935.799421186854</v>
+        <v>-1972.8852470936486</v>
       </c>
       <c r="F213" s="27">
         <f>F212*(1+C210)^(-DCF!F10)</f>
-        <v>3181.0525143983705</v>
+        <v>1105.5091489745878</v>
       </c>
       <c r="G213" s="27">
         <f>G212*(1+C210)^(-DCF!G10)</f>
-        <v>5029.989485068939</v>
+        <v>3723.8494444468424</v>
       </c>
       <c r="H213" s="27">
         <f>H212*(1+C210)^(-DCF!H10)</f>
-        <v>6440.538160464656</v>
+        <v>5814.529921040547</v>
       </c>
       <c r="I213" s="27">
         <f>I212*(1+C210)^(-DCF!I10)</f>
-        <v>6901.821586487482</v>
+        <v>6351.984815199088</v>
       </c>
       <c r="J213" s="27">
         <f>J212*(1+C210)^(-DCF!J10)</f>
-        <v>7194.300391466639</v>
+        <v>6713.6146392136</v>
       </c>
       <c r="K213" s="27">
         <f>K212*(1+C210)^(-DCF!K10)</f>
-        <v>12055.796635074461</v>
+        <v>12121.402152633133</v>
       </c>
       <c r="L213" s="27">
         <f>L212*(1+C210)^(-DCF!L10)</f>
-        <v>10788.613253675243</v>
+        <v>10857.781363164273</v>
       </c>
       <c r="M213" s="27">
         <f>M212*(1+C210)^(-DCF!M10)</f>
-        <v>9654.671536555574</v>
+        <v>9725.937874284331</v>
       </c>
       <c r="N213" s="27">
         <f>N212*(1+C210)^(-DCF!N10)</f>
-        <v>8638.40994281149</v>
+        <v>8710.576353138546</v>
       </c>
       <c r="O213" s="27">
         <f>O212*(1+C210)^(-DCF!O10)</f>
-        <v>7729.1582884338595</v>
+        <v>7801.253265558338</v>
       </c>
       <c r="P213" s="27">
         <f>P212*(1+C210)^(-DCF!P10)</f>
-        <v>6916.881482460377</v>
+        <v>6988.1308899974065</v>
       </c>
       <c r="Q213" s="27">
         <f>Q212*(1+C210)^(-DCF!Q10)</f>
-        <v>6189.997487606997</v>
+        <v>6259.788933004187</v>
       </c>
       <c r="R213" s="27">
         <f>R212*(1+C210)^(-DCF!R10)</f>
-        <v>5538.534709867344</v>
+        <v>5606.388546821556</v>
       </c>
     </row>
     <row r="214" spans="1:18">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C214" s="27">
         <f>C181*(1-GTermCfg/C211)/(C210-GTermCfg)*IF(MidYear=1,(1+C210)^0.5,1)</f>
-        <v>314546.7112443123</v>
+        <v>316888.28564831446</v>
       </c>
     </row>
     <row r="215" spans="1:18">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="C215" s="27">
         <f>C214*(1+C210)^(-DCF!R9)</f>
-        <v>47251.08450291616</v>
+        <v>48273.37607810338</v>
       </c>
     </row>
     <row r="216" spans="1:18">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="C216" s="40">
         <f>SUM(D213:R213)+C215</f>
-        <v>146566.0086981727</v>
+        <v>129350.05056937136</v>
       </c>
     </row>
     <row r="217" spans="1:18">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="C217" s="27">
         <f>C216*(1+C210)^((ValDate-DiscDate)/DaysYr)</f>
-        <v>151470.98131516395</v>
+        <v>133646.40791202278</v>
       </c>
     </row>
     <row r="218" spans="1:18">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="C218" s="27">
         <f>C217+BridgeAdj</f>
-        <v>222451.02957516396</v>
+        <v>199626.4561720228</v>
       </c>
     </row>
     <row r="219" spans="1:18">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="C219" s="56">
         <f>C218*MnToWon/Shares</f>
-        <v>7562.232416944719</v>
+        <v>6786.310052270534</v>
       </c>
     </row>
     <row r="220" spans="1:18">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="C220" s="29">
         <f>C215/C216</f>
-        <v>0.3223877413501897</v>
+        <v>0.373199514539146</v>
       </c>
     </row>
   </sheetData>
@@ -14919,15 +14919,15 @@
       </c>
       <c r="C5" s="57">
         <f>MIN(Scenarios!$B$6:$D$6)</f>
-        <v>4628.393636578313</v>
+        <v>3982.276759282653</v>
       </c>
       <c r="D5" s="57">
         <f>MAX(Scenarios!$B$6:$D$6)</f>
-        <v>5345.077547961856</v>
+        <v>4691.380095525618</v>
       </c>
       <c r="E5" s="57">
         <f>Scenarios!$B$6</f>
-        <v>5345.077547961856</v>
+        <v>4691.380095525618</v>
       </c>
       <c r="F5" s="35">
         <f>ROWS(B5:$B$13)</f>
@@ -14950,15 +14950,15 @@
       </c>
       <c r="C6" s="57">
         <f>MIN(Scenarios!$B$7:$D$7)</f>
-        <v>6035.580005626037</v>
+        <v>5325.210821879023</v>
       </c>
       <c r="D6" s="57">
         <f>MAX(Scenarios!$B$7:$D$7)</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="E6" s="57">
         <f>Scenarios!$B$7</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="F6" s="35">
         <f>ROWS(B6:$B$13)</f>
@@ -14981,15 +14981,15 @@
       </c>
       <c r="C7" s="57">
         <f>MIN(Scenarios!$B$8:$D$8)</f>
-        <v>7562.232416944719</v>
+        <v>6786.310052270534</v>
       </c>
       <c r="D7" s="57">
         <f>MAX(Scenarios!$B$8:$D$8)</f>
-        <v>8801.431083570636</v>
+        <v>8014.795986412259</v>
       </c>
       <c r="E7" s="57">
         <f>Scenarios!$B$8</f>
-        <v>8801.431083570636</v>
+        <v>8014.795986412259</v>
       </c>
       <c r="F7" s="35">
         <f>ROWS(B7:$B$13)</f>
@@ -15013,15 +15013,15 @@
       </c>
       <c r="C8" s="57">
         <f>Peers!$H$15</f>
-        <v>5260.596670699279</v>
+        <v>5090.621453425907</v>
       </c>
       <c r="D8" s="57">
         <f>Peers!$J$15</f>
-        <v>7286.707794228766</v>
+        <v>7116.732576955395</v>
       </c>
       <c r="E8" s="57">
         <f>Peers!$I$15</f>
-        <v>6561.230037235493</v>
+        <v>6391.2548199621215</v>
       </c>
       <c r="F8" s="35">
         <f>ROWS(B8:$B$13)</f>
@@ -15077,15 +15077,15 @@
       </c>
       <c r="C10" s="57">
         <f>Peers!$H$17</f>
-        <v>10755.750497574374</v>
+        <v>10585.775280301003</v>
       </c>
       <c r="D10" s="57">
         <f>Peers!$J$17</f>
-        <v>17067.37314657971</v>
+        <v>16897.39792930634</v>
       </c>
       <c r="E10" s="57">
         <f>Peers!$I$17</f>
-        <v>12826.06021530625</v>
+        <v>12656.084998032879</v>
       </c>
       <c r="F10" s="35">
         <f>ROWS(B10:$B$13)</f>
@@ -15284,13 +15284,13 @@
         <v>768</v>
       </c>
       <c r="B7" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="C7" s="58">
-        <v>5260.596670699277</v>
+        <v>5090.621453425906</v>
       </c>
       <c r="D7" s="58">
-        <v>7286.707794228767</v>
+        <v>7116.732576955396</v>
       </c>
       <c r="E7" s="19">
         <v>8</v>
@@ -15307,13 +15307,13 @@
         <v>771</v>
       </c>
       <c r="B8" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="C8" s="58">
-        <v>5260.596670699277</v>
+        <v>5090.621453425906</v>
       </c>
       <c r="D8" s="58">
-        <v>7286.707794228767</v>
+        <v>7116.732576955396</v>
       </c>
       <c r="E8" s="19">
         <v>8</v>
@@ -15330,10 +15330,10 @@
         <v>773</v>
       </c>
       <c r="C9" s="58">
-        <v>5260.596670699277</v>
+        <v>5090.621453425906</v>
       </c>
       <c r="D9" s="58">
-        <v>7286.707794228767</v>
+        <v>7116.732576955396</v>
       </c>
       <c r="E9" s="19">
         <v>8</v>
@@ -15370,15 +15370,15 @@
       </c>
       <c r="B13" s="57">
         <f>INDEX(ScenGridPS,MATCH("기본",ScenNames,0),1)</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="C13" s="57">
         <f>Peers!$H$15</f>
-        <v>5260.596670699279</v>
+        <v>5090.621453425907</v>
       </c>
       <c r="D13" s="57">
         <f>Peers!$J$15</f>
-        <v>7286.707794228766</v>
+        <v>7116.732576955395</v>
       </c>
       <c r="E13" s="34">
         <f>Peers!$C$15</f>
@@ -15395,15 +15395,15 @@
       </c>
       <c r="B14" s="57">
         <f>INDEX(ScenGridPS,MATCH("기본",ScenNames,0),1)</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="C14" s="57">
         <f>Peers!$H$16</f>
-        <v>5260.596670699279</v>
+        <v>5090.621453425907</v>
       </c>
       <c r="D14" s="57">
         <f>Peers!$J$16</f>
-        <v>7286.707794228766</v>
+        <v>7116.732576955395</v>
       </c>
       <c r="E14" s="34">
         <f>Peers!$C$16</f>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="B17" s="28">
         <f>Convergence!$B$13/Close-1</f>
-        <v>-0.6498667765749739</v>
+        <v>-0.6858403182870311</v>
       </c>
     </row>
   </sheetData>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="D6" s="5">
         <f>Equity</f>
-        <v>205990.74914662816</v>
+        <v>184826.75695463648</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>786</v>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="D7" s="5">
         <f>NetDebt</f>
-        <v>-59146.183334</v>
+        <v>-54146.183334</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>786</v>
@@ -15550,11 +15550,11 @@
       </c>
       <c r="D8" s="5">
         <f>PerShare*Shares/MnToWon-BridgeAdj</f>
-        <v>135010.70088662815</v>
+        <v>118846.70869463647</v>
       </c>
       <c r="E8" s="5">
         <f>EV_930</f>
-        <v>135010.70088662815</v>
+        <v>118846.70869463647</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>786</v>
@@ -15573,11 +15573,11 @@
       </c>
       <c r="D9" s="5">
         <f>ScenSelPS</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="E9" s="5">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>786</v>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="D10" s="5">
         <f>MIN(Scenarios!$B$12:$D$14)</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="E10" s="5">
         <f>MAX(GTermCfg)</f>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="D36" s="5">
         <f>RONIC</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>829</v>
@@ -16235,11 +16235,11 @@
       </c>
       <c r="D38" s="5">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="E38" s="5">
         <f>INDEX(Scenarios!$B$32:$D$34,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>844</v>
@@ -16261,11 +16261,11 @@
       </c>
       <c r="D39" s="5">
         <f>WACC</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="E39" s="5">
         <f>INDEX(Scenarios!$B$37:$D$39,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>0.119741768913095</v>
+        <v>0.118952603223987</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>844</v>
@@ -16287,11 +16287,11 @@
       </c>
       <c r="D40" s="5">
         <f>RONIC</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="E40" s="5">
         <f>INDEX(Scenarios!$B$42:$D$44,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>0.119741768913095</v>
+        <v>0.118952603223987</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>844</v>
@@ -16313,11 +16313,11 @@
       </c>
       <c r="D41" s="5">
         <f>TVShare</f>
-        <v>0.4285652185570535</v>
+        <v>0.4948615812826791</v>
       </c>
       <c r="E41" s="5">
         <f>INDEX(Scenarios!$B$47:$D$49,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>0.428565218557055</v>
+        <v>0.494861581282681</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>844</v>
@@ -16339,11 +16339,11 @@
       </c>
       <c r="D42" s="5">
         <f>ImpliedMultiple</f>
-        <v>6.355342936027976</v>
+        <v>6.395251306345912</v>
       </c>
       <c r="E42" s="5">
         <f>INDEX(Scenarios!$B$52:$D$54,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>6.355342936027975</v>
+        <v>6.39525130634591</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>844</v>
@@ -16365,11 +16365,11 @@
       </c>
       <c r="D43" s="5">
         <f>PerShareExit</f>
-        <v>7344.433524163212</v>
+        <v>6615.940270514709</v>
       </c>
       <c r="E43" s="5">
         <f>INDEX(Scenarios!$B$57:$D$59,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>7344.433524163182</v>
+        <v>6615.940270514668</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>844</v>
@@ -16391,11 +16391,11 @@
       </c>
       <c r="D44" s="5">
         <f>EV_930</f>
-        <v>135010.70088662815</v>
+        <v>118846.70869463647</v>
       </c>
       <c r="E44" s="5">
         <f>INDEX(Scenarios!$B$62:$D$64,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>135010.7008866273</v>
+        <v>118846.7086946353</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>844</v>
@@ -16417,11 +16417,11 @@
       </c>
       <c r="D45" s="5">
         <f>ImpliedG_Exit</f>
-        <v>0.03362948443738433</v>
+        <v>0.0330346553356744</v>
       </c>
       <c r="E45" s="5">
         <f>INDEX(Scenarios!$B$67:$D$69,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>0.033629484437384</v>
+        <v>0.033034655335674</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>844</v>
@@ -16443,11 +16443,11 @@
       </c>
       <c r="D46" s="5">
         <f>TVShare_Exit</f>
-        <v>0.46816780666091573</v>
+        <v>0.5332986263853344</v>
       </c>
       <c r="E46" s="5">
         <f>INDEX(Scenarios!$B$72:$D$74,ScenIdx,MATCH(SRP_Sel,SRP_List,0))</f>
-        <v>0.468167806660917</v>
+        <v>0.533298626385336</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>844</v>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="D47" s="5">
         <f>MAX(ABS(MAX(ScenDiff)),ABS(MIN(ScenDiff)))</f>
-        <v>4.18367562815547e-11</v>
+        <v>4.547473508864641e-11</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>245</v>
@@ -16561,11 +16561,11 @@
       </c>
       <c r="D51" s="5">
         <f>Peers!$I$17</f>
-        <v>12826.06021530625</v>
+        <v>12656.084998032879</v>
       </c>
       <c r="E51" s="5">
         <f>Peers!$M$17</f>
-        <v>12826.06021530625</v>
+        <v>12656.08499803288</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>844</v>
@@ -16587,11 +16587,11 @@
       </c>
       <c r="D52" s="5">
         <f>Peers!$I$15</f>
-        <v>6561.230037235493</v>
+        <v>6391.2548199621215</v>
       </c>
       <c r="E52" s="5">
         <f>Peers!$M$15</f>
-        <v>6561.230037235491</v>
+        <v>6391.25481996212</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>844</v>
@@ -16736,11 +16736,11 @@
       </c>
       <c r="D58" s="5">
         <f>Scenarios!$D$91</f>
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="E58" s="5">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>844</v>
@@ -16784,11 +16784,11 @@
       </c>
       <c r="D60" s="5">
         <f>Scenarios!$D$100</f>
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="E60" s="5">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>844</v>
@@ -16832,11 +16832,11 @@
       </c>
       <c r="D62" s="5">
         <f>Scenarios!$B$108</f>
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="E62" s="5">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>844</v>
@@ -16880,11 +16880,11 @@
       </c>
       <c r="D64" s="5">
         <f>Scenarios!$B$121</f>
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="E64" s="5">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>844</v>
@@ -16926,11 +16926,11 @@
       </c>
       <c r="D66" s="5">
         <f>Convergence!$B$13</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="E66" s="5">
         <f>Convergence!$B$8</f>
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>844</v>
@@ -16949,11 +16949,11 @@
       </c>
       <c r="D67" s="5">
         <f>Convergence!$C$13</f>
-        <v>5260.596670699279</v>
+        <v>5090.621453425907</v>
       </c>
       <c r="E67" s="5">
         <f>Convergence!$C$8</f>
-        <v>5260.596670699277</v>
+        <v>5090.621453425906</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>844</v>
@@ -16972,11 +16972,11 @@
       </c>
       <c r="D68" s="5">
         <f>Convergence!$C$14</f>
-        <v>5260.596670699279</v>
+        <v>5090.621453425907</v>
       </c>
       <c r="E68" s="5">
         <f>Convergence!$C$7</f>
-        <v>5260.596670699277</v>
+        <v>5090.621453425906</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>844</v>
@@ -16995,11 +16995,11 @@
       </c>
       <c r="D69" s="5">
         <f>Scenarios!$K$91</f>
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="E69" s="5">
         <f>INDEX(ScenGridPS,MATCH("기본",ScenNames,0),1)</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>844</v>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="B5" s="57">
         <f>INDEX(ScenGridPS,MATCH("기본",ScenNames,0),1)</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -17088,7 +17088,7 @@
         <v>920</v>
       </c>
       <c r="B6" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -17107,7 +17107,7 @@
         <v>923</v>
       </c>
       <c r="B8" s="58">
-        <v>5260.596670699277</v>
+        <v>5090.621453425906</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>924</v>
@@ -17118,7 +17118,7 @@
         <v>925</v>
       </c>
       <c r="B9" s="58">
-        <v>6561.230037235491</v>
+        <v>6391.25481996212</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -17126,7 +17126,7 @@
         <v>926</v>
       </c>
       <c r="B10" s="58">
-        <v>7286.707794228767</v>
+        <v>7116.732576955396</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="B14" s="39">
         <f>DiagDcf/Close</f>
-        <v>0.35013322342502606</v>
+        <v>0.31415968171296893</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -17306,7 +17306,7 @@
         <v>725</v>
       </c>
       <c r="C29" s="58">
-        <v>6561.230037235491</v>
+        <v>6391.25481996212</v>
       </c>
       <c r="D29" s="58" t="s">
         <v>725</v>
@@ -17320,10 +17320,10 @@
         <v>0.05350592826251555</v>
       </c>
       <c r="C30" s="18">
-        <v>0.04799873107724061</v>
+        <v>0.05484556279624331</v>
       </c>
       <c r="D30" s="18">
-        <v>-0.00550719718527494</v>
+        <v>0.001339634533727763</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -17334,10 +17334,10 @@
         <v>0.067855882642325</v>
       </c>
       <c r="C31" s="18">
-        <v>-0.008089723663892892</v>
+        <v>0.1113063272046849</v>
       </c>
       <c r="D31" s="18">
-        <v>-0.0759456063062179</v>
+        <v>0.04345044456235991</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -17345,13 +17345,13 @@
         <v>627</v>
       </c>
       <c r="B32" s="18">
-        <v>0.1197417689130948</v>
+        <v>0.1189526032239875</v>
       </c>
       <c r="C32" s="18">
-        <v>0.1279335819911316</v>
+        <v>0.1171320661224297</v>
       </c>
       <c r="D32" s="18">
-        <v>0.008191813078036791</v>
+        <v>-0.001820537101557843</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -17362,7 +17362,7 @@
         <v>725</v>
       </c>
       <c r="C33" s="58">
-        <v>1.818989403545856E-12</v>
+        <v>2.728484105318785E-12</v>
       </c>
       <c r="D33" s="58" t="s">
         <v>725</v>
@@ -17389,10 +17389,10 @@
         <v>960</v>
       </c>
       <c r="B37" s="62">
-        <v>135010.7008866273</v>
+        <v>118846.7086946353</v>
       </c>
       <c r="C37" s="18">
-        <v>0.6554211849121664</v>
+        <v>0.6430167939580608</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -17400,10 +17400,10 @@
         <v>961</v>
       </c>
       <c r="B38" s="62">
-        <v>57860.89053301859</v>
+        <v>58812.67019486937</v>
       </c>
       <c r="C38" s="18">
-        <v>0.2808907233588064</v>
+        <v>0.3182043074494058</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -17411,10 +17411,10 @@
         <v>962</v>
       </c>
       <c r="B39" s="62">
-        <v>77149.81035360871</v>
+        <v>60034.03849976595</v>
       </c>
       <c r="C39" s="18">
-        <v>0.3745304615533599</v>
+        <v>0.3248124865086551</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -17425,7 +17425,7 @@
         <v>62197.64586300001</v>
       </c>
       <c r="C40" s="18">
-        <v>0.3019438791337507</v>
+        <v>0.3365186236442274</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -17436,7 +17436,7 @@
         <v>12011.071574</v>
       </c>
       <c r="C41" s="18">
-        <v>0.05830879116542432</v>
+        <v>0.06498556687302613</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -17444,10 +17444,10 @@
         <v>965</v>
       </c>
       <c r="B42" s="62">
-        <v>-3051.462529</v>
+        <v>-8051.462528999999</v>
       </c>
       <c r="C42" s="18">
-        <v>-0.01481359013276816</v>
+        <v>-0.04356221286172427</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -17458,7 +17458,7 @@
         <v>-177.206648</v>
       </c>
       <c r="C43" s="18">
-        <v>-0.000860265078573318</v>
+        <v>-0.000958771613589987</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -17466,7 +17466,7 @@
         <v>967</v>
       </c>
       <c r="B44" s="62">
-        <v>205990.7491466273</v>
+        <v>184826.7569546353</v>
       </c>
       <c r="C44" s="18">
         <v>1</v>
@@ -17529,7 +17529,7 @@
         <v>970</v>
       </c>
       <c r="C51" s="63">
-        <v>-0.02082219473938386</v>
+        <v>-0.04715401463368224</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -17540,7 +17540,7 @@
         <v>330</v>
       </c>
       <c r="C52" s="63">
-        <v>0.4285652185570548</v>
+        <v>0.4948615812826809</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -17551,7 +17551,7 @@
         <v>330</v>
       </c>
       <c r="C53" s="63">
-        <v>0.3019438791337507</v>
+        <v>0.3365186236442274</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -17592,7 +17592,7 @@
         <v>0.05350592826251555</v>
       </c>
       <c r="C58" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
       <c r="D58" s="58">
         <v>0</v>
@@ -17606,10 +17606,10 @@
         <v>0.07491254735451337</v>
       </c>
       <c r="C59" s="58">
-        <v>8714.435549679818</v>
+        <v>8005.857484993916</v>
       </c>
       <c r="D59" s="58">
-        <v>1711.771081179326</v>
+        <v>1722.663850734579</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -17620,10 +17620,10 @@
         <v>0.1494934241073008</v>
       </c>
       <c r="C60" s="58">
-        <v>14671.46449579852</v>
+        <v>14000.83562403628</v>
       </c>
       <c r="D60" s="58">
-        <v>7668.80002729803</v>
+        <v>7717.641989776944</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -17667,7 +17667,7 @@
         <v>0.88</v>
       </c>
       <c r="C65" s="58">
-        <v>7002.634552862252</v>
+        <v>6283.163718621097</v>
       </c>
       <c r="D65" s="58">
         <v>-0.02991563824011332</v>
@@ -17695,10 +17695,10 @@
         <v>0.0007007027853948415</v>
       </c>
       <c r="C67" s="58">
-        <v>7003.777608564374</v>
+        <v>6284.810909540782</v>
       </c>
       <c r="D67" s="58">
-        <v>1.113140063880478</v>
+        <v>1.617275281444371</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -17709,10 +17709,10 @@
         <v>1.4577799351609</v>
       </c>
       <c r="C68" s="58">
-        <v>6999.906734557346</v>
+        <v>6280.435900316189</v>
       </c>
       <c r="D68" s="58">
-        <v>-2.757733943147116</v>
+        <v>-2.75773394314789</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -17754,10 +17754,10 @@
         <v>1001</v>
       </c>
       <c r="F72" s="58">
-        <v>7668.80002729803</v>
+        <v>7717.641989776944</v>
       </c>
       <c r="G72" s="18">
-        <v>1.095126014075636</v>
+        <v>1.228299243826615</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -17774,10 +17774,10 @@
         <v>1005</v>
       </c>
       <c r="F73" s="58">
-        <v>-2876.925833883918</v>
+        <v>-2900.261946352231</v>
       </c>
       <c r="G73" s="18">
-        <v>-0.4108330260324418</v>
+        <v>-0.461590413279395</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -17794,10 +17794,10 @@
         <v>1009</v>
       </c>
       <c r="F74" s="58">
-        <v>-2869.861242361436</v>
+        <v>-2821.152503237437</v>
       </c>
       <c r="G74" s="18">
-        <v>-0.4098241826765649</v>
+        <v>-0.4489997710487549</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -17814,10 +17814,10 @@
         <v>1013</v>
       </c>
       <c r="F75" s="58">
-        <v>1798.76661507011</v>
+        <v>2120.076478402026</v>
       </c>
       <c r="G75" s="18">
-        <v>0.2568688851452691</v>
+        <v>0.3374202040889259</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -17834,10 +17834,10 @@
         <v>1017</v>
       </c>
       <c r="F76" s="58">
-        <v>-967.0844628744808</v>
+        <v>1731.602352152876</v>
       </c>
       <c r="G76" s="18">
-        <v>-0.1381023562137865</v>
+        <v>0.2755927085727953</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -17854,10 +17854,10 @@
         <v>1020</v>
       </c>
       <c r="F77" s="58">
-        <v>649.0722288358038</v>
+        <v>-957.98281238034</v>
       </c>
       <c r="G77" s="18">
-        <v>0.09268932300775967</v>
+        <v>-0.1524674979228564</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -17865,7 +17865,7 @@
         <v>257</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>1021</v>
@@ -17874,10 +17874,10 @@
         <v>1022</v>
       </c>
       <c r="F78" s="58">
-        <v>613.8117434862406</v>
+        <v>615.8663728981464</v>
       </c>
       <c r="G78" s="18">
-        <v>0.08765402744159732</v>
+        <v>0.09801804762789947</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -17885,19 +17885,19 @@
         <v>259</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F79" s="58">
-        <v>444.5293674642207</v>
+        <v>-557.2149320389944</v>
       </c>
       <c r="G79" s="18">
-        <v>0.06348003241677658</v>
+        <v>-0.08868339326688265</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -17905,19 +17905,19 @@
         <v>261</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F80" s="58">
-        <v>292.3325803279577</v>
+        <v>539.5592942004287</v>
       </c>
       <c r="G80" s="18">
-        <v>0.04174590709621076</v>
+        <v>0.08587341495548735</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -17925,7 +17925,7 @@
         <v>263</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>1027</v>
+        <v>1003</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>1028</v>
@@ -17934,10 +17934,10 @@
         <v>1029</v>
       </c>
       <c r="F81" s="58">
-        <v>-175.2997633786954</v>
+        <v>292.9434942508615</v>
       </c>
       <c r="G81" s="18">
-        <v>-0.02503329470764048</v>
+        <v>0.04662334336691084</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -17945,7 +17945,7 @@
         <v>265</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>502</v>
+        <v>1018</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>1030</v>
@@ -17954,10 +17954,10 @@
         <v>1031</v>
       </c>
       <c r="F82" s="58">
-        <v>-145.9193751771118</v>
+        <v>-113.6924228273901</v>
       </c>
       <c r="G82" s="18">
-        <v>-0.02083769339991783</v>
+        <v>-0.01809468710425828</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -17965,7 +17965,7 @@
         <v>796</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>1015</v>
+        <v>502</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>1032</v>
@@ -17974,10 +17974,10 @@
         <v>1033</v>
       </c>
       <c r="F83" s="58">
-        <v>-114.8087815487188</v>
+        <v>60.42913012821009</v>
       </c>
       <c r="G83" s="18">
-        <v>-0.01639501393578882</v>
+        <v>0.009617582020505958</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -17985,19 +17985,19 @@
         <v>798</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>1018</v>
+        <v>1034</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F84" s="58">
-        <v>-59.93326258545858</v>
+        <v>-60.05670256871872</v>
       </c>
       <c r="G84" s="18">
-        <v>-0.008558636909572268</v>
+        <v>-0.009558308412024326</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -18005,19 +18005,19 @@
         <v>800</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>574</v>
+        <v>1011</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F85" s="58">
-        <v>28.2187969197139</v>
+        <v>-60.04895095283973</v>
       </c>
       <c r="G85" s="18">
-        <v>0.004029722835736052</v>
+        <v>-0.009557074705675262</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -18025,7 +18025,7 @@
         <v>803</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1038</v>
+        <v>574</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>1039</v>
@@ -18034,10 +18034,10 @@
         <v>1040</v>
       </c>
       <c r="F86" s="58">
-        <v>5.975793469320706</v>
+        <v>28.58037487079309</v>
       </c>
       <c r="G86" s="18">
-        <v>0.0008533599597983203</v>
+        <v>0.004548701907730104</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -18054,10 +18054,10 @@
         <v>1042</v>
       </c>
       <c r="F87" s="58">
-        <v>-2.757733943147116</v>
+        <v>-2.75773394314789</v>
       </c>
       <c r="G87" s="18">
-        <v>-0.0003938120918904516</v>
+        <v>-0.000438906407103427</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -18077,7 +18077,7 @@
         <v>-0.02991563824011332</v>
       </c>
       <c r="G88" s="18">
-        <v>-4.272036504773342E-06</v>
+        <v>-4.761215391643707E-06</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -18085,7 +18085,7 @@
         <v>1046</v>
       </c>
       <c r="G89" s="18">
-        <v>0.8646643109869251</v>
+        <v>0.8401759701853452</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -18317,7 +18317,7 @@
         <v>1072</v>
       </c>
       <c r="B114" s="58">
-        <v>7002.664468500492</v>
+        <v>6283.193634259337</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -18325,7 +18325,7 @@
         <v>1073</v>
       </c>
       <c r="B115" s="58">
-        <v>4132.803226139056</v>
+        <v>3462.041131021901</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -19488,7 +19488,7 @@
         <v>105</v>
       </c>
       <c r="B33" s="20">
-        <v>0.01167186110211138</v>
+        <v>0.02770553752646638</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>106</v>
@@ -20872,10 +20872,10 @@
         <v>278</v>
       </c>
       <c r="B126" s="16">
-        <v>0.116498</v>
+        <v>0.05563</v>
       </c>
       <c r="C126" s="22">
-        <v>2741.858462</v>
+        <v>5741.858462</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>279</v>
@@ -21297,7 +21297,7 @@
         <v>332</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -21658,28 +21658,28 @@
         <v>353</v>
       </c>
       <c r="C18" s="22">
-        <v>0</v>
+        <v>49973.679483</v>
       </c>
       <c r="D18" s="22">
-        <v>0</v>
+        <v>54827.64016800001</v>
       </c>
       <c r="E18" s="22">
-        <v>0</v>
+        <v>46495.032403</v>
       </c>
       <c r="F18" s="22">
-        <v>0</v>
+        <v>60628.13035399999</v>
       </c>
       <c r="G18" s="22">
-        <v>0</v>
+        <v>41965.464075</v>
       </c>
       <c r="H18" s="22">
-        <v>0</v>
+        <v>51336.529562</v>
       </c>
       <c r="I18" s="22">
-        <v>0</v>
+        <v>52790.166168</v>
       </c>
       <c r="J18" s="22">
-        <v>0</v>
+        <v>55258.956195</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -21722,28 +21722,28 @@
         <v>357</v>
       </c>
       <c r="C20" s="22">
-        <v>0</v>
+        <v>16103.355056</v>
       </c>
       <c r="D20" s="22">
-        <v>0</v>
+        <v>12497.341044</v>
       </c>
       <c r="E20" s="22">
-        <v>0</v>
+        <v>11219.472002</v>
       </c>
       <c r="F20" s="22">
-        <v>0</v>
+        <v>8930.538911</v>
       </c>
       <c r="G20" s="22">
-        <v>0</v>
+        <v>14750.961143</v>
       </c>
       <c r="H20" s="22">
-        <v>0</v>
+        <v>17626.177095</v>
       </c>
       <c r="I20" s="22">
-        <v>0</v>
+        <v>17166.415181</v>
       </c>
       <c r="J20" s="22">
-        <v>0</v>
+        <v>19722.054095</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -21850,28 +21850,28 @@
         <v>365</v>
       </c>
       <c r="C24" s="22">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="D24" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E24" s="22">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F24" s="22">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G24" s="22">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H24" s="22">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I24" s="22">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J24" s="22">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -22324,19 +22324,19 @@
       </c>
       <c r="C17" s="32">
         <f>IF((FS_Hist!$F$8)=0,"n/a",(FS_Hist!$F$18)/(FS_Hist!$F$8)*DaysYr)</f>
-        <v>0.0</v>
+        <v>95.33885400175808</v>
       </c>
       <c r="D17" s="32">
         <f>IF((FS_Hist!$G$8)=0,"n/a",(FS_Hist!$G$18)/(FS_Hist!$G$8)*DaysYr)</f>
-        <v>0.0</v>
+        <v>70.21150869439911</v>
       </c>
       <c r="E17" s="32">
         <f>IF((FS_Hist!$H$8)=0,"n/a",(FS_Hist!$H$18)/(FS_Hist!$H$8)*DaysYr)</f>
-        <v>0.0</v>
+        <v>68.55377546801134</v>
       </c>
       <c r="F17" s="33">
         <f>IF(COUNT(C17:E17)=0,0,AVERAGE(C17:E17))</f>
-        <v>0.0</v>
+        <v>78.03471272138951</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -22366,19 +22366,19 @@
       </c>
       <c r="C19" s="32">
         <f>IF((FS_Hist!$F$9)=0,"n/a",(FS_Hist!$F$20)/(FS_Hist!$F$9)*DaysYr)</f>
-        <v>0.0</v>
+        <v>16.652412009946783</v>
       </c>
       <c r="D19" s="32">
         <f>IF((FS_Hist!$G$9)=0,"n/a",(FS_Hist!$G$20)/(FS_Hist!$G$9)*DaysYr)</f>
-        <v>0.0</v>
+        <v>27.91968033675968</v>
       </c>
       <c r="E19" s="32">
         <f>IF((FS_Hist!$H$9)=0,"n/a",(FS_Hist!$H$20)/(FS_Hist!$H$9)*DaysYr)</f>
-        <v>0.0</v>
+        <v>26.307709330037472</v>
       </c>
       <c r="F19" s="33">
         <f>IF(COUNT(C19:E19)=0,0,AVERAGE(C19:E19))</f>
-        <v>0.0</v>
+        <v>23.626600558914646</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -22387,15 +22387,15 @@
       </c>
       <c r="C20" s="27">
         <f>FS_Hist!$E$18+FS_Hist!$E$19-FS_Hist!$E$20+FS_Hist!$E$21+FS_Hist!$E$22+FS_Hist!$E$23</f>
-        <v>82350.141788</v>
+        <v>117625.70218899999</v>
       </c>
       <c r="D20" s="27">
         <f>FS_Hist!$F$18+FS_Hist!$F$19-FS_Hist!$F$20+FS_Hist!$F$21+FS_Hist!$F$22+FS_Hist!$F$23</f>
-        <v>114930.62205900002</v>
+        <v>166628.213502</v>
       </c>
       <c r="E20" s="27">
         <f>FS_Hist!$G$18+FS_Hist!$G$19-FS_Hist!$G$20+FS_Hist!$G$21+FS_Hist!$G$22+FS_Hist!$G$23</f>
-        <v>133393.65231900002</v>
+        <v>160608.15525100002</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -22421,19 +22421,19 @@
       </c>
       <c r="C22" s="31">
         <f>IF(C20&gt;0,C21/C20,"")</f>
-        <v>0.16496272645373336</v>
+        <v>0.11549094849501694</v>
       </c>
       <c r="D22" s="31">
         <f>IF(D20&gt;0,D21/D20,"")</f>
-        <v>0.06788410257585517</v>
+        <v>0.04682257567903622</v>
       </c>
       <c r="E22" s="31">
         <f>IF(E20&gt;0,E21/E20,"")</f>
-        <v>0.06391189349154415</v>
+        <v>0.0530822415968626</v>
       </c>
       <c r="F22" s="31">
         <f>AVERAGE(C22:E22)</f>
-        <v>0.09891957417371089</v>
+        <v>0.07179858859030525</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>407</v>
@@ -22460,7 +22460,7 @@
       </c>
       <c r="C25" s="27">
         <f>FS_Hist!$J$18+FS_Hist!$J$19-FS_Hist!$J$20</f>
-        <v>59585.00276</v>
+        <v>95121.90486000001</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>410</v>
@@ -23755,67 +23755,67 @@
       </c>
       <c r="C62" s="40">
         <f>NWC_Open</f>
-        <v>59585.00276</v>
+        <v>95121.90486000001</v>
       </c>
       <c r="D62" s="27">
         <f>IF(D54=1,D56*DSO/DaysYr+D56*COGSR*DIO/DaysYr-D56*COGSR*DPO/DaysYr,C62)</f>
-        <v>57816.8772557815</v>
+        <v>103705.79965848745</v>
       </c>
       <c r="E62" s="27">
         <f>IF(E54=1,E56*DSO/DaysYr+E56*COGSR*DIO/DaysYr-E56*COGSR*DPO/DaysYr,D62)</f>
-        <v>61048.37307042094</v>
+        <v>109502.115084996</v>
       </c>
       <c r="F62" s="27">
         <f>IF(F54=1,F56*DSO/DaysYr+F56*COGSR*DIO/DaysYr-F56*COGSR*DPO/DaysYr,E62)</f>
-        <v>63730.10242041083</v>
+        <v>114312.31757099289</v>
       </c>
       <c r="G62" s="27">
         <f>IF(G54=1,G56*DSO/DaysYr+G56*COGSR*DIO/DaysYr-G56*COGSR*DPO/DaysYr,F62)</f>
-        <v>65767.16954437266</v>
+        <v>117966.19313597513</v>
       </c>
       <c r="H62" s="27">
         <f>IF(H54=1,H56*DSO/DaysYr+H56*COGSR*DIO/DaysYr-H56*COGSR*DPO/DaysYr,G62)</f>
-        <v>67082.51293526014</v>
+        <v>120325.51699869466</v>
       </c>
       <c r="I62" s="27">
         <f>IF(I54=1,I56*DSO/DaysYr+I56*COGSR*DIO/DaysYr-I56*COGSR*DPO/DaysYr,H62)</f>
-        <v>68424.16319396533</v>
+        <v>122732.02733866854</v>
       </c>
       <c r="J62" s="27">
         <f>IF(J54=1,J56*DSO/DaysYr+J56*COGSR*DIO/DaysYr-J56*COGSR*DPO/DaysYr,I62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="K62" s="27">
         <f>IF(K54=1,K56*DSO/DaysYr+K56*COGSR*DIO/DaysYr-K56*COGSR*DPO/DaysYr,J62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="L62" s="27">
         <f>IF(L54=1,L56*DSO/DaysYr+L56*COGSR*DIO/DaysYr-L56*COGSR*DPO/DaysYr,K62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="M62" s="27">
         <f>IF(M54=1,M56*DSO/DaysYr+M56*COGSR*DIO/DaysYr-M56*COGSR*DPO/DaysYr,L62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="N62" s="27">
         <f>IF(N54=1,N56*DSO/DaysYr+N56*COGSR*DIO/DaysYr-N56*COGSR*DPO/DaysYr,M62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="O62" s="27">
         <f>IF(O54=1,O56*DSO/DaysYr+O56*COGSR*DIO/DaysYr-O56*COGSR*DPO/DaysYr,N62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="P62" s="27">
         <f>IF(P54=1,P56*DSO/DaysYr+P56*COGSR*DIO/DaysYr-P56*COGSR*DPO/DaysYr,O62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="Q62" s="27">
         <f>IF(Q54=1,Q56*DSO/DaysYr+Q56*COGSR*DIO/DaysYr-Q56*COGSR*DPO/DaysYr,P62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
       <c r="R62" s="27">
         <f>IF(R54=1,R56*DSO/DaysYr+R56*COGSR*DIO/DaysYr-R56*COGSR*DPO/DaysYr,Q62)</f>
-        <v>69792.64645784463</v>
+        <v>125186.66788544192</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -23827,31 +23827,31 @@
       </c>
       <c r="D63" s="40">
         <f>IF(D54=1,D62-C62,0)</f>
-        <v>-1768.1255042185003</v>
+        <v>8583.89479848744</v>
       </c>
       <c r="E63" s="40">
         <f>IF(E54=1,E62-D62,0)</f>
-        <v>3231.4958146394347</v>
+        <v>5796.315426508547</v>
       </c>
       <c r="F63" s="40">
         <f>IF(F54=1,F62-E62,0)</f>
-        <v>2681.729349989895</v>
+        <v>4810.202485996895</v>
       </c>
       <c r="G63" s="40">
         <f>IF(G54=1,G62-F62,0)</f>
-        <v>2037.0671239618314</v>
+        <v>3653.8755649822415</v>
       </c>
       <c r="H63" s="40">
         <f>IF(H54=1,H62-G62,0)</f>
-        <v>1315.3433908874722</v>
+        <v>2359.323862719524</v>
       </c>
       <c r="I63" s="40">
         <f>IF(I54=1,I62-H62,0)</f>
-        <v>1341.6502587051946</v>
+        <v>2406.5103399738873</v>
       </c>
       <c r="J63" s="40">
         <f>IF(J54=1,J62-I62,0)</f>
-        <v>1368.4832638793014</v>
+        <v>2454.640546773371</v>
       </c>
       <c r="K63" s="40">
         <f>IF(K54=1,K62-J62,0)</f>
@@ -24127,35 +24127,35 @@
       </c>
       <c r="K67" s="30">
         <f>IF(K54=1,0,K55/RONIC)</f>
-        <v>0.16702609441585456</v>
+        <v>0.16813419343450642</v>
       </c>
       <c r="L67" s="30">
         <f>IF(L54=1,0,L55/RONIC)</f>
-        <v>0.16702609441585456</v>
+        <v>0.16813419343450642</v>
       </c>
       <c r="M67" s="30">
         <f>IF(M54=1,0,M55/RONIC)</f>
-        <v>0.16702609441585456</v>
+        <v>0.16813419343450642</v>
       </c>
       <c r="N67" s="30">
         <f>IF(N54=1,0,N55/RONIC)</f>
-        <v>0.16702609441585456</v>
+        <v>0.16813419343450642</v>
       </c>
       <c r="O67" s="30">
         <f>IF(O54=1,0,O55/RONIC)</f>
-        <v>0.16702609441585453</v>
+        <v>0.1681341934345064</v>
       </c>
       <c r="P67" s="30">
         <f>IF(P54=1,0,P55/RONIC)</f>
-        <v>0.16702609441585453</v>
+        <v>0.1681341934345064</v>
       </c>
       <c r="Q67" s="30">
         <f>IF(Q54=1,0,Q55/RONIC)</f>
-        <v>0.16702609441585453</v>
+        <v>0.1681341934345064</v>
       </c>
       <c r="R67" s="30">
         <f>IF(R54=1,0,R55/RONIC)</f>
-        <v>0.16702609441585453</v>
+        <v>0.1681341934345064</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -24195,35 +24195,35 @@
       </c>
       <c r="K68" s="40">
         <f>K66*K67</f>
-        <v>4695.37983705998</v>
+        <v>4726.530333680525</v>
       </c>
       <c r="L68" s="40">
         <f>L66*L67</f>
-        <v>4787.744112688775</v>
+        <v>4819.507380406799</v>
       </c>
       <c r="M68" s="40">
         <f>M66*M67</f>
-        <v>4881.955673830149</v>
+        <v>4914.343968067601</v>
       </c>
       <c r="N68" s="40">
         <f>N66*N67</f>
-        <v>4978.05146619435</v>
+        <v>5011.077287481618</v>
       </c>
       <c r="O68" s="40">
         <f>O66*O67</f>
-        <v>5076.069174405833</v>
+        <v>5109.745273283915</v>
       </c>
       <c r="P68" s="40">
         <f>P66*P67</f>
-        <v>5176.047236781547</v>
+        <v>5210.386618802258</v>
       </c>
       <c r="Q68" s="40">
         <f>Q66*Q67</f>
-        <v>5278.0248604047765</v>
+        <v>5313.040791230968</v>
       </c>
       <c r="R68" s="40">
         <f>R66*R67</f>
-        <v>5382.042036500469</v>
+        <v>5417.748047108253</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -24235,63 +24235,63 @@
       </c>
       <c r="D69" s="40">
         <f>D66+D60-D61-D63-D68</f>
-        <v>1088.1558589868573</v>
+        <v>-9263.864443719081</v>
       </c>
       <c r="E69" s="40">
         <f>E66+E60-E61-E63-E68</f>
-        <v>-2837.8321879682517</v>
+        <v>-5402.651799837364</v>
       </c>
       <c r="F69" s="40">
         <f>F66+F60-F61-F63-F68</f>
-        <v>-316.36124490337534</v>
+        <v>-2444.8343809103753</v>
       </c>
       <c r="G69" s="40">
         <f>G66+G60-G61-G63-G68</f>
-        <v>2402.205094190198</v>
+        <v>785.3966531697879</v>
       </c>
       <c r="H69" s="40">
         <f>H66+H60-H61-H63-H68</f>
-        <v>5256.800480641788</v>
+        <v>4212.8200088097365</v>
       </c>
       <c r="I69" s="40">
         <f>I66+I60-I61-I63-I68</f>
-        <v>7447.089223449144</v>
+        <v>6382.229142180451</v>
       </c>
       <c r="J69" s="40">
         <f>J66+J60-J61-J63-J68</f>
-        <v>9723.071595776491</v>
+        <v>8636.914312882422</v>
       </c>
       <c r="K69" s="40">
         <f>K66+K60-K61-K63-K68</f>
-        <v>23416.274533362044</v>
+        <v>23385.1240367415</v>
       </c>
       <c r="L69" s="40">
         <f>L66+L60-L61-L63-L68</f>
-        <v>23876.903345141684</v>
+        <v>23845.14007742366</v>
       </c>
       <c r="M69" s="40">
         <f>M66+M60-M61-M63-M68</f>
-        <v>24346.74473315692</v>
+        <v>24314.35643891947</v>
       </c>
       <c r="N69" s="40">
         <f>N66+N60-N61-N63-N68</f>
-        <v>24825.982948932466</v>
+        <v>24792.957127645197</v>
       </c>
       <c r="O69" s="40">
         <f>O66+O60-O61-O63-O68</f>
-        <v>25314.805929023518</v>
+        <v>25281.129830145434</v>
       </c>
       <c r="P69" s="40">
         <f>P66+P60-P61-P63-P68</f>
-        <v>25813.40536871639</v>
+        <v>25779.065986695678</v>
       </c>
       <c r="Q69" s="40">
         <f>Q66+Q60-Q61-Q63-Q68</f>
-        <v>26321.97679720312</v>
+        <v>26286.96086637693</v>
       </c>
       <c r="R69" s="40">
         <f>R66+R60-R61-R63-R68</f>
-        <v>26840.719654259585</v>
+        <v>26805.0136436518</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -24936,7 +24936,7 @@
       </c>
       <c r="C15" s="39">
         <f>DE_Target</f>
-        <v>0.011671861102111</v>
+        <v>0.027705537526466</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -24945,7 +24945,7 @@
       </c>
       <c r="C16" s="44">
         <f>BetaU*(1+(1-T_Hamada)*DE_Target)</f>
-        <v>0.9756096799715498</v>
+        <v>0.9877008371931824</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -24954,7 +24954,7 @@
       </c>
       <c r="C17" s="47">
         <f>Rf+BetaL*MRP_Eff+SRP_Eff</f>
-        <v>0.12007877439772398</v>
+        <v>0.12104606697545459</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="C20" s="45">
         <f>IF(SUM(BorrowAmt)&gt;0,SUMPRODUCT(BorrowRate,BorrowAmt)/SUM(BorrowAmt),0)</f>
-        <v>0.11649800000000002</v>
+        <v>0.05563</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>509</v>
@@ -25021,7 +25021,7 @@
       </c>
       <c r="C22" s="47">
         <f>N(Kd_Actual)</f>
-        <v>0.11649800000000002</v>
+        <v>0.05563</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="C23" s="47">
         <f>MAX(C22,Rf)</f>
-        <v>0.11649800000000002</v>
+        <v>0.05563</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -25045,11 +25045,11 @@
       </c>
       <c r="C24" s="47">
         <f>Kd_Pre*(1-T_Kd)</f>
-        <v>0.09086844000000002</v>
+        <v>0.043391400000000004</v>
       </c>
       <c r="E24" s="5" t="str">
         <f>IF(DE_Target=0,"미사용(D/E 0 → WACC에 Kd 반영 안 됨)","사용(D/V "&amp;TEXT(DE_Target/(1+DE_Target),"0.0%")&amp;")")</f>
-        <v>사용(D/V 1.2%)</v>
+        <v>사용(D/V 2.7%)</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -25061,7 +25061,7 @@
       </c>
       <c r="C25" s="30">
         <f>DE_Target/(1+DE_Target)</f>
-        <v>0.011537200500363552</v>
+        <v>0.026958634078346116</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="C26" s="47">
         <f>(1-WD)*Ke+WD*Kd_AT</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="C27" s="48">
         <f>IF(ISNUMBER(WaccOvr),WaccOvr,WaccCalc)</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>517</v>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="C31" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_1)+WD*Kd_AT</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="C32" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_2)+WD*Kd_AT</f>
-        <v>0.12962639690809113</v>
+        <v>0.12868301688320402</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -25134,7 +25134,7 @@
       </c>
       <c r="C33" s="45">
         <f>(1-WD)*(Rf+BetaL*MRP+SRP_3)+WD*Kd_AT</f>
-        <v>0.1395110249030875</v>
+        <v>0.13841343054242056</v>
       </c>
     </row>
   </sheetData>
@@ -25435,63 +25435,63 @@
       </c>
       <c r="D8" s="27">
         <f>Forecast!D69</f>
-        <v>1088.1558589868573</v>
+        <v>-9263.864443719081</v>
       </c>
       <c r="E8" s="27">
         <f>Forecast!E69</f>
-        <v>-2837.8321879682517</v>
+        <v>-5402.651799837364</v>
       </c>
       <c r="F8" s="27">
         <f>Forecast!F69</f>
-        <v>-316.36124490337534</v>
+        <v>-2444.8343809103753</v>
       </c>
       <c r="G8" s="27">
         <f>Forecast!G69</f>
-        <v>2402.205094190198</v>
+        <v>785.3966531697879</v>
       </c>
       <c r="H8" s="27">
         <f>Forecast!H69</f>
-        <v>5256.800480641788</v>
+        <v>4212.8200088097365</v>
       </c>
       <c r="I8" s="27">
         <f>Forecast!I69</f>
-        <v>7447.089223449144</v>
+        <v>6382.229142180451</v>
       </c>
       <c r="J8" s="27">
         <f>Forecast!J69</f>
-        <v>9723.071595776491</v>
+        <v>8636.914312882422</v>
       </c>
       <c r="K8" s="27">
         <f>Forecast!K69</f>
-        <v>23416.274533362044</v>
+        <v>23385.1240367415</v>
       </c>
       <c r="L8" s="27">
         <f>Forecast!L69</f>
-        <v>23876.903345141684</v>
+        <v>23845.14007742366</v>
       </c>
       <c r="M8" s="27">
         <f>Forecast!M69</f>
-        <v>24346.74473315692</v>
+        <v>24314.35643891947</v>
       </c>
       <c r="N8" s="27">
         <f>Forecast!N69</f>
-        <v>24825.982948932466</v>
+        <v>24792.957127645197</v>
       </c>
       <c r="O8" s="27">
         <f>Forecast!O69</f>
-        <v>25314.805929023518</v>
+        <v>25281.129830145434</v>
       </c>
       <c r="P8" s="27">
         <f>Forecast!P69</f>
-        <v>25813.40536871639</v>
+        <v>25779.065986695678</v>
       </c>
       <c r="Q8" s="27">
         <f>Forecast!Q69</f>
-        <v>26321.97679720312</v>
+        <v>26286.96086637693</v>
       </c>
       <c r="R8" s="27">
         <f>Forecast!R69</f>
-        <v>26840.719654259585</v>
+        <v>26805.0136436518</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -25636,63 +25636,63 @@
       </c>
       <c r="D11" s="39">
         <f>(1+WACC)^(-D10)</f>
-        <v>0.9718955713661164</v>
+        <v>0.9720682969048091</v>
       </c>
       <c r="E11" s="39">
         <f>(1+WACC)^(-E10)</f>
-        <v>0.8926480631994347</v>
+        <v>0.8932802108304524</v>
       </c>
       <c r="F11" s="39">
         <f>(1+WACC)^(-F10)</f>
-        <v>0.7970675040531315</v>
+        <v>0.7981952824833334</v>
       </c>
       <c r="G11" s="39">
         <f>(1+WACC)^(-G10)</f>
-        <v>0.7117212619499593</v>
+        <v>0.7132316391363281</v>
       </c>
       <c r="H11" s="39">
         <f>(1+WACC)^(-H10)</f>
-        <v>0.6356119613549911</v>
+        <v>0.637410053903379</v>
       </c>
       <c r="I11" s="39">
         <f>(1+WACC)^(-I10)</f>
-        <v>0.5676415571886396</v>
+        <v>0.5696488413064489</v>
       </c>
       <c r="J11" s="39">
         <f>(1+WACC)^(-J10)</f>
-        <v>0.5068611671698616</v>
+        <v>0.5090127513069989</v>
       </c>
       <c r="K11" s="39">
         <f>(1+WACC)^(-K10)</f>
-        <v>0.4525888556454266</v>
+        <v>0.4548310506502692</v>
       </c>
       <c r="L11" s="39">
         <f>(1+WACC)^(-L10)</f>
-        <v>0.40419038407823543</v>
+        <v>0.40647928191040894</v>
       </c>
       <c r="M11" s="39">
         <f>(1+WACC)^(-M10)</f>
-        <v>0.36096749741734907</v>
+        <v>0.36326764935283107</v>
       </c>
       <c r="N11" s="39">
         <f>(1+WACC)^(-N10)</f>
-        <v>0.32231679434728183</v>
+        <v>0.32459973978677403</v>
       </c>
       <c r="O11" s="39">
         <f>(1+WACC)^(-O10)</f>
-        <v>0.28780462690299496</v>
+        <v>0.2900478235740269</v>
       </c>
       <c r="P11" s="39">
         <f>(1+WACC)^(-P10)</f>
-        <v>0.25702767807113214</v>
+        <v>0.259213681382326</v>
       </c>
       <c r="Q11" s="39">
         <f>(1+WACC)^(-Q10)</f>
-        <v>0.22954192226000683</v>
+        <v>0.23165742734362954</v>
       </c>
       <c r="R11" s="39">
         <f>(1+WACC)^(-R10)</f>
-        <v>0.2049636520753473</v>
+        <v>0.2069987260615659</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -25704,63 +25704,63 @@
       </c>
       <c r="D12" s="40">
         <f>D8*D11</f>
-        <v>1057.5738603054187</v>
+        <v>-9005.108932563024</v>
       </c>
       <c r="E12" s="40">
         <f>E8*E11</f>
-        <v>-2533.185406274874</v>
+        <v>-4826.081938802244</v>
       </c>
       <c r="F12" s="40">
         <f>F8*F11</f>
-        <v>-252.16126785427485</v>
+        <v>-1951.4552692957225</v>
       </c>
       <c r="G12" s="40">
         <f>G8*G11</f>
-        <v>1709.7004410996685</v>
+        <v>560.169742312474</v>
       </c>
       <c r="H12" s="40">
         <f>H8*H11</f>
-        <v>3341.2852639525872</v>
+        <v>2685.293828900648</v>
       </c>
       <c r="I12" s="40">
         <f>I8*I11</f>
-        <v>4227.277323321409</v>
+        <v>3635.629435795345</v>
       </c>
       <c r="J12" s="40">
         <f>J8*J11</f>
-        <v>4928.247417511401</v>
+        <v>4396.299517203079</v>
       </c>
       <c r="K12" s="40">
         <f>K8*K11</f>
-        <v>10597.944894533473</v>
+        <v>10636.280535218</v>
       </c>
       <c r="L12" s="40">
         <f>L8*L11</f>
-        <v>9650.814733671721</v>
+        <v>9692.555415724282</v>
       </c>
       <c r="M12" s="40">
         <f>M8*M11</f>
-        <v>8788.383516586679</v>
+        <v>8832.619109093148</v>
       </c>
       <c r="N12" s="40">
         <f>N8*N11</f>
-        <v>8001.831240620191</v>
+        <v>8047.787432178276</v>
       </c>
       <c r="O12" s="40">
         <f>O8*O11</f>
-        <v>7285.718275524338</v>
+        <v>7332.736684726092</v>
       </c>
       <c r="P12" s="40">
         <f>P8*P11</f>
-        <v>6634.759645030071</v>
+        <v>6682.28659700929</v>
       </c>
       <c r="Q12" s="40">
         <f>Q8*Q11</f>
-        <v>6041.997151713302</v>
+        <v>6089.569726987546</v>
       </c>
       <c r="R12" s="40">
         <f>R8*R11</f>
-        <v>5501.371924667598</v>
+        <v>5548.603676298816</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="C22" s="27">
         <f>SUMPRODUCT((Forecast!$D$48:$R$48&gt;1)*Forecast!$D$54:$R$54*(Forecast!$D$61:$R$61-Forecast!$D$60:$R$60+Forecast!$D$63:$R$63))</f>
-        <v>105434.23062591458</v>
+        <v>114939.32965080593</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -25873,7 +25873,7 @@
       </c>
       <c r="C23" s="31">
         <f>IF(C22&gt;0,(C21-C19)/C22,0)</f>
-        <v>0.14574114982678935</v>
+        <v>0.13368884305491455</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="C24" s="49">
         <f>IF(C22&lt;=0,WACC,IF(C23&lt;WACC,WACC,IF(C23&gt;RonicCap,MAX(RonicCap,WACC),C23)))</f>
-        <v>0.11974176891309476</v>
+        <v>0.11895260322398749</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>539</v>
@@ -25971,7 +25971,7 @@
       </c>
       <c r="C33" s="27">
         <f>C32*(1-GEff/RONIC)</f>
-        <v>27369.837368457178</v>
+        <v>27333.42747647217</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="C34" s="50">
         <f>C33/(WACC-GEff)*IF(MidYear=1,(1+WACC)^0.5,1)</f>
-        <v>290371.5681902389</v>
+        <v>292194.95619459706</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="C36" s="27">
         <f>C34*(1+WACC)^(-C35)</f>
-        <v>56234.743264340585</v>
+        <v>57169.932152751244</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="C37" s="40">
         <f>SUM(D12:R12)</f>
-        <v>74981.55901440872</v>
+        <v>58357.185560786005</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -26028,7 +26028,7 @@
       </c>
       <c r="C38" s="40">
         <f>C37+C36</f>
-        <v>131216.3022787493</v>
+        <v>115527.11771353724</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -26049,7 +26049,7 @@
       </c>
       <c r="C40" s="50">
         <f>C38*(1+WACC)^(C39/DaysYr)</f>
-        <v>135010.70088662815</v>
+        <v>118846.70869463647</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -26058,7 +26058,7 @@
       </c>
       <c r="C41" s="29">
         <f>C36/C38</f>
-        <v>0.4285652185570535</v>
+        <v>0.4948615812826791</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -26115,7 +26115,7 @@
       </c>
       <c r="C46" s="52">
         <f>IF(C45&gt;0,C34/C45,"N/M")</f>
-        <v>6.355342936027976</v>
+        <v>6.395251306345912</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -26154,7 +26154,7 @@
       </c>
       <c r="C49" s="27">
         <f>IF(ISNUMBER(C47),C48*(1+WACC)^(-C35),"N/M")</f>
-        <v>66005.69214020905</v>
+        <v>66684.62674158988</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C50" s="40">
         <f>IF(ISNUMBER(C47),C37+C49,"N/M")</f>
-        <v>140987.25115461776</v>
+        <v>125041.81230237588</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="C51" s="27">
         <f>IF(ISNUMBER(C47),C50*(1+WACC)^(C39/DaysYr),"N/M")</f>
-        <v>145064.1975417618</v>
+        <v>128634.801382295</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -26187,7 +26187,7 @@
       </c>
       <c r="C52" s="29">
         <f>IF(ISNUMBER(C47),C49/C50,"N/M")</f>
-        <v>0.46816780666091573</v>
+        <v>0.5332986263853344</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -26196,7 +26196,7 @@
       </c>
       <c r="C53" s="30">
         <f>IF(ISNUMBER(C47),(C48/IF(MidYear=1,(1+WACC)^0.5,1)*WACC-C33/(1+GEff))/(C48/IF(MidYear=1,(1+WACC)^0.5,1)+C33/(1+GEff)),"N/M")</f>
-        <v>0.03362948443738433</v>
+        <v>0.0330346553356744</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -26230,11 +26230,11 @@
       </c>
       <c r="C57" s="54">
         <f>PerShare</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="D57" s="52">
         <f>ImpliedMultiple</f>
-        <v>6.355342936027976</v>
+        <v>6.395251306345912</v>
       </c>
       <c r="E57" s="30">
         <f>GEff</f>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="F57" s="29">
         <f>TVShare</f>
-        <v>0.4285652185570535</v>
+        <v>0.4948615812826791</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="C58" s="54">
         <f>PerShareExit</f>
-        <v>7344.433524163212</v>
+        <v>6615.940270514709</v>
       </c>
       <c r="D58" s="52">
         <f>ExitMult</f>
@@ -26259,11 +26259,11 @@
       </c>
       <c r="E58" s="31">
         <f>ImpliedG_Exit</f>
-        <v>0.03362948443738433</v>
+        <v>0.0330346553356744</v>
       </c>
       <c r="F58" s="29">
         <f>TVShare_Exit</f>
-        <v>0.46816780666091573</v>
+        <v>0.5332986263853344</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -26309,7 +26309,7 @@
       </c>
       <c r="C4" s="27">
         <f>EV_930</f>
-        <v>135010.70088662815</v>
+        <v>118846.70869463647</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>582</v>
@@ -26324,7 +26324,7 @@
       </c>
       <c r="C5" s="27">
         <f>FS_Hist!$J$24</f>
-        <v>0.0</v>
+        <v>5000.0</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>584</v>
@@ -26369,7 +26369,7 @@
       </c>
       <c r="C8" s="40">
         <f>C5+C6-C7</f>
-        <v>-59146.183334</v>
+        <v>-54146.183334</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="C12" s="55">
         <f>C4-C8+C9-C11</f>
-        <v>205990.74914662816</v>
+        <v>184826.75695463648</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -26438,7 +26438,7 @@
       </c>
       <c r="C13" s="40">
         <f>C12-C4</f>
-        <v>70980.04826000001</v>
+        <v>65980.04826000001</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>598</v>
@@ -26483,7 +26483,7 @@
       </c>
       <c r="C16" s="56">
         <f>C12*MnToWon/Shares</f>
-        <v>7002.664468500521</v>
+        <v>6283.193634259378</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>604</v>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C17" s="28">
         <f>PerShare/Close-1</f>
-        <v>-0.6498667765749739</v>
+        <v>-0.6858403182870311</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>606</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C18" s="27">
         <f>IF(ISNUMBER(EVExit_930),EVExit_930+BridgeAdj,"N/M")</f>
-        <v>216044.2458017618</v>
+        <v>194614.849642295</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -26522,7 +26522,7 @@
       </c>
       <c r="C19" s="57">
         <f>IF(ISNUMBER(C18),C18*MnToWon/Shares,"N/M")</f>
-        <v>7344.433524163212</v>
+        <v>6615.940270514709</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -26794,28 +26794,28 @@
       </c>
       <c r="H15" s="57">
         <f>IF(OR(C15=0,NOT(ISNUMBER(D15)),NOT(ISNUMBER(G15)),N(G15)&lt;=0),"N/M",(D15*G15+BridgeAdj)*MnToWon/Shares)</f>
-        <v>5260.596670699279</v>
+        <v>5090.621453425907</v>
       </c>
       <c r="I15" s="57">
         <f>IF(OR(C15=0,NOT(ISNUMBER(E15)),NOT(ISNUMBER(G15)),N(G15)&lt;=0),"N/M",(E15*G15+BridgeAdj)*MnToWon/Shares)</f>
-        <v>6561.230037235493</v>
+        <v>6391.2548199621215</v>
       </c>
       <c r="J15" s="57">
         <f>IF(OR(C15=0,NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15)),N(G15)&lt;=0),"N/M",(F15*G15+BridgeAdj)*MnToWon/Shares)</f>
-        <v>7286.707794228766</v>
+        <v>7116.732576955395</v>
       </c>
       <c r="K15" s="5">
         <f>IF(C15&lt;PeerNWarn,"n&lt;"&amp;PeerNWarn,"")</f>
         <v/>
       </c>
       <c r="L15" s="58">
-        <v>5260.596670699277</v>
+        <v>5090.621453425906</v>
       </c>
       <c r="M15" s="58">
-        <v>6561.230037235491</v>
+        <v>6391.25481996212</v>
       </c>
       <c r="N15" s="58">
-        <v>7286.707794228767</v>
+        <v>7116.732576955396</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -26844,15 +26844,15 @@
       </c>
       <c r="H16" s="57">
         <f>IF(OR(C16=0,NOT(ISNUMBER(D16)),NOT(ISNUMBER(G16)),N(G16)&lt;=0),"N/M",(D16*G16+BridgeAdj)*MnToWon/Shares)</f>
-        <v>5260.596670699279</v>
+        <v>5090.621453425907</v>
       </c>
       <c r="I16" s="57">
         <f>IF(OR(C16=0,NOT(ISNUMBER(E16)),NOT(ISNUMBER(G16)),N(G16)&lt;=0),"N/M",(E16*G16+BridgeAdj)*MnToWon/Shares)</f>
-        <v>6561.230037235493</v>
+        <v>6391.2548199621215</v>
       </c>
       <c r="J16" s="57">
         <f>IF(OR(C16=0,NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16)),N(G16)&lt;=0),"N/M",(F16*G16+BridgeAdj)*MnToWon/Shares)</f>
-        <v>7286.707794228766</v>
+        <v>7116.732576955395</v>
       </c>
       <c r="K16" s="5">
         <f>IF(C16&lt;PeerNWarn,"n&lt;"&amp;PeerNWarn,"")</f>
@@ -26885,28 +26885,28 @@
       </c>
       <c r="H17" s="57">
         <f>IF(OR(C17=0,NOT(ISNUMBER(D17)),NOT(ISNUMBER(G17)),N(G17)&lt;=0),"N/M",(D17*G17+BridgeAdj)*MnToWon/Shares)</f>
-        <v>10755.750497574374</v>
+        <v>10585.775280301003</v>
       </c>
       <c r="I17" s="57">
         <f>IF(OR(C17=0,NOT(ISNUMBER(E17)),NOT(ISNUMBER(G17)),N(G17)&lt;=0),"N/M",(E17*G17+BridgeAdj)*MnToWon/Shares)</f>
-        <v>12826.06021530625</v>
+        <v>12656.084998032879</v>
       </c>
       <c r="J17" s="57">
         <f>IF(OR(C17=0,NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17)),N(G17)&lt;=0),"N/M",(F17*G17+BridgeAdj)*MnToWon/Shares)</f>
-        <v>17067.37314657971</v>
+        <v>16897.39792930634</v>
       </c>
       <c r="K17" s="5">
         <f>IF(C17&lt;PeerNWarn,"n&lt;"&amp;PeerNWarn,"")</f>
         <v/>
       </c>
       <c r="L17" s="58">
-        <v>10755.75049757438</v>
+        <v>10585.775280301</v>
       </c>
       <c r="M17" s="58">
-        <v>12826.06021530625</v>
+        <v>12656.08499803288</v>
       </c>
       <c r="N17" s="58">
-        <v>17067.37314657971</v>
+        <v>16897.39792930633</v>
       </c>
     </row>
     <row r="18" spans="1:14">
